--- a/data/raw/FORMATOS RA CICLO UNO RC/FormatoRA_AdmonHotelGastro_PBOG.xlsx
+++ b/data/raw/FORMATOS RA CICLO UNO RC/FormatoRA_AdmonHotelGastro_PBOG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://poligran-my.sharepoint.com/personal/micortes_poligran_edu_co/Documents/Escritorio/FORMATOS RA CICLO UNO RC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Analisis_Curricular/data/raw/FORMATOS RA CICLO UNO RC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2394" documentId="13_ncr:1_{22BA8ED0-1E41-4BD6-8060-7101AA11B8A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AF80861-3958-4003-90C4-78723DAB2D43}"/>
+  <xr:revisionPtr revIDLastSave="2395" documentId="13_ncr:1_{22BA8ED0-1E41-4BD6-8060-7101AA11B8A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F93BE8A1-6272-4EC3-B5B8-6535C0D2FBF0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Paso1 Analisis perfil egreso" sheetId="1" r:id="rId1"/>
@@ -885,6 +885,7 @@
         <sz val="8"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Gill Sans MT"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Componentes fundamentales aplicables a la solución de problemas en la vida profesional
 </t>
@@ -894,6 +895,7 @@
         <sz val="8"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Gill Sans MT"/>
+        <family val="2"/>
       </rPr>
       <t>[Listar, según lo escrito en el perfil profesional, qué debe saber el egresado en las categorías de Saber -conocimientos, hechos, teorías-, Saber hacer -técnicas, procedimientos, metodologías-, y Saber ser -valores, condiciones, etc.]</t>
     </r>
@@ -905,6 +907,7 @@
         <sz val="8"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Gill Sans MT"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Componentes fundamentales de la ocupación laboral del profesional
 </t>
@@ -914,6 +917,7 @@
         <sz val="8"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Gill Sans MT"/>
+        <family val="2"/>
       </rPr>
       <t>[Listar, según lo escrito en el perfil ocupacional, en qué áreas, qué tareas potenciales y en qué poblaciones o contextos podrá laborar el profesional.]</t>
     </r>
@@ -925,6 +929,7 @@
         <sz val="8"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Gill Sans MT"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve">Diferencial (valor agregado) del profesional
 </t>
@@ -934,6 +939,7 @@
         <sz val="8"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Gill Sans MT"/>
+        <family val="2"/>
       </rPr>
       <t>[Listar, según lo escrito en los perfiles, los elementos que son diferenciales y generan un valor agregado al egresado.]</t>
     </r>
@@ -3702,7 +3708,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3763,6 +3769,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Gill Sans MT"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -3796,11 +3803,7 @@
       <sz val="8"/>
       <color rgb="FFFFFFFF"/>
       <name val="Gill Sans MT"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Gill Sans MT"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -4231,10 +4234,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4253,10 +4256,10 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4316,34 +4319,34 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4367,11 +4370,11 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4380,27 +4383,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4412,10 +4412,10 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4423,6 +4423,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4436,14 +4439,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -7518,7 +7521,7 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="3" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+  <tableStyles count="4" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Estilo de tabla 1" pivot="0" count="1" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="headerRow" dxfId="155"/>
     </tableStyle>
@@ -7528,6 +7531,7 @@
     <tableStyle name="Estilo de tabla 3" pivot="0" count="1" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
       <tableStyleElement type="headerRow" dxfId="153"/>
     </tableStyle>
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{65A7FD53-397E-4589-A622-65A9193C631C}"/>
   </tableStyles>
   <colors>
     <mruColors>
@@ -8515,20 +8519,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="76.26953125" defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="76.21875" defaultRowHeight="17.25" customHeight="1" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="19.1796875" style="16" customWidth="1"/>
-    <col min="2" max="2" width="12.7265625" style="16" customWidth="1"/>
+    <col min="1" max="1" width="19.21875" style="16" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" style="16" customWidth="1"/>
     <col min="3" max="3" width="38" style="16" customWidth="1"/>
-    <col min="4" max="4" width="48.26953125" style="16" customWidth="1"/>
-    <col min="5" max="5" width="24.453125" style="16" customWidth="1"/>
-    <col min="6" max="6" width="32.26953125" style="21" customWidth="1"/>
-    <col min="7" max="7" width="40.26953125" style="21" customWidth="1"/>
-    <col min="8" max="8" width="22.7265625" style="16" customWidth="1"/>
-    <col min="9" max="9" width="25.453125" style="16" customWidth="1"/>
+    <col min="4" max="4" width="48.21875" style="16" customWidth="1"/>
+    <col min="5" max="5" width="24.44140625" style="16" customWidth="1"/>
+    <col min="6" max="6" width="32.21875" style="21" customWidth="1"/>
+    <col min="7" max="7" width="40.21875" style="21" customWidth="1"/>
+    <col min="8" max="8" width="22.77734375" style="16" customWidth="1"/>
+    <col min="9" max="9" width="25.44140625" style="16" customWidth="1"/>
     <col min="10" max="10" width="39" style="16" customWidth="1"/>
-    <col min="11" max="11" width="40.54296875" style="16" customWidth="1"/>
-    <col min="12" max="16384" width="76.26953125" style="16"/>
+    <col min="11" max="11" width="40.5546875" style="16" customWidth="1"/>
+    <col min="12" max="16384" width="76.21875" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="39.75" customHeight="1" x14ac:dyDescent="0.5">
@@ -8544,16 +8548,16 @@
       <c r="D1" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="92" t="s">
+      <c r="E1" s="91" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="93"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="92" t="s">
+      <c r="F1" s="92"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="93"/>
-      <c r="J1" s="94"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="93"/>
       <c r="K1" s="29" t="s">
         <v>6</v>
       </c>
@@ -8593,17 +8597,17 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="49.5" x14ac:dyDescent="0.5">
-      <c r="A3" s="96" t="s">
+    <row r="3" spans="1:11" ht="54" x14ac:dyDescent="0.5">
+      <c r="A3" s="94" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="96" t="s">
+      <c r="B3" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="97" t="s">
+      <c r="C3" s="96" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="97" t="s">
+      <c r="D3" s="96" t="s">
         <v>21</v>
       </c>
       <c r="E3" s="4" t="s">
@@ -8615,24 +8619,24 @@
       <c r="G3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="95" t="s">
+      <c r="H3" s="98" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="95" t="s">
+      <c r="I3" s="98" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="95" t="s">
+      <c r="J3" s="98" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="91" t="s">
+      <c r="K3" s="95" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="3" customFormat="1" ht="82.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="91"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="98"/>
+    <row r="4" spans="1:11" s="3" customFormat="1" ht="90" x14ac:dyDescent="0.3">
+      <c r="A4" s="95"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="97"/>
       <c r="E4" s="4" t="s">
         <v>29</v>
       </c>
@@ -8642,16 +8646,16 @@
       <c r="G4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="95"/>
-      <c r="I4" s="95"/>
-      <c r="J4" s="95"/>
-      <c r="K4" s="91"/>
-    </row>
-    <row r="5" spans="1:11" ht="66.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="91"/>
-      <c r="B5" s="91"/>
-      <c r="C5" s="98"/>
-      <c r="D5" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="95"/>
+    </row>
+    <row r="5" spans="1:11" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="95"/>
+      <c r="B5" s="95"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="97"/>
       <c r="E5" s="30" t="s">
         <v>32</v>
       </c>
@@ -8661,16 +8665,16 @@
       <c r="G5" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="95"/>
-      <c r="I5" s="95"/>
-      <c r="J5" s="95"/>
-      <c r="K5" s="91"/>
-    </row>
-    <row r="6" spans="1:11" s="3" customFormat="1" ht="66" x14ac:dyDescent="0.35">
-      <c r="A6" s="91"/>
-      <c r="B6" s="91"/>
-      <c r="C6" s="98"/>
-      <c r="D6" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="98"/>
+      <c r="K5" s="95"/>
+    </row>
+    <row r="6" spans="1:11" s="3" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="95"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="97"/>
       <c r="E6" s="38" t="s">
         <v>35</v>
       </c>
@@ -8681,13 +8685,13 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:11" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.5">
       <c r="E7" s="19"/>
       <c r="F7" s="19"/>
       <c r="G7" s="19"/>
       <c r="J7" s="16"/>
     </row>
-    <row r="8" spans="1:11" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:11" ht="18" x14ac:dyDescent="0.5">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -8696,29 +8700,29 @@
       <c r="F8" s="19"/>
       <c r="G8" s="19"/>
     </row>
-    <row r="9" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:11" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.5">
       <c r="E9" s="19"/>
       <c r="F9" s="19"/>
       <c r="G9" s="19"/>
       <c r="J9" s="16"/>
     </row>
-    <row r="10" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:11" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.5">
       <c r="E10" s="19"/>
       <c r="F10" s="19"/>
       <c r="G10" s="19"/>
       <c r="J10" s="16"/>
     </row>
-    <row r="11" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="E11" s="19"/>
       <c r="F11" s="19"/>
       <c r="G11" s="19"/>
     </row>
-    <row r="12" spans="1:11" s="3" customFormat="1" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" s="3" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="E12" s="19"/>
       <c r="F12" s="19"/>
       <c r="G12" s="19"/>
     </row>
-    <row r="13" spans="1:11" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:11" ht="18" x14ac:dyDescent="0.5">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -8727,7 +8731,7 @@
       <c r="F13" s="19"/>
       <c r="G13" s="19"/>
     </row>
-    <row r="14" spans="1:11" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:11" ht="18" x14ac:dyDescent="0.5">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -8735,14 +8739,14 @@
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
     </row>
-    <row r="15" spans="1:11" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:11" ht="18" x14ac:dyDescent="0.5">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
     </row>
-    <row r="16" spans="1:11" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:11" ht="18" x14ac:dyDescent="0.5">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="E16" s="20"/>
@@ -8756,7 +8760,7 @@
       <c r="F17" s="4"/>
       <c r="G17" s="3"/>
     </row>
-    <row r="18" spans="1:8" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:8" ht="18" x14ac:dyDescent="0.5">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="E18" s="17"/>
@@ -8768,16 +8772,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="J3:J5"/>
+    <mergeCell ref="I3:I5"/>
+    <mergeCell ref="H3:H5"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="C3:C6"/>
     <mergeCell ref="D3:D6"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="I3:I5"/>
-    <mergeCell ref="H3:H5"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E11 E3:E5 E7:E9" xr:uid="{A2477E48-5835-4B16-9FBF-C78279A05481}">
@@ -8796,19 +8800,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="3" customWidth="1"/>
-    <col min="2" max="2" width="20.26953125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="30.1796875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="30.7265625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="37.453125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20.21875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="30.21875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="30.77734375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="37.44140625" style="3" customWidth="1"/>
     <col min="6" max="6" width="84" style="3" customWidth="1"/>
     <col min="7" max="7" width="34" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="11.453125" style="3"/>
+    <col min="8" max="16384" width="11.44140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="99" t="s">
         <v>39</v>
       </c>
@@ -8819,7 +8823,7 @@
       <c r="F1" s="100"/>
       <c r="G1" s="100"/>
     </row>
-    <row r="2" spans="1:7" ht="52" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="48" x14ac:dyDescent="0.3">
       <c r="A2" s="34" t="s">
         <v>40</v>
       </c>
@@ -8842,7 +8846,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="36" t="s">
         <v>47</v>
       </c>
@@ -8865,7 +8869,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="66" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" s="18">
         <v>1</v>
       </c>
@@ -8888,7 +8892,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="82.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="108" x14ac:dyDescent="0.3">
       <c r="A5" s="18">
         <v>2</v>
       </c>
@@ -8911,7 +8915,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="83" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" ht="90.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="47">
         <v>3</v>
       </c>
@@ -8934,7 +8938,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="66" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="55">
         <v>4</v>
       </c>
@@ -8987,21 +8991,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="82.54296875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="15.1796875" style="18" customWidth="1"/>
-    <col min="3" max="3" width="15.26953125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="30.1796875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="82.5546875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" style="18" customWidth="1"/>
+    <col min="3" max="3" width="15.21875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="30.21875" style="4" customWidth="1"/>
     <col min="5" max="5" width="20" style="4" customWidth="1"/>
-    <col min="6" max="6" width="14.7265625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="15.81640625" style="40" customWidth="1"/>
-    <col min="8" max="8" width="14.1796875" style="49" customWidth="1"/>
-    <col min="9" max="9" width="108.453125" style="49" customWidth="1"/>
-    <col min="10" max="16384" width="11.453125" style="4"/>
+    <col min="6" max="6" width="14.77734375" style="4" customWidth="1"/>
+    <col min="7" max="7" width="15.77734375" style="40" customWidth="1"/>
+    <col min="8" max="8" width="14.21875" style="49" customWidth="1"/>
+    <col min="9" max="9" width="108.44140625" style="49" customWidth="1"/>
+    <col min="10" max="16384" width="11.44140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="78" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A1" s="41" t="s">
         <v>67</v>
       </c>
@@ -9031,7 +9035,7 @@
       </c>
       <c r="J1" s="63"/>
     </row>
-    <row r="2" spans="1:10" ht="33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" ht="36" x14ac:dyDescent="0.3">
       <c r="A2" s="44" t="s">
         <v>76</v>
       </c>
@@ -9061,7 +9065,7 @@
       </c>
       <c r="J2" s="64"/>
     </row>
-    <row r="3" spans="1:10" ht="66" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>56</v>
       </c>
@@ -9090,7 +9094,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="66" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>56</v>
       </c>
@@ -9119,7 +9123,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="66" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="33" t="s">
         <v>56</v>
       </c>
@@ -9148,7 +9152,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="66" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="90" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>60</v>
       </c>
@@ -9177,7 +9181,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="101.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="101.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>60</v>
       </c>
@@ -9206,7 +9210,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="99" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="108" x14ac:dyDescent="0.3">
       <c r="A8" s="33" t="s">
         <v>60</v>
       </c>
@@ -9235,7 +9239,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="66" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>63</v>
       </c>
@@ -9264,7 +9268,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="66" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>63</v>
       </c>
@@ -9293,7 +9297,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="99" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="108" x14ac:dyDescent="0.3">
       <c r="A11" s="33" t="s">
         <v>63</v>
       </c>
@@ -9322,7 +9326,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="54" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>65</v>
       </c>
@@ -9394,19 +9398,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="80" style="49" customWidth="1"/>
-    <col min="2" max="2" width="47.7265625" style="40" customWidth="1"/>
-    <col min="3" max="3" width="31.54296875" style="49" customWidth="1"/>
-    <col min="4" max="4" width="43.1796875" style="49" customWidth="1"/>
-    <col min="5" max="5" width="30.453125" style="49" customWidth="1"/>
-    <col min="6" max="6" width="32.1796875" style="49" customWidth="1"/>
-    <col min="7" max="7" width="45.453125" style="49" customWidth="1"/>
-    <col min="8" max="16384" width="11.453125" style="49"/>
+    <col min="2" max="2" width="47.77734375" style="40" customWidth="1"/>
+    <col min="3" max="3" width="31.5546875" style="49" customWidth="1"/>
+    <col min="4" max="4" width="43.21875" style="49" customWidth="1"/>
+    <col min="5" max="5" width="30.44140625" style="49" customWidth="1"/>
+    <col min="6" max="6" width="32.21875" style="49" customWidth="1"/>
+    <col min="7" max="7" width="45.44140625" style="49" customWidth="1"/>
+    <col min="8" max="16384" width="11.44140625" style="49"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="65" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="60" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>101</v>
       </c>
@@ -9426,7 +9430,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" ht="54" x14ac:dyDescent="0.3">
       <c r="A2" s="52" t="s">
         <v>107</v>
       </c>
@@ -9446,7 +9450,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A3" s="50" t="s">
         <v>89</v>
       </c>
@@ -9459,14 +9463,14 @@
       <c r="D3" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="E3" s="89" t="s">
+      <c r="E3" s="84" t="s">
         <v>116</v>
       </c>
       <c r="F3" s="50" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A4" s="50" t="s">
         <v>93</v>
       </c>
@@ -9475,12 +9479,12 @@
       <c r="D4" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="E4" s="89"/>
+      <c r="E4" s="84"/>
       <c r="F4" s="50" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="50" t="s">
         <v>97</v>
       </c>
@@ -9489,12 +9493,12 @@
       <c r="D5" s="50" t="s">
         <v>120</v>
       </c>
-      <c r="E5" s="89"/>
+      <c r="E5" s="84"/>
       <c r="F5" s="50" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" s="32" t="s">
         <v>99</v>
       </c>
@@ -9503,12 +9507,12 @@
       <c r="D6" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="E6" s="90"/>
+      <c r="E6" s="85"/>
       <c r="F6" s="32" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="50" t="s">
         <v>89</v>
       </c>
@@ -9521,14 +9525,14 @@
       <c r="D7" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="E7" s="89" t="s">
+      <c r="E7" s="84" t="s">
         <v>125</v>
       </c>
       <c r="F7" s="50" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A8" s="50" t="s">
         <v>93</v>
       </c>
@@ -9537,12 +9541,12 @@
       <c r="D8" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="E8" s="89"/>
+      <c r="E8" s="84"/>
       <c r="F8" s="50" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A9" s="50" t="s">
         <v>97</v>
       </c>
@@ -9551,12 +9555,12 @@
       <c r="D9" s="50" t="s">
         <v>127</v>
       </c>
-      <c r="E9" s="89"/>
+      <c r="E9" s="84"/>
       <c r="F9" s="50" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A10" s="32" t="s">
         <v>99</v>
       </c>
@@ -9565,12 +9569,12 @@
       <c r="D10" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="E10" s="90"/>
+      <c r="E10" s="85"/>
       <c r="F10" s="32" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A11" s="50" t="s">
         <v>89</v>
       </c>
@@ -9583,14 +9587,14 @@
       <c r="D11" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="E11" s="89" t="s">
+      <c r="E11" s="84" t="s">
         <v>131</v>
       </c>
       <c r="F11" s="50" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A12" s="50" t="s">
         <v>93</v>
       </c>
@@ -9599,12 +9603,12 @@
       <c r="D12" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="E12" s="89"/>
+      <c r="E12" s="84"/>
       <c r="F12" s="50" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A13" s="50" t="s">
         <v>97</v>
       </c>
@@ -9613,12 +9617,12 @@
       <c r="D13" s="50" t="s">
         <v>133</v>
       </c>
-      <c r="E13" s="89"/>
+      <c r="E13" s="84"/>
       <c r="F13" s="50" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A14" s="32" t="s">
         <v>99</v>
       </c>
@@ -9627,104 +9631,109 @@
       <c r="D14" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="E14" s="90"/>
+      <c r="E14" s="85"/>
       <c r="F14" s="32" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A15" s="50" t="s">
         <v>97</v>
       </c>
       <c r="B15" s="82" t="s">
         <v>135</v>
       </c>
-      <c r="C15" s="89" t="s">
+      <c r="C15" s="84" t="s">
         <v>136</v>
       </c>
       <c r="D15" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="E15" s="89" t="s">
+      <c r="E15" s="84" t="s">
         <v>137</v>
       </c>
       <c r="F15" s="50" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A16" s="32" t="s">
         <v>99</v>
       </c>
       <c r="B16" s="83"/>
-      <c r="C16" s="90"/>
+      <c r="C16" s="85"/>
       <c r="D16" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="E16" s="90"/>
+      <c r="E16" s="85"/>
       <c r="F16" s="32" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A17" s="50" t="s">
         <v>89</v>
       </c>
       <c r="B17" s="82" t="s">
         <v>139</v>
       </c>
-      <c r="C17" s="89" t="s">
+      <c r="C17" s="84" t="s">
         <v>140</v>
       </c>
       <c r="D17" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="E17" s="89" t="s">
+      <c r="E17" s="84" t="s">
         <v>141</v>
       </c>
       <c r="F17" s="50" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A18" s="50" t="s">
         <v>93</v>
       </c>
       <c r="B18" s="82"/>
-      <c r="C18" s="89"/>
+      <c r="C18" s="84"/>
       <c r="D18" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="E18" s="89"/>
+      <c r="E18" s="84"/>
       <c r="F18" s="50" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A19" s="50" t="s">
         <v>97</v>
       </c>
       <c r="B19" s="82"/>
-      <c r="C19" s="89"/>
+      <c r="C19" s="84"/>
       <c r="D19" s="50"/>
-      <c r="E19" s="89"/>
+      <c r="E19" s="84"/>
       <c r="F19" s="50"/>
     </row>
-    <row r="20" spans="1:6" ht="66" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" ht="72" x14ac:dyDescent="0.3">
       <c r="A20" s="32" t="s">
         <v>99</v>
       </c>
       <c r="B20" s="83"/>
-      <c r="C20" s="90"/>
+      <c r="C20" s="85"/>
       <c r="D20" s="53"/>
-      <c r="E20" s="90"/>
+      <c r="E20" s="85"/>
       <c r="F20" s="54"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="E3:E6"/>
+    <mergeCell ref="E7:E10"/>
+    <mergeCell ref="E11:E14"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="E17:E20"/>
     <mergeCell ref="B15:B16"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="B17:B20"/>
@@ -9735,11 +9744,6 @@
     <mergeCell ref="C7:C10"/>
     <mergeCell ref="B11:B14"/>
     <mergeCell ref="C11:C14"/>
-    <mergeCell ref="E3:E6"/>
-    <mergeCell ref="E7:E10"/>
-    <mergeCell ref="E11:E14"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="E17:E20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -9761,29 +9765,29 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:T215"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.1796875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="46.26953125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="16.26953125" style="18" customWidth="1"/>
-    <col min="4" max="4" width="23.81640625" style="18" customWidth="1"/>
-    <col min="5" max="5" width="52.453125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="16.453125" style="18" customWidth="1"/>
-    <col min="7" max="7" width="15.54296875" style="18" customWidth="1"/>
-    <col min="8" max="8" width="15.1796875" style="18" customWidth="1"/>
-    <col min="9" max="9" width="13.81640625" style="18" customWidth="1"/>
-    <col min="10" max="10" width="21.26953125" style="18" customWidth="1"/>
+    <col min="1" max="1" width="17.21875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="46.21875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" style="18" customWidth="1"/>
+    <col min="4" max="4" width="23.77734375" style="18" customWidth="1"/>
+    <col min="5" max="5" width="52.44140625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" style="18" customWidth="1"/>
+    <col min="7" max="7" width="15.5546875" style="18" customWidth="1"/>
+    <col min="8" max="8" width="15.21875" style="18" customWidth="1"/>
+    <col min="9" max="9" width="13.77734375" style="18" customWidth="1"/>
+    <col min="10" max="10" width="21.21875" style="18" customWidth="1"/>
     <col min="11" max="11" width="27" style="18" customWidth="1"/>
-    <col min="12" max="12" width="21.26953125" style="18" customWidth="1"/>
-    <col min="13" max="13" width="15.1796875" style="18" customWidth="1"/>
-    <col min="14" max="14" width="32.1796875" style="3" customWidth="1"/>
-    <col min="15" max="15" width="41.7265625" style="3" customWidth="1"/>
-    <col min="16" max="16" width="41.54296875" style="3" customWidth="1"/>
-    <col min="17" max="17" width="55.81640625" style="4" customWidth="1"/>
-    <col min="18" max="16384" width="11.453125" style="3"/>
+    <col min="12" max="12" width="21.21875" style="18" customWidth="1"/>
+    <col min="13" max="13" width="15.21875" style="18" customWidth="1"/>
+    <col min="14" max="14" width="32.21875" style="3" customWidth="1"/>
+    <col min="15" max="15" width="41.77734375" style="3" customWidth="1"/>
+    <col min="16" max="16" width="41.5546875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="55.77734375" style="4" customWidth="1"/>
+    <col min="18" max="16384" width="11.44140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="65" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" ht="60" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>143</v>
       </c>
@@ -9802,11 +9806,11 @@
       <c r="F1" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="G1" s="80" t="s">
+      <c r="G1" s="89" t="s">
         <v>149</v>
       </c>
-      <c r="H1" s="80"/>
-      <c r="I1" s="81"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="90"/>
       <c r="J1" s="23" t="s">
         <v>150</v>
       </c>
@@ -9835,7 +9839,7 @@
       <c r="S1" s="56"/>
       <c r="T1" s="55"/>
     </row>
-    <row r="2" spans="1:20" ht="49.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="54" x14ac:dyDescent="0.3">
       <c r="A2" s="51" t="s">
         <v>158</v>
       </c>
@@ -9891,7 +9895,7 @@
       <c r="S2" s="57"/>
       <c r="T2" s="55"/>
     </row>
-    <row r="3" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A3" s="38" t="str">
         <f>_xlfn.XLOOKUP(B3,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -9905,7 +9909,7 @@
       <c r="D3" s="82" t="s">
         <v>174</v>
       </c>
-      <c r="E3" s="84" t="s">
+      <c r="E3" s="80" t="s">
         <v>175</v>
       </c>
       <c r="F3" s="82" t="s">
@@ -9931,20 +9935,20 @@
         <f>SUM(K3:L3)</f>
         <v>144</v>
       </c>
-      <c r="N3" s="84" t="s">
+      <c r="N3" s="80" t="s">
         <v>178</v>
       </c>
-      <c r="O3" s="84" t="s">
+      <c r="O3" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="P3" s="84" t="s">
+      <c r="P3" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q3" s="84" t="s">
+      <c r="Q3" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A4" s="38" t="str">
         <f>_xlfn.XLOOKUP(B4,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -9954,7 +9958,7 @@
       </c>
       <c r="C4" s="82"/>
       <c r="D4" s="82"/>
-      <c r="E4" s="84"/>
+      <c r="E4" s="80"/>
       <c r="F4" s="82"/>
       <c r="G4" s="82"/>
       <c r="H4" s="82"/>
@@ -9963,12 +9967,12 @@
       <c r="K4" s="82"/>
       <c r="L4" s="82"/>
       <c r="M4" s="82"/>
-      <c r="N4" s="84"/>
-      <c r="O4" s="84"/>
-      <c r="P4" s="84"/>
-      <c r="Q4" s="84"/>
-    </row>
-    <row r="5" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N4" s="80"/>
+      <c r="O4" s="80"/>
+      <c r="P4" s="80"/>
+      <c r="Q4" s="80"/>
+    </row>
+    <row r="5" spans="1:20" ht="144" x14ac:dyDescent="0.3">
       <c r="A5" s="48" t="str">
         <f>_xlfn.XLOOKUP(B5,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -9978,7 +9982,7 @@
       </c>
       <c r="C5" s="83"/>
       <c r="D5" s="83"/>
-      <c r="E5" s="85"/>
+      <c r="E5" s="81"/>
       <c r="F5" s="83"/>
       <c r="G5" s="83"/>
       <c r="H5" s="83"/>
@@ -9987,12 +9991,12 @@
       <c r="K5" s="83"/>
       <c r="L5" s="83"/>
       <c r="M5" s="83"/>
-      <c r="N5" s="85"/>
-      <c r="O5" s="85"/>
-      <c r="P5" s="85"/>
-      <c r="Q5" s="85"/>
-    </row>
-    <row r="6" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N5" s="81"/>
+      <c r="O5" s="81"/>
+      <c r="P5" s="81"/>
+      <c r="Q5" s="81"/>
+    </row>
+    <row r="6" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A6" s="38" t="str">
         <f>_xlfn.XLOOKUP(B6,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -10006,7 +10010,7 @@
       <c r="D6" s="82" t="s">
         <v>182</v>
       </c>
-      <c r="E6" s="84" t="s">
+      <c r="E6" s="80" t="s">
         <v>183</v>
       </c>
       <c r="F6" s="82" t="s">
@@ -10032,20 +10036,20 @@
         <f>SUM(K6:L6)</f>
         <v>144</v>
       </c>
-      <c r="N6" s="84" t="s">
+      <c r="N6" s="80" t="s">
         <v>184</v>
       </c>
-      <c r="O6" s="84" t="s">
+      <c r="O6" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="P6" s="84" t="s">
+      <c r="P6" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q6" s="84" t="s">
+      <c r="Q6" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" ht="144" x14ac:dyDescent="0.3">
       <c r="A7" s="38" t="str">
         <f>_xlfn.XLOOKUP(B7,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -10055,7 +10059,7 @@
       </c>
       <c r="C7" s="82"/>
       <c r="D7" s="82"/>
-      <c r="E7" s="84"/>
+      <c r="E7" s="80"/>
       <c r="F7" s="82"/>
       <c r="G7" s="82"/>
       <c r="H7" s="82"/>
@@ -10064,12 +10068,12 @@
       <c r="K7" s="82"/>
       <c r="L7" s="82"/>
       <c r="M7" s="82"/>
-      <c r="N7" s="84"/>
-      <c r="O7" s="84"/>
-      <c r="P7" s="84"/>
-      <c r="Q7" s="84"/>
-    </row>
-    <row r="8" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N7" s="80"/>
+      <c r="O7" s="80"/>
+      <c r="P7" s="80"/>
+      <c r="Q7" s="80"/>
+    </row>
+    <row r="8" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A8" s="48" t="str">
         <f>_xlfn.XLOOKUP(B8,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10079,7 +10083,7 @@
       </c>
       <c r="C8" s="83"/>
       <c r="D8" s="83"/>
-      <c r="E8" s="85"/>
+      <c r="E8" s="81"/>
       <c r="F8" s="83"/>
       <c r="G8" s="83"/>
       <c r="H8" s="83"/>
@@ -10088,12 +10092,12 @@
       <c r="K8" s="83"/>
       <c r="L8" s="83"/>
       <c r="M8" s="83"/>
-      <c r="N8" s="85"/>
-      <c r="O8" s="85"/>
-      <c r="P8" s="85"/>
-      <c r="Q8" s="85"/>
-    </row>
-    <row r="9" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N8" s="81"/>
+      <c r="O8" s="81"/>
+      <c r="P8" s="81"/>
+      <c r="Q8" s="81"/>
+    </row>
+    <row r="9" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A9" s="38" t="str">
         <f>_xlfn.XLOOKUP(B9,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -10107,7 +10111,7 @@
       <c r="D9" s="82" t="s">
         <v>185</v>
       </c>
-      <c r="E9" s="84" t="s">
+      <c r="E9" s="80" t="s">
         <v>186</v>
       </c>
       <c r="F9" s="82" t="s">
@@ -10133,20 +10137,20 @@
         <f>SUM(K9:L10)</f>
         <v>144</v>
       </c>
-      <c r="N9" s="84" t="s">
+      <c r="N9" s="80" t="s">
         <v>188</v>
       </c>
-      <c r="O9" s="84" t="s">
+      <c r="O9" s="80" t="s">
         <v>189</v>
       </c>
-      <c r="P9" s="84" t="s">
+      <c r="P9" s="80" t="s">
         <v>190</v>
       </c>
-      <c r="Q9" s="84" t="s">
+      <c r="Q9" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A10" s="38" t="str">
         <f>_xlfn.XLOOKUP(B10,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10156,7 +10160,7 @@
       </c>
       <c r="C10" s="82"/>
       <c r="D10" s="82"/>
-      <c r="E10" s="84"/>
+      <c r="E10" s="80"/>
       <c r="F10" s="82"/>
       <c r="G10" s="82"/>
       <c r="H10" s="82"/>
@@ -10165,12 +10169,12 @@
       <c r="K10" s="82"/>
       <c r="L10" s="82"/>
       <c r="M10" s="82"/>
-      <c r="N10" s="84"/>
-      <c r="O10" s="84"/>
-      <c r="P10" s="84"/>
-      <c r="Q10" s="84"/>
-    </row>
-    <row r="11" spans="1:20" ht="396" x14ac:dyDescent="0.35">
+      <c r="N10" s="80"/>
+      <c r="O10" s="80"/>
+      <c r="P10" s="80"/>
+      <c r="Q10" s="80"/>
+    </row>
+    <row r="11" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A11" s="60" t="s">
         <v>11</v>
       </c>
@@ -10226,7 +10230,7 @@
       <c r="S11" s="38"/>
       <c r="T11" s="38"/>
     </row>
-    <row r="12" spans="1:20" ht="313.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" ht="360" x14ac:dyDescent="0.3">
       <c r="A12" s="60" t="s">
         <v>11</v>
       </c>
@@ -10282,7 +10286,7 @@
       <c r="S12" s="38"/>
       <c r="T12" s="38"/>
     </row>
-    <row r="13" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A13" s="38" t="str">
         <f>_xlfn.XLOOKUP(B13,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10296,7 +10300,7 @@
       <c r="D13" s="82" t="s">
         <v>203</v>
       </c>
-      <c r="E13" s="84" t="s">
+      <c r="E13" s="80" t="s">
         <v>204</v>
       </c>
       <c r="F13" s="82" t="s">
@@ -10322,27 +10326,27 @@
         <f>SUM(K13:L13)</f>
         <v>144</v>
       </c>
-      <c r="N13" s="84" t="s">
+      <c r="N13" s="80" t="s">
         <v>205</v>
       </c>
-      <c r="O13" s="84" t="s">
+      <c r="O13" s="80" t="s">
         <v>206</v>
       </c>
-      <c r="P13" s="84" t="s">
+      <c r="P13" s="80" t="s">
         <v>207</v>
       </c>
-      <c r="Q13" s="84" t="s">
+      <c r="Q13" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A14" s="38"/>
       <c r="B14" s="38" t="s">
         <v>93</v>
       </c>
       <c r="C14" s="82"/>
       <c r="D14" s="82"/>
-      <c r="E14" s="84"/>
+      <c r="E14" s="80"/>
       <c r="F14" s="82"/>
       <c r="G14" s="82"/>
       <c r="H14" s="82"/>
@@ -10351,12 +10355,12 @@
       <c r="K14" s="82"/>
       <c r="L14" s="82"/>
       <c r="M14" s="82"/>
-      <c r="N14" s="84"/>
-      <c r="O14" s="84"/>
-      <c r="P14" s="84"/>
-      <c r="Q14" s="84"/>
-    </row>
-    <row r="15" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N14" s="80"/>
+      <c r="O14" s="80"/>
+      <c r="P14" s="80"/>
+      <c r="Q14" s="80"/>
+    </row>
+    <row r="15" spans="1:20" ht="144" x14ac:dyDescent="0.3">
       <c r="A15" s="48" t="str">
         <f>_xlfn.XLOOKUP(B15,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -10366,7 +10370,7 @@
       </c>
       <c r="C15" s="83"/>
       <c r="D15" s="83"/>
-      <c r="E15" s="85"/>
+      <c r="E15" s="81"/>
       <c r="F15" s="83"/>
       <c r="G15" s="83"/>
       <c r="H15" s="83"/>
@@ -10375,12 +10379,12 @@
       <c r="K15" s="83"/>
       <c r="L15" s="83"/>
       <c r="M15" s="83"/>
-      <c r="N15" s="85"/>
-      <c r="O15" s="85"/>
-      <c r="P15" s="85"/>
-      <c r="Q15" s="85"/>
-    </row>
-    <row r="16" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N15" s="81"/>
+      <c r="O15" s="81"/>
+      <c r="P15" s="81"/>
+      <c r="Q15" s="81"/>
+    </row>
+    <row r="16" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A16" s="38" t="str">
         <f>_xlfn.XLOOKUP(B16,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -10394,7 +10398,7 @@
       <c r="D16" s="82" t="s">
         <v>208</v>
       </c>
-      <c r="E16" s="84" t="s">
+      <c r="E16" s="80" t="s">
         <v>209</v>
       </c>
       <c r="F16" s="82" t="s">
@@ -10420,20 +10424,20 @@
         <f>SUM(K16:L16)</f>
         <v>144</v>
       </c>
-      <c r="N16" s="84" t="s">
+      <c r="N16" s="80" t="s">
         <v>210</v>
       </c>
       <c r="O16" s="86" t="s">
         <v>211</v>
       </c>
-      <c r="P16" s="84" t="s">
+      <c r="P16" s="80" t="s">
         <v>207</v>
       </c>
-      <c r="Q16" s="84" t="s">
+      <c r="Q16" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" ht="144" x14ac:dyDescent="0.3">
       <c r="A17" s="38" t="str">
         <f>_xlfn.XLOOKUP(B17,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -10443,7 +10447,7 @@
       </c>
       <c r="C17" s="82"/>
       <c r="D17" s="82"/>
-      <c r="E17" s="84"/>
+      <c r="E17" s="80"/>
       <c r="F17" s="82"/>
       <c r="G17" s="82"/>
       <c r="H17" s="82"/>
@@ -10452,12 +10456,12 @@
       <c r="K17" s="82"/>
       <c r="L17" s="82"/>
       <c r="M17" s="82"/>
-      <c r="N17" s="84"/>
-      <c r="O17" s="84"/>
-      <c r="P17" s="84"/>
-      <c r="Q17" s="84"/>
-    </row>
-    <row r="18" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N17" s="80"/>
+      <c r="O17" s="80"/>
+      <c r="P17" s="80"/>
+      <c r="Q17" s="80"/>
+    </row>
+    <row r="18" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A18" s="48" t="str">
         <f>_xlfn.XLOOKUP(B18,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10467,7 +10471,7 @@
       </c>
       <c r="C18" s="83"/>
       <c r="D18" s="83"/>
-      <c r="E18" s="85"/>
+      <c r="E18" s="81"/>
       <c r="F18" s="83"/>
       <c r="G18" s="83"/>
       <c r="H18" s="83"/>
@@ -10476,12 +10480,12 @@
       <c r="K18" s="83"/>
       <c r="L18" s="83"/>
       <c r="M18" s="83"/>
-      <c r="N18" s="85"/>
-      <c r="O18" s="85"/>
-      <c r="P18" s="85"/>
-      <c r="Q18" s="85"/>
-    </row>
-    <row r="19" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N18" s="81"/>
+      <c r="O18" s="81"/>
+      <c r="P18" s="81"/>
+      <c r="Q18" s="81"/>
+    </row>
+    <row r="19" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A19" s="38" t="str">
         <f>_xlfn.XLOOKUP(B19,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10495,7 +10499,7 @@
       <c r="D19" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="E19" s="84" t="s">
+      <c r="E19" s="80" t="s">
         <v>213</v>
       </c>
       <c r="F19" s="82" t="s">
@@ -10521,20 +10525,20 @@
         <f>SUM(K19:L19)</f>
         <v>144</v>
       </c>
-      <c r="N19" s="84" t="s">
+      <c r="N19" s="80" t="s">
         <v>214</v>
       </c>
       <c r="O19" s="86" t="s">
         <v>179</v>
       </c>
-      <c r="P19" s="84" t="s">
+      <c r="P19" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q19" s="84" t="s">
+      <c r="Q19" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A20" s="38" t="str">
         <f>_xlfn.XLOOKUP(B20,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -10544,7 +10548,7 @@
       </c>
       <c r="C20" s="82"/>
       <c r="D20" s="82"/>
-      <c r="E20" s="84"/>
+      <c r="E20" s="80"/>
       <c r="F20" s="82"/>
       <c r="G20" s="82"/>
       <c r="H20" s="82"/>
@@ -10553,12 +10557,12 @@
       <c r="K20" s="82"/>
       <c r="L20" s="82"/>
       <c r="M20" s="82"/>
-      <c r="N20" s="84"/>
-      <c r="O20" s="84"/>
-      <c r="P20" s="84"/>
-      <c r="Q20" s="84"/>
-    </row>
-    <row r="21" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N20" s="80"/>
+      <c r="O20" s="80"/>
+      <c r="P20" s="80"/>
+      <c r="Q20" s="80"/>
+    </row>
+    <row r="21" spans="1:20" ht="144" x14ac:dyDescent="0.3">
       <c r="A21" s="48" t="str">
         <f>_xlfn.XLOOKUP(B21,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -10568,7 +10572,7 @@
       </c>
       <c r="C21" s="83"/>
       <c r="D21" s="83"/>
-      <c r="E21" s="85"/>
+      <c r="E21" s="81"/>
       <c r="F21" s="83"/>
       <c r="G21" s="83"/>
       <c r="H21" s="83"/>
@@ -10577,12 +10581,12 @@
       <c r="K21" s="83"/>
       <c r="L21" s="83"/>
       <c r="M21" s="83"/>
-      <c r="N21" s="85"/>
-      <c r="O21" s="85"/>
-      <c r="P21" s="85"/>
-      <c r="Q21" s="85"/>
-    </row>
-    <row r="22" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N21" s="81"/>
+      <c r="O21" s="81"/>
+      <c r="P21" s="81"/>
+      <c r="Q21" s="81"/>
+    </row>
+    <row r="22" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A22" s="38" t="str">
         <f>_xlfn.XLOOKUP(B22,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -10596,7 +10600,7 @@
       <c r="D22" s="82" t="s">
         <v>215</v>
       </c>
-      <c r="E22" s="84" t="s">
+      <c r="E22" s="80" t="s">
         <v>216</v>
       </c>
       <c r="F22" s="82" t="s">
@@ -10622,20 +10626,20 @@
         <f>SUM(K22:L22)</f>
         <v>144</v>
       </c>
-      <c r="N22" s="84" t="s">
+      <c r="N22" s="80" t="s">
         <v>217</v>
       </c>
       <c r="O22" s="86" t="s">
         <v>179</v>
       </c>
-      <c r="P22" s="84" t="s">
+      <c r="P22" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q22" s="84" t="s">
+      <c r="Q22" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:20" ht="144" x14ac:dyDescent="0.3">
       <c r="A23" s="38" t="str">
         <f>_xlfn.XLOOKUP(B23,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -10645,7 +10649,7 @@
       </c>
       <c r="C23" s="82"/>
       <c r="D23" s="82"/>
-      <c r="E23" s="84"/>
+      <c r="E23" s="80"/>
       <c r="F23" s="82"/>
       <c r="G23" s="82"/>
       <c r="H23" s="82"/>
@@ -10654,12 +10658,12 @@
       <c r="K23" s="82"/>
       <c r="L23" s="82"/>
       <c r="M23" s="82"/>
-      <c r="N23" s="84"/>
-      <c r="O23" s="84"/>
-      <c r="P23" s="84"/>
-      <c r="Q23" s="84"/>
-    </row>
-    <row r="24" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N23" s="80"/>
+      <c r="O23" s="80"/>
+      <c r="P23" s="80"/>
+      <c r="Q23" s="80"/>
+    </row>
+    <row r="24" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A24" s="48" t="str">
         <f>_xlfn.XLOOKUP(B24,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10669,7 +10673,7 @@
       </c>
       <c r="C24" s="83"/>
       <c r="D24" s="83"/>
-      <c r="E24" s="85"/>
+      <c r="E24" s="81"/>
       <c r="F24" s="83"/>
       <c r="G24" s="83"/>
       <c r="H24" s="83"/>
@@ -10678,12 +10682,12 @@
       <c r="K24" s="83"/>
       <c r="L24" s="83"/>
       <c r="M24" s="83"/>
-      <c r="N24" s="85"/>
-      <c r="O24" s="85"/>
-      <c r="P24" s="85"/>
-      <c r="Q24" s="85"/>
-    </row>
-    <row r="25" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N24" s="81"/>
+      <c r="O24" s="81"/>
+      <c r="P24" s="81"/>
+      <c r="Q24" s="81"/>
+    </row>
+    <row r="25" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A25" s="38" t="str">
         <f>_xlfn.XLOOKUP(B25,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -10697,7 +10701,7 @@
       <c r="D25" s="82" t="s">
         <v>218</v>
       </c>
-      <c r="E25" s="84" t="s">
+      <c r="E25" s="80" t="s">
         <v>219</v>
       </c>
       <c r="F25" s="82" t="s">
@@ -10723,20 +10727,20 @@
         <f>SUM(K25:L25)</f>
         <v>144</v>
       </c>
-      <c r="N25" s="84" t="s">
+      <c r="N25" s="80" t="s">
         <v>220</v>
       </c>
       <c r="O25" s="86" t="s">
         <v>189</v>
       </c>
-      <c r="P25" s="84" t="s">
+      <c r="P25" s="80" t="s">
         <v>221</v>
       </c>
-      <c r="Q25" s="84" t="s">
+      <c r="Q25" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A26" s="38" t="str">
         <f>_xlfn.XLOOKUP(B26,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10746,7 +10750,7 @@
       </c>
       <c r="C26" s="83"/>
       <c r="D26" s="83"/>
-      <c r="E26" s="85"/>
+      <c r="E26" s="81"/>
       <c r="F26" s="83"/>
       <c r="G26" s="83"/>
       <c r="H26" s="83"/>
@@ -10755,12 +10759,12 @@
       <c r="K26" s="83"/>
       <c r="L26" s="83"/>
       <c r="M26" s="83"/>
-      <c r="N26" s="85"/>
-      <c r="O26" s="85"/>
-      <c r="P26" s="85"/>
-      <c r="Q26" s="85"/>
-    </row>
-    <row r="27" spans="1:20" ht="313.5" x14ac:dyDescent="0.35">
+      <c r="N26" s="81"/>
+      <c r="O26" s="81"/>
+      <c r="P26" s="81"/>
+      <c r="Q26" s="81"/>
+    </row>
+    <row r="27" spans="1:20" ht="360" x14ac:dyDescent="0.3">
       <c r="A27" s="60" t="s">
         <v>222</v>
       </c>
@@ -10819,7 +10823,7 @@
       <c r="S27" s="38"/>
       <c r="T27" s="38"/>
     </row>
-    <row r="28" spans="1:20" ht="114" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:20" ht="114" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="38" t="str">
         <f>_xlfn.XLOOKUP(B28,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10827,35 +10831,35 @@
       <c r="B28" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="C28" s="88">
+      <c r="C28" s="87">
         <v>3</v>
       </c>
-      <c r="D28" s="88" t="s">
+      <c r="D28" s="87" t="s">
         <v>228</v>
       </c>
       <c r="E28" s="86" t="s">
         <v>229</v>
       </c>
-      <c r="F28" s="88" t="s">
+      <c r="F28" s="87" t="s">
         <v>187</v>
       </c>
-      <c r="G28" s="88"/>
-      <c r="H28" s="88" t="s">
+      <c r="G28" s="87"/>
+      <c r="H28" s="87" t="s">
         <v>177</v>
       </c>
-      <c r="I28" s="88"/>
-      <c r="J28" s="88">
+      <c r="I28" s="87"/>
+      <c r="J28" s="87">
         <v>3</v>
       </c>
-      <c r="K28" s="88">
+      <c r="K28" s="87">
         <f>J28*16</f>
         <v>48</v>
       </c>
-      <c r="L28" s="88">
+      <c r="L28" s="87">
         <f>J28*32</f>
         <v>96</v>
       </c>
-      <c r="M28" s="88">
+      <c r="M28" s="87">
         <f>SUM(K28:L28)</f>
         <v>144</v>
       </c>
@@ -10872,7 +10876,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A29" s="38" t="str">
         <f>_xlfn.XLOOKUP(B29,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -10882,7 +10886,7 @@
       </c>
       <c r="C29" s="82"/>
       <c r="D29" s="82"/>
-      <c r="E29" s="84"/>
+      <c r="E29" s="80"/>
       <c r="F29" s="82"/>
       <c r="G29" s="82"/>
       <c r="H29" s="82"/>
@@ -10891,12 +10895,12 @@
       <c r="K29" s="82"/>
       <c r="L29" s="82"/>
       <c r="M29" s="82"/>
-      <c r="N29" s="84"/>
-      <c r="O29" s="84"/>
-      <c r="P29" s="84"/>
-      <c r="Q29" s="84"/>
-    </row>
-    <row r="30" spans="1:20" ht="116" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="N29" s="80"/>
+      <c r="O29" s="80"/>
+      <c r="P29" s="80"/>
+      <c r="Q29" s="80"/>
+    </row>
+    <row r="30" spans="1:20" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="48" t="str">
         <f>_xlfn.XLOOKUP(B30,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -10906,7 +10910,7 @@
       </c>
       <c r="C30" s="83"/>
       <c r="D30" s="83"/>
-      <c r="E30" s="85"/>
+      <c r="E30" s="81"/>
       <c r="F30" s="83"/>
       <c r="G30" s="83"/>
       <c r="H30" s="83"/>
@@ -10915,12 +10919,12 @@
       <c r="K30" s="83"/>
       <c r="L30" s="83"/>
       <c r="M30" s="83"/>
-      <c r="N30" s="85"/>
-      <c r="O30" s="85"/>
-      <c r="P30" s="85"/>
-      <c r="Q30" s="85"/>
-    </row>
-    <row r="31" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N30" s="81"/>
+      <c r="O30" s="81"/>
+      <c r="P30" s="81"/>
+      <c r="Q30" s="81"/>
+    </row>
+    <row r="31" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A31" s="38" t="str">
         <f>_xlfn.XLOOKUP(B31,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -10934,7 +10938,7 @@
       <c r="D31" s="82" t="s">
         <v>232</v>
       </c>
-      <c r="E31" s="84" t="s">
+      <c r="E31" s="80" t="s">
         <v>233</v>
       </c>
       <c r="F31" s="82" t="s">
@@ -10960,20 +10964,20 @@
         <f>SUM(K31:L31)</f>
         <v>144</v>
       </c>
-      <c r="N31" s="84" t="s">
+      <c r="N31" s="80" t="s">
         <v>234</v>
       </c>
-      <c r="O31" s="84" t="s">
+      <c r="O31" s="80" t="s">
         <v>235</v>
       </c>
-      <c r="P31" s="84" t="s">
+      <c r="P31" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q31" s="84" t="s">
+      <c r="Q31" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A32" s="38" t="str">
         <f>_xlfn.XLOOKUP(B32,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -10983,7 +10987,7 @@
       </c>
       <c r="C32" s="82"/>
       <c r="D32" s="82"/>
-      <c r="E32" s="84"/>
+      <c r="E32" s="80"/>
       <c r="F32" s="82"/>
       <c r="G32" s="82"/>
       <c r="H32" s="82"/>
@@ -10992,12 +10996,12 @@
       <c r="K32" s="82"/>
       <c r="L32" s="82"/>
       <c r="M32" s="82"/>
-      <c r="N32" s="84"/>
-      <c r="O32" s="84"/>
-      <c r="P32" s="84"/>
-      <c r="Q32" s="84"/>
-    </row>
-    <row r="33" spans="1:20" ht="116" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="N32" s="80"/>
+      <c r="O32" s="80"/>
+      <c r="P32" s="80"/>
+      <c r="Q32" s="80"/>
+    </row>
+    <row r="33" spans="1:20" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="48" t="str">
         <f>_xlfn.XLOOKUP(B33,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -11007,7 +11011,7 @@
       </c>
       <c r="C33" s="83"/>
       <c r="D33" s="83"/>
-      <c r="E33" s="85"/>
+      <c r="E33" s="81"/>
       <c r="F33" s="83"/>
       <c r="G33" s="83"/>
       <c r="H33" s="83"/>
@@ -11016,12 +11020,12 @@
       <c r="K33" s="83"/>
       <c r="L33" s="83"/>
       <c r="M33" s="83"/>
-      <c r="N33" s="85"/>
-      <c r="O33" s="85"/>
-      <c r="P33" s="85"/>
-      <c r="Q33" s="85"/>
-    </row>
-    <row r="34" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N33" s="81"/>
+      <c r="O33" s="81"/>
+      <c r="P33" s="81"/>
+      <c r="Q33" s="81"/>
+    </row>
+    <row r="34" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A34" s="38" t="str">
         <f>_xlfn.XLOOKUP(B34,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -11035,7 +11039,7 @@
       <c r="D34" s="82" t="s">
         <v>236</v>
       </c>
-      <c r="E34" s="84" t="s">
+      <c r="E34" s="80" t="s">
         <v>237</v>
       </c>
       <c r="F34" s="82" t="s">
@@ -11061,20 +11065,20 @@
         <f>SUM(K34:L34)</f>
         <v>144</v>
       </c>
-      <c r="N34" s="84" t="s">
+      <c r="N34" s="80" t="s">
         <v>238</v>
       </c>
-      <c r="O34" s="84" t="s">
+      <c r="O34" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="P34" s="84" t="s">
+      <c r="P34" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q34" s="84" t="s">
+      <c r="Q34" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:20" ht="144" x14ac:dyDescent="0.3">
       <c r="A35" s="38" t="str">
         <f>_xlfn.XLOOKUP(B35,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -11084,7 +11088,7 @@
       </c>
       <c r="C35" s="82"/>
       <c r="D35" s="82"/>
-      <c r="E35" s="84"/>
+      <c r="E35" s="80"/>
       <c r="F35" s="82"/>
       <c r="G35" s="82"/>
       <c r="H35" s="82"/>
@@ -11093,12 +11097,12 @@
       <c r="K35" s="82"/>
       <c r="L35" s="82"/>
       <c r="M35" s="82"/>
-      <c r="N35" s="84"/>
-      <c r="O35" s="84"/>
-      <c r="P35" s="84"/>
-      <c r="Q35" s="84"/>
-    </row>
-    <row r="36" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N35" s="80"/>
+      <c r="O35" s="80"/>
+      <c r="P35" s="80"/>
+      <c r="Q35" s="80"/>
+    </row>
+    <row r="36" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A36" s="48" t="str">
         <f>_xlfn.XLOOKUP(B36,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11108,7 +11112,7 @@
       </c>
       <c r="C36" s="83"/>
       <c r="D36" s="83"/>
-      <c r="E36" s="85"/>
+      <c r="E36" s="81"/>
       <c r="F36" s="83"/>
       <c r="G36" s="83"/>
       <c r="H36" s="83"/>
@@ -11117,12 +11121,12 @@
       <c r="K36" s="83"/>
       <c r="L36" s="83"/>
       <c r="M36" s="83"/>
-      <c r="N36" s="85"/>
-      <c r="O36" s="85"/>
-      <c r="P36" s="85"/>
-      <c r="Q36" s="85"/>
-    </row>
-    <row r="37" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N36" s="81"/>
+      <c r="O36" s="81"/>
+      <c r="P36" s="81"/>
+      <c r="Q36" s="81"/>
+    </row>
+    <row r="37" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A37" s="38" t="str">
         <f>_xlfn.XLOOKUP(B37,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -11136,7 +11140,7 @@
       <c r="D37" s="82" t="s">
         <v>239</v>
       </c>
-      <c r="E37" s="84" t="s">
+      <c r="E37" s="80" t="s">
         <v>240</v>
       </c>
       <c r="F37" s="82" t="s">
@@ -11162,20 +11166,20 @@
         <f>SUM(K37:L37)</f>
         <v>144</v>
       </c>
-      <c r="N37" s="84" t="s">
+      <c r="N37" s="80" t="s">
         <v>241</v>
       </c>
-      <c r="O37" s="84" t="s">
+      <c r="O37" s="80" t="s">
         <v>242</v>
       </c>
-      <c r="P37" s="84" t="s">
+      <c r="P37" s="80" t="s">
         <v>221</v>
       </c>
-      <c r="Q37" s="84" t="s">
+      <c r="Q37" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A38" s="38" t="str">
         <f>_xlfn.XLOOKUP(B38,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11185,7 +11189,7 @@
       </c>
       <c r="C38" s="82"/>
       <c r="D38" s="82"/>
-      <c r="E38" s="84"/>
+      <c r="E38" s="80"/>
       <c r="F38" s="82"/>
       <c r="G38" s="82"/>
       <c r="H38" s="82"/>
@@ -11194,12 +11198,12 @@
       <c r="K38" s="82"/>
       <c r="L38" s="82"/>
       <c r="M38" s="82"/>
-      <c r="N38" s="84"/>
-      <c r="O38" s="84"/>
-      <c r="P38" s="84"/>
-      <c r="Q38" s="84"/>
-    </row>
-    <row r="39" spans="1:20" ht="396" x14ac:dyDescent="0.35">
+      <c r="N38" s="80"/>
+      <c r="O38" s="80"/>
+      <c r="P38" s="80"/>
+      <c r="Q38" s="80"/>
+    </row>
+    <row r="39" spans="1:20" ht="409.6" x14ac:dyDescent="0.3">
       <c r="A39" s="60" t="s">
         <v>11</v>
       </c>
@@ -11257,7 +11261,7 @@
       <c r="S39" s="38"/>
       <c r="T39" s="38"/>
     </row>
-    <row r="40" spans="1:20" ht="314" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:20" ht="360.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="60" t="s">
         <v>11</v>
       </c>
@@ -11316,7 +11320,7 @@
       <c r="S40" s="38"/>
       <c r="T40" s="38"/>
     </row>
-    <row r="41" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A41" s="38" t="str">
         <f>_xlfn.XLOOKUP(B41,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11330,7 +11334,7 @@
       <c r="D41" s="82" t="s">
         <v>252</v>
       </c>
-      <c r="E41" s="84" t="s">
+      <c r="E41" s="80" t="s">
         <v>253</v>
       </c>
       <c r="F41" s="82" t="s">
@@ -11356,20 +11360,20 @@
         <f>SUM(K41:L41)</f>
         <v>144</v>
       </c>
-      <c r="N41" s="84" t="s">
+      <c r="N41" s="80" t="s">
         <v>254</v>
       </c>
-      <c r="O41" s="87" t="s">
+      <c r="O41" s="88" t="s">
         <v>255</v>
       </c>
-      <c r="P41" s="84" t="s">
+      <c r="P41" s="80" t="s">
         <v>256</v>
       </c>
-      <c r="Q41" s="84" t="s">
+      <c r="Q41" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A42" s="38" t="str">
         <f>_xlfn.XLOOKUP(B42,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -11379,7 +11383,7 @@
       </c>
       <c r="C42" s="82"/>
       <c r="D42" s="82"/>
-      <c r="E42" s="84"/>
+      <c r="E42" s="80"/>
       <c r="F42" s="82"/>
       <c r="G42" s="82"/>
       <c r="H42" s="82"/>
@@ -11388,12 +11392,12 @@
       <c r="K42" s="82"/>
       <c r="L42" s="82"/>
       <c r="M42" s="82"/>
-      <c r="N42" s="84"/>
-      <c r="O42" s="84"/>
-      <c r="P42" s="84"/>
-      <c r="Q42" s="84"/>
-    </row>
-    <row r="43" spans="1:20" ht="116" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="N42" s="80"/>
+      <c r="O42" s="80"/>
+      <c r="P42" s="80"/>
+      <c r="Q42" s="80"/>
+    </row>
+    <row r="43" spans="1:20" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="48" t="str">
         <f>_xlfn.XLOOKUP(B43,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -11403,7 +11407,7 @@
       </c>
       <c r="C43" s="83"/>
       <c r="D43" s="83"/>
-      <c r="E43" s="85"/>
+      <c r="E43" s="81"/>
       <c r="F43" s="83"/>
       <c r="G43" s="83"/>
       <c r="H43" s="83"/>
@@ -11412,12 +11416,12 @@
       <c r="K43" s="83"/>
       <c r="L43" s="83"/>
       <c r="M43" s="83"/>
-      <c r="N43" s="85"/>
-      <c r="O43" s="85"/>
-      <c r="P43" s="85"/>
-      <c r="Q43" s="85"/>
-    </row>
-    <row r="44" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N43" s="81"/>
+      <c r="O43" s="81"/>
+      <c r="P43" s="81"/>
+      <c r="Q43" s="81"/>
+    </row>
+    <row r="44" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A44" s="38" t="str">
         <f>_xlfn.XLOOKUP(B44,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11431,7 +11435,7 @@
       <c r="D44" s="82" t="s">
         <v>257</v>
       </c>
-      <c r="E44" s="84" t="s">
+      <c r="E44" s="80" t="s">
         <v>258</v>
       </c>
       <c r="F44" s="82" t="s">
@@ -11457,20 +11461,20 @@
         <f>SUM(K44:L44)</f>
         <v>144</v>
       </c>
-      <c r="N44" s="84" t="s">
+      <c r="N44" s="80" t="s">
         <v>259</v>
       </c>
-      <c r="O44" s="84" t="s">
+      <c r="O44" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="P44" s="84" t="s">
+      <c r="P44" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q44" s="84" t="s">
+      <c r="Q44" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A45" s="38" t="str">
         <f>_xlfn.XLOOKUP(B45,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -11480,7 +11484,7 @@
       </c>
       <c r="C45" s="82"/>
       <c r="D45" s="82"/>
-      <c r="E45" s="84"/>
+      <c r="E45" s="80"/>
       <c r="F45" s="82"/>
       <c r="G45" s="82"/>
       <c r="H45" s="82"/>
@@ -11489,12 +11493,12 @@
       <c r="K45" s="82"/>
       <c r="L45" s="82"/>
       <c r="M45" s="82"/>
-      <c r="N45" s="84"/>
-      <c r="O45" s="84"/>
-      <c r="P45" s="84"/>
-      <c r="Q45" s="84"/>
-    </row>
-    <row r="46" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N45" s="80"/>
+      <c r="O45" s="80"/>
+      <c r="P45" s="80"/>
+      <c r="Q45" s="80"/>
+    </row>
+    <row r="46" spans="1:20" ht="144" x14ac:dyDescent="0.3">
       <c r="A46" s="48" t="str">
         <f>_xlfn.XLOOKUP(B46,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -11504,7 +11508,7 @@
       </c>
       <c r="C46" s="83"/>
       <c r="D46" s="83"/>
-      <c r="E46" s="85"/>
+      <c r="E46" s="81"/>
       <c r="F46" s="83"/>
       <c r="G46" s="83"/>
       <c r="H46" s="83"/>
@@ -11513,12 +11517,12 @@
       <c r="K46" s="83"/>
       <c r="L46" s="83"/>
       <c r="M46" s="83"/>
-      <c r="N46" s="85"/>
-      <c r="O46" s="85"/>
-      <c r="P46" s="85"/>
-      <c r="Q46" s="85"/>
-    </row>
-    <row r="47" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N46" s="81"/>
+      <c r="O46" s="81"/>
+      <c r="P46" s="81"/>
+      <c r="Q46" s="81"/>
+    </row>
+    <row r="47" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A47" s="38" t="str">
         <f>_xlfn.XLOOKUP(B47,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11532,7 +11536,7 @@
       <c r="D47" s="82" t="s">
         <v>260</v>
       </c>
-      <c r="E47" s="84" t="s">
+      <c r="E47" s="80" t="s">
         <v>261</v>
       </c>
       <c r="F47" s="82" t="s">
@@ -11558,20 +11562,20 @@
         <f>SUM(K47:L47)</f>
         <v>144</v>
       </c>
-      <c r="N47" s="84" t="s">
+      <c r="N47" s="80" t="s">
         <v>262</v>
       </c>
-      <c r="O47" s="84" t="s">
+      <c r="O47" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="P47" s="84" t="s">
+      <c r="P47" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q47" s="84" t="s">
+      <c r="Q47" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="48" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A48" s="38" t="str">
         <f>_xlfn.XLOOKUP(B48,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -11581,7 +11585,7 @@
       </c>
       <c r="C48" s="82"/>
       <c r="D48" s="82"/>
-      <c r="E48" s="84"/>
+      <c r="E48" s="80"/>
       <c r="F48" s="82"/>
       <c r="G48" s="82"/>
       <c r="H48" s="82"/>
@@ -11590,12 +11594,12 @@
       <c r="K48" s="82"/>
       <c r="L48" s="82"/>
       <c r="M48" s="82"/>
-      <c r="N48" s="84"/>
-      <c r="O48" s="84"/>
-      <c r="P48" s="84"/>
-      <c r="Q48" s="84"/>
-    </row>
-    <row r="49" spans="1:20" ht="116" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="N48" s="80"/>
+      <c r="O48" s="80"/>
+      <c r="P48" s="80"/>
+      <c r="Q48" s="80"/>
+    </row>
+    <row r="49" spans="1:20" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="48" t="str">
         <f>_xlfn.XLOOKUP(B49,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -11605,7 +11609,7 @@
       </c>
       <c r="C49" s="83"/>
       <c r="D49" s="83"/>
-      <c r="E49" s="85"/>
+      <c r="E49" s="81"/>
       <c r="F49" s="83"/>
       <c r="G49" s="83"/>
       <c r="H49" s="83"/>
@@ -11614,12 +11618,12 @@
       <c r="K49" s="83"/>
       <c r="L49" s="83"/>
       <c r="M49" s="83"/>
-      <c r="N49" s="85"/>
-      <c r="O49" s="85"/>
-      <c r="P49" s="85"/>
-      <c r="Q49" s="85"/>
-    </row>
-    <row r="50" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N49" s="81"/>
+      <c r="O49" s="81"/>
+      <c r="P49" s="81"/>
+      <c r="Q49" s="81"/>
+    </row>
+    <row r="50" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A50" s="38" t="str">
         <f>_xlfn.XLOOKUP(B50,'[1]Paso 3 Redacción RA '!I$3:I$12,'[1]Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11633,7 +11637,7 @@
       <c r="D50" s="82" t="s">
         <v>263</v>
       </c>
-      <c r="E50" s="84" t="s">
+      <c r="E50" s="80" t="s">
         <v>264</v>
       </c>
       <c r="F50" s="82" t="s">
@@ -11659,20 +11663,20 @@
         <f>SUM(K50:L50)</f>
         <v>144</v>
       </c>
-      <c r="N50" s="84" t="s">
+      <c r="N50" s="80" t="s">
         <v>265</v>
       </c>
-      <c r="O50" s="84" t="s">
+      <c r="O50" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="P50" s="84" t="s">
+      <c r="P50" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q50" s="84" t="s">
+      <c r="Q50" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="51" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A51" s="38" t="str">
         <f>_xlfn.XLOOKUP(B51,'[1]Paso 3 Redacción RA '!I$3:I$12,'[1]Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -11682,7 +11686,7 @@
       </c>
       <c r="C51" s="82"/>
       <c r="D51" s="82"/>
-      <c r="E51" s="84"/>
+      <c r="E51" s="80"/>
       <c r="F51" s="82"/>
       <c r="G51" s="82"/>
       <c r="H51" s="82"/>
@@ -11691,12 +11695,12 @@
       <c r="K51" s="82"/>
       <c r="L51" s="82"/>
       <c r="M51" s="82"/>
-      <c r="N51" s="84"/>
-      <c r="O51" s="84"/>
-      <c r="P51" s="84"/>
-      <c r="Q51" s="84"/>
-    </row>
-    <row r="52" spans="1:20" ht="116" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="N51" s="80"/>
+      <c r="O51" s="80"/>
+      <c r="P51" s="80"/>
+      <c r="Q51" s="80"/>
+    </row>
+    <row r="52" spans="1:20" ht="144.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="48" t="str">
         <f>_xlfn.XLOOKUP(B52,'[1]Paso 3 Redacción RA '!I$3:I$12,'[1]Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -11706,7 +11710,7 @@
       </c>
       <c r="C52" s="83"/>
       <c r="D52" s="83"/>
-      <c r="E52" s="85"/>
+      <c r="E52" s="81"/>
       <c r="F52" s="83"/>
       <c r="G52" s="83"/>
       <c r="H52" s="83"/>
@@ -11715,12 +11719,12 @@
       <c r="K52" s="83"/>
       <c r="L52" s="83"/>
       <c r="M52" s="83"/>
-      <c r="N52" s="85"/>
-      <c r="O52" s="85"/>
-      <c r="P52" s="85"/>
-      <c r="Q52" s="85"/>
-    </row>
-    <row r="53" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N52" s="81"/>
+      <c r="O52" s="81"/>
+      <c r="P52" s="81"/>
+      <c r="Q52" s="81"/>
+    </row>
+    <row r="53" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A53" s="38" t="str">
         <f>_xlfn.XLOOKUP(B53,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -11734,7 +11738,7 @@
       <c r="D53" s="82" t="s">
         <v>266</v>
       </c>
-      <c r="E53" s="84" t="s">
+      <c r="E53" s="80" t="s">
         <v>267</v>
       </c>
       <c r="F53" s="82" t="s">
@@ -11760,20 +11764,20 @@
         <f>SUM(K53:L53)</f>
         <v>144</v>
       </c>
-      <c r="N53" s="84" t="s">
+      <c r="N53" s="80" t="s">
         <v>268</v>
       </c>
-      <c r="O53" s="84" t="s">
+      <c r="O53" s="80" t="s">
         <v>242</v>
       </c>
-      <c r="P53" s="84" t="s">
+      <c r="P53" s="80" t="s">
         <v>221</v>
       </c>
-      <c r="Q53" s="84" t="s">
+      <c r="Q53" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="54" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A54" s="38" t="str">
         <f>_xlfn.XLOOKUP(B54,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11783,7 +11787,7 @@
       </c>
       <c r="C54" s="82"/>
       <c r="D54" s="82"/>
-      <c r="E54" s="84"/>
+      <c r="E54" s="80"/>
       <c r="F54" s="82"/>
       <c r="G54" s="82"/>
       <c r="H54" s="82"/>
@@ -11792,12 +11796,12 @@
       <c r="K54" s="82"/>
       <c r="L54" s="82"/>
       <c r="M54" s="82"/>
-      <c r="N54" s="84"/>
-      <c r="O54" s="84"/>
-      <c r="P54" s="84"/>
-      <c r="Q54" s="84"/>
-    </row>
-    <row r="55" spans="1:20" ht="313.5" x14ac:dyDescent="0.35">
+      <c r="N54" s="80"/>
+      <c r="O54" s="80"/>
+      <c r="P54" s="80"/>
+      <c r="Q54" s="80"/>
+    </row>
+    <row r="55" spans="1:20" ht="360" x14ac:dyDescent="0.3">
       <c r="A55" s="60" t="s">
         <v>11</v>
       </c>
@@ -11855,7 +11859,7 @@
       <c r="S55" s="38"/>
       <c r="T55" s="38"/>
     </row>
-    <row r="56" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A56" s="38" t="str">
         <f>_xlfn.XLOOKUP(B56,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11869,7 +11873,7 @@
       <c r="D56" s="82" t="s">
         <v>273</v>
       </c>
-      <c r="E56" s="84" t="s">
+      <c r="E56" s="80" t="s">
         <v>274</v>
       </c>
       <c r="F56" s="82" t="s">
@@ -11895,20 +11899,20 @@
         <f>SUM(K56:L56)</f>
         <v>144</v>
       </c>
-      <c r="N56" s="84" t="s">
+      <c r="N56" s="80" t="s">
         <v>275</v>
       </c>
-      <c r="O56" s="84" t="s">
+      <c r="O56" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="P56" s="84" t="s">
+      <c r="P56" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q56" s="84" t="s">
+      <c r="Q56" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="57" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A57" s="38" t="str">
         <f>_xlfn.XLOOKUP(B57,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -11918,7 +11922,7 @@
       </c>
       <c r="C57" s="82"/>
       <c r="D57" s="82"/>
-      <c r="E57" s="84"/>
+      <c r="E57" s="80"/>
       <c r="F57" s="82"/>
       <c r="G57" s="82"/>
       <c r="H57" s="82"/>
@@ -11927,12 +11931,12 @@
       <c r="K57" s="82"/>
       <c r="L57" s="82"/>
       <c r="M57" s="82"/>
-      <c r="N57" s="84"/>
-      <c r="O57" s="84"/>
-      <c r="P57" s="84"/>
-      <c r="Q57" s="84"/>
-    </row>
-    <row r="58" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N57" s="80"/>
+      <c r="O57" s="80"/>
+      <c r="P57" s="80"/>
+      <c r="Q57" s="80"/>
+    </row>
+    <row r="58" spans="1:20" ht="144" x14ac:dyDescent="0.3">
       <c r="A58" s="38" t="str">
         <f>_xlfn.XLOOKUP(B58,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -11942,7 +11946,7 @@
       </c>
       <c r="C58" s="82"/>
       <c r="D58" s="82"/>
-      <c r="E58" s="84"/>
+      <c r="E58" s="80"/>
       <c r="F58" s="82"/>
       <c r="G58" s="82"/>
       <c r="H58" s="82"/>
@@ -11951,12 +11955,12 @@
       <c r="K58" s="82"/>
       <c r="L58" s="82"/>
       <c r="M58" s="82"/>
-      <c r="N58" s="84"/>
-      <c r="O58" s="84"/>
-      <c r="P58" s="84"/>
-      <c r="Q58" s="84"/>
-    </row>
-    <row r="59" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N58" s="80"/>
+      <c r="O58" s="80"/>
+      <c r="P58" s="80"/>
+      <c r="Q58" s="80"/>
+    </row>
+    <row r="59" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A59" s="48" t="str">
         <f>_xlfn.XLOOKUP(B59,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11966,7 +11970,7 @@
       </c>
       <c r="C59" s="83"/>
       <c r="D59" s="83"/>
-      <c r="E59" s="85"/>
+      <c r="E59" s="81"/>
       <c r="F59" s="83"/>
       <c r="G59" s="83"/>
       <c r="H59" s="83"/>
@@ -11975,12 +11979,12 @@
       <c r="K59" s="83"/>
       <c r="L59" s="83"/>
       <c r="M59" s="83"/>
-      <c r="N59" s="85"/>
-      <c r="O59" s="85"/>
-      <c r="P59" s="85"/>
-      <c r="Q59" s="85"/>
-    </row>
-    <row r="60" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N59" s="81"/>
+      <c r="O59" s="81"/>
+      <c r="P59" s="81"/>
+      <c r="Q59" s="81"/>
+    </row>
+    <row r="60" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A60" s="38" t="str">
         <f>_xlfn.XLOOKUP(B60,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -11994,7 +11998,7 @@
       <c r="D60" s="82" t="s">
         <v>276</v>
       </c>
-      <c r="E60" s="84" t="s">
+      <c r="E60" s="80" t="s">
         <v>277</v>
       </c>
       <c r="F60" s="82" t="s">
@@ -12020,20 +12024,20 @@
         <f>SUM(K60:L60)</f>
         <v>144</v>
       </c>
-      <c r="N60" s="84" t="s">
+      <c r="N60" s="80" t="s">
         <v>278</v>
       </c>
-      <c r="O60" s="84" t="s">
+      <c r="O60" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="P60" s="84" t="s">
+      <c r="P60" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q60" s="84" t="s">
+      <c r="Q60" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="61" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A61" s="38" t="str">
         <f>_xlfn.XLOOKUP(B61,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -12043,7 +12047,7 @@
       </c>
       <c r="C61" s="82"/>
       <c r="D61" s="82"/>
-      <c r="E61" s="84"/>
+      <c r="E61" s="80"/>
       <c r="F61" s="82"/>
       <c r="G61" s="82"/>
       <c r="H61" s="82"/>
@@ -12052,12 +12056,12 @@
       <c r="K61" s="82"/>
       <c r="L61" s="82"/>
       <c r="M61" s="82"/>
-      <c r="N61" s="84"/>
-      <c r="O61" s="84"/>
-      <c r="P61" s="84"/>
-      <c r="Q61" s="84"/>
-    </row>
-    <row r="62" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N61" s="80"/>
+      <c r="O61" s="80"/>
+      <c r="P61" s="80"/>
+      <c r="Q61" s="80"/>
+    </row>
+    <row r="62" spans="1:20" ht="144" x14ac:dyDescent="0.3">
       <c r="A62" s="38" t="str">
         <f>_xlfn.XLOOKUP(B62,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -12067,7 +12071,7 @@
       </c>
       <c r="C62" s="82"/>
       <c r="D62" s="82"/>
-      <c r="E62" s="84"/>
+      <c r="E62" s="80"/>
       <c r="F62" s="82"/>
       <c r="G62" s="82"/>
       <c r="H62" s="82"/>
@@ -12076,12 +12080,12 @@
       <c r="K62" s="82"/>
       <c r="L62" s="82"/>
       <c r="M62" s="82"/>
-      <c r="N62" s="84"/>
-      <c r="O62" s="84"/>
-      <c r="P62" s="84"/>
-      <c r="Q62" s="84"/>
-    </row>
-    <row r="63" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N62" s="80"/>
+      <c r="O62" s="80"/>
+      <c r="P62" s="80"/>
+      <c r="Q62" s="80"/>
+    </row>
+    <row r="63" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A63" s="48" t="str">
         <f>_xlfn.XLOOKUP(B63,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12091,7 +12095,7 @@
       </c>
       <c r="C63" s="83"/>
       <c r="D63" s="83"/>
-      <c r="E63" s="85"/>
+      <c r="E63" s="81"/>
       <c r="F63" s="83"/>
       <c r="G63" s="83"/>
       <c r="H63" s="83"/>
@@ -12100,12 +12104,12 @@
       <c r="K63" s="83"/>
       <c r="L63" s="83"/>
       <c r="M63" s="83"/>
-      <c r="N63" s="85"/>
-      <c r="O63" s="85"/>
-      <c r="P63" s="85"/>
-      <c r="Q63" s="85"/>
-    </row>
-    <row r="64" spans="1:20" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N63" s="81"/>
+      <c r="O63" s="81"/>
+      <c r="P63" s="81"/>
+      <c r="Q63" s="81"/>
+    </row>
+    <row r="64" spans="1:20" ht="126" x14ac:dyDescent="0.3">
       <c r="A64" s="38" t="str">
         <f>_xlfn.XLOOKUP(B64,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12119,7 +12123,7 @@
       <c r="D64" s="82" t="s">
         <v>279</v>
       </c>
-      <c r="E64" s="84" t="s">
+      <c r="E64" s="80" t="s">
         <v>280</v>
       </c>
       <c r="F64" s="82" t="s">
@@ -12145,20 +12149,20 @@
         <f>SUM(K64:L64)</f>
         <v>144</v>
       </c>
-      <c r="N64" s="84" t="s">
+      <c r="N64" s="80" t="s">
         <v>281</v>
       </c>
-      <c r="O64" s="84" t="s">
+      <c r="O64" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="P64" s="84" t="s">
+      <c r="P64" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q64" s="84" t="s">
+      <c r="Q64" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A65" s="38" t="str">
         <f>_xlfn.XLOOKUP(B65,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -12168,7 +12172,7 @@
       </c>
       <c r="C65" s="82"/>
       <c r="D65" s="82"/>
-      <c r="E65" s="84"/>
+      <c r="E65" s="80"/>
       <c r="F65" s="82"/>
       <c r="G65" s="82"/>
       <c r="H65" s="82"/>
@@ -12177,12 +12181,12 @@
       <c r="K65" s="82"/>
       <c r="L65" s="82"/>
       <c r="M65" s="82"/>
-      <c r="N65" s="84"/>
-      <c r="O65" s="84"/>
-      <c r="P65" s="84"/>
-      <c r="Q65" s="84"/>
-    </row>
-    <row r="66" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N65" s="80"/>
+      <c r="O65" s="80"/>
+      <c r="P65" s="80"/>
+      <c r="Q65" s="80"/>
+    </row>
+    <row r="66" spans="1:18" ht="144" x14ac:dyDescent="0.3">
       <c r="A66" s="38" t="str">
         <f>_xlfn.XLOOKUP(B66,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -12192,7 +12196,7 @@
       </c>
       <c r="C66" s="82"/>
       <c r="D66" s="82"/>
-      <c r="E66" s="84"/>
+      <c r="E66" s="80"/>
       <c r="F66" s="82"/>
       <c r="G66" s="82"/>
       <c r="H66" s="82"/>
@@ -12201,12 +12205,12 @@
       <c r="K66" s="82"/>
       <c r="L66" s="82"/>
       <c r="M66" s="82"/>
-      <c r="N66" s="84"/>
-      <c r="O66" s="84"/>
-      <c r="P66" s="84"/>
-      <c r="Q66" s="84"/>
-    </row>
-    <row r="67" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N66" s="80"/>
+      <c r="O66" s="80"/>
+      <c r="P66" s="80"/>
+      <c r="Q66" s="80"/>
+    </row>
+    <row r="67" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A67" s="48" t="str">
         <f>_xlfn.XLOOKUP(B67,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12216,7 +12220,7 @@
       </c>
       <c r="C67" s="83"/>
       <c r="D67" s="83"/>
-      <c r="E67" s="85"/>
+      <c r="E67" s="81"/>
       <c r="F67" s="83"/>
       <c r="G67" s="83"/>
       <c r="H67" s="83"/>
@@ -12225,12 +12229,12 @@
       <c r="K67" s="83"/>
       <c r="L67" s="83"/>
       <c r="M67" s="83"/>
-      <c r="N67" s="85"/>
-      <c r="O67" s="85"/>
-      <c r="P67" s="85"/>
-      <c r="Q67" s="85"/>
-    </row>
-    <row r="68" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N67" s="81"/>
+      <c r="O67" s="81"/>
+      <c r="P67" s="81"/>
+      <c r="Q67" s="81"/>
+    </row>
+    <row r="68" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A68" s="38" t="str">
         <f>_xlfn.XLOOKUP(B68,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12244,7 +12248,7 @@
       <c r="D68" s="82" t="s">
         <v>282</v>
       </c>
-      <c r="E68" s="84" t="s">
+      <c r="E68" s="80" t="s">
         <v>283</v>
       </c>
       <c r="F68" s="82" t="s">
@@ -12270,20 +12274,20 @@
         <f>SUM(K68:L68)</f>
         <v>144</v>
       </c>
-      <c r="N68" s="84" t="s">
+      <c r="N68" s="80" t="s">
         <v>284</v>
       </c>
-      <c r="O68" s="84" t="s">
+      <c r="O68" s="80" t="s">
         <v>285</v>
       </c>
-      <c r="P68" s="84" t="s">
+      <c r="P68" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q68" s="84" t="s">
+      <c r="Q68" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A69" s="38" t="str">
         <f>_xlfn.XLOOKUP(B69,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -12293,7 +12297,7 @@
       </c>
       <c r="C69" s="82"/>
       <c r="D69" s="82"/>
-      <c r="E69" s="84"/>
+      <c r="E69" s="80"/>
       <c r="F69" s="82"/>
       <c r="G69" s="82"/>
       <c r="H69" s="82"/>
@@ -12302,12 +12306,12 @@
       <c r="K69" s="82"/>
       <c r="L69" s="82"/>
       <c r="M69" s="82"/>
-      <c r="N69" s="84"/>
-      <c r="O69" s="84"/>
-      <c r="P69" s="84"/>
-      <c r="Q69" s="84"/>
-    </row>
-    <row r="70" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N69" s="80"/>
+      <c r="O69" s="80"/>
+      <c r="P69" s="80"/>
+      <c r="Q69" s="80"/>
+    </row>
+    <row r="70" spans="1:18" ht="144" x14ac:dyDescent="0.3">
       <c r="A70" s="48" t="str">
         <f>_xlfn.XLOOKUP(B70,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -12317,7 +12321,7 @@
       </c>
       <c r="C70" s="83"/>
       <c r="D70" s="83"/>
-      <c r="E70" s="85"/>
+      <c r="E70" s="81"/>
       <c r="F70" s="83"/>
       <c r="G70" s="83"/>
       <c r="H70" s="83"/>
@@ -12326,12 +12330,12 @@
       <c r="K70" s="83"/>
       <c r="L70" s="83"/>
       <c r="M70" s="83"/>
-      <c r="N70" s="85"/>
-      <c r="O70" s="85"/>
-      <c r="P70" s="85"/>
-      <c r="Q70" s="85"/>
-    </row>
-    <row r="71" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N70" s="81"/>
+      <c r="O70" s="81"/>
+      <c r="P70" s="81"/>
+      <c r="Q70" s="81"/>
+    </row>
+    <row r="71" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A71" s="38" t="str">
         <f>_xlfn.XLOOKUP(B71,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12345,7 +12349,7 @@
       <c r="D71" s="82" t="s">
         <v>286</v>
       </c>
-      <c r="E71" s="84" t="s">
+      <c r="E71" s="80" t="s">
         <v>287</v>
       </c>
       <c r="F71" s="82" t="s">
@@ -12371,20 +12375,20 @@
         <f>SUM(K71:L71)</f>
         <v>144</v>
       </c>
-      <c r="N71" s="84" t="s">
+      <c r="N71" s="80" t="s">
         <v>288</v>
       </c>
-      <c r="O71" s="84" t="s">
+      <c r="O71" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="P71" s="84" t="s">
+      <c r="P71" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q71" s="84" t="s">
+      <c r="Q71" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:18" ht="144" x14ac:dyDescent="0.3">
       <c r="A72" s="38" t="str">
         <f>_xlfn.XLOOKUP(B72,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -12394,7 +12398,7 @@
       </c>
       <c r="C72" s="82"/>
       <c r="D72" s="82"/>
-      <c r="E72" s="84"/>
+      <c r="E72" s="80"/>
       <c r="F72" s="82"/>
       <c r="G72" s="82"/>
       <c r="H72" s="82"/>
@@ -12403,12 +12407,12 @@
       <c r="K72" s="82"/>
       <c r="L72" s="82"/>
       <c r="M72" s="82"/>
-      <c r="N72" s="84"/>
-      <c r="O72" s="84"/>
-      <c r="P72" s="84"/>
-      <c r="Q72" s="84"/>
-    </row>
-    <row r="73" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N72" s="80"/>
+      <c r="O72" s="80"/>
+      <c r="P72" s="80"/>
+      <c r="Q72" s="80"/>
+    </row>
+    <row r="73" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A73" s="48" t="str">
         <f>_xlfn.XLOOKUP(B73,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12418,7 +12422,7 @@
       </c>
       <c r="C73" s="83"/>
       <c r="D73" s="83"/>
-      <c r="E73" s="85"/>
+      <c r="E73" s="81"/>
       <c r="F73" s="83"/>
       <c r="G73" s="83"/>
       <c r="H73" s="83"/>
@@ -12427,12 +12431,12 @@
       <c r="K73" s="83"/>
       <c r="L73" s="83"/>
       <c r="M73" s="83"/>
-      <c r="N73" s="85"/>
-      <c r="O73" s="85"/>
-      <c r="P73" s="85"/>
-      <c r="Q73" s="85"/>
-    </row>
-    <row r="74" spans="1:18" ht="159" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="N73" s="81"/>
+      <c r="O73" s="81"/>
+      <c r="P73" s="81"/>
+      <c r="Q73" s="81"/>
+    </row>
+    <row r="74" spans="1:18" ht="159" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="38" t="str">
         <f>_xlfn.XLOOKUP(B74,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -12446,7 +12450,7 @@
       <c r="D74" s="82" t="s">
         <v>289</v>
       </c>
-      <c r="E74" s="84" t="s">
+      <c r="E74" s="80" t="s">
         <v>290</v>
       </c>
       <c r="F74" s="82" t="s">
@@ -12472,20 +12476,20 @@
         <f>SUM(K74:L74)</f>
         <v>144</v>
       </c>
-      <c r="N74" s="84" t="s">
+      <c r="N74" s="80" t="s">
         <v>291</v>
       </c>
-      <c r="O74" s="84" t="s">
+      <c r="O74" s="80" t="s">
         <v>292</v>
       </c>
-      <c r="P74" s="84" t="s">
+      <c r="P74" s="80" t="s">
         <v>293</v>
       </c>
-      <c r="Q74" s="84" t="s">
+      <c r="Q74" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="193" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:18" ht="193.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="48" t="str">
         <f>_xlfn.XLOOKUP(B75,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -12495,7 +12499,7 @@
       </c>
       <c r="C75" s="83"/>
       <c r="D75" s="83"/>
-      <c r="E75" s="85"/>
+      <c r="E75" s="81"/>
       <c r="F75" s="83"/>
       <c r="G75" s="83"/>
       <c r="H75" s="83"/>
@@ -12504,12 +12508,12 @@
       <c r="K75" s="83"/>
       <c r="L75" s="83"/>
       <c r="M75" s="83"/>
-      <c r="N75" s="85"/>
-      <c r="O75" s="85"/>
-      <c r="P75" s="85"/>
-      <c r="Q75" s="85"/>
-    </row>
-    <row r="76" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N75" s="81"/>
+      <c r="O75" s="81"/>
+      <c r="P75" s="81"/>
+      <c r="Q75" s="81"/>
+    </row>
+    <row r="76" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A76" s="38" t="str">
         <f>_xlfn.XLOOKUP(B76,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12523,7 +12527,7 @@
       <c r="D76" s="82" t="s">
         <v>294</v>
       </c>
-      <c r="E76" s="84" t="s">
+      <c r="E76" s="80" t="s">
         <v>295</v>
       </c>
       <c r="F76" s="82" t="s">
@@ -12549,20 +12553,20 @@
         <f>SUM(K76:L76)</f>
         <v>144</v>
       </c>
-      <c r="N76" s="84" t="s">
+      <c r="N76" s="80" t="s">
         <v>296</v>
       </c>
-      <c r="O76" s="84" t="s">
+      <c r="O76" s="80" t="s">
         <v>297</v>
       </c>
-      <c r="P76" s="84" t="s">
+      <c r="P76" s="80" t="s">
         <v>293</v>
       </c>
-      <c r="Q76" s="84" t="s">
+      <c r="Q76" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A77" s="38" t="str">
         <f>_xlfn.XLOOKUP(B77,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -12572,7 +12576,7 @@
       </c>
       <c r="C77" s="82"/>
       <c r="D77" s="82"/>
-      <c r="E77" s="84"/>
+      <c r="E77" s="80"/>
       <c r="F77" s="82"/>
       <c r="G77" s="82"/>
       <c r="H77" s="82"/>
@@ -12581,12 +12585,12 @@
       <c r="K77" s="82"/>
       <c r="L77" s="82"/>
       <c r="M77" s="82"/>
-      <c r="N77" s="84"/>
-      <c r="O77" s="84"/>
-      <c r="P77" s="84"/>
-      <c r="Q77" s="84"/>
-    </row>
-    <row r="78" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N77" s="80"/>
+      <c r="O77" s="80"/>
+      <c r="P77" s="80"/>
+      <c r="Q77" s="80"/>
+    </row>
+    <row r="78" spans="1:18" ht="144" x14ac:dyDescent="0.3">
       <c r="A78" s="48" t="str">
         <f>_xlfn.XLOOKUP(B78,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -12596,7 +12600,7 @@
       </c>
       <c r="C78" s="83"/>
       <c r="D78" s="83"/>
-      <c r="E78" s="85"/>
+      <c r="E78" s="81"/>
       <c r="F78" s="83"/>
       <c r="G78" s="83"/>
       <c r="H78" s="83"/>
@@ -12605,16 +12609,16 @@
       <c r="K78" s="83"/>
       <c r="L78" s="83"/>
       <c r="M78" s="83"/>
-      <c r="N78" s="85"/>
-      <c r="O78" s="85"/>
-      <c r="P78" s="85"/>
-      <c r="Q78" s="85"/>
+      <c r="N78" s="81"/>
+      <c r="O78" s="81"/>
+      <c r="P78" s="81"/>
+      <c r="Q78" s="81"/>
       <c r="R78" s="3">
         <f>SUM(J56:J78)</f>
         <v>21</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A79" s="38" t="str">
         <f>_xlfn.XLOOKUP(B79,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12628,7 +12632,7 @@
       <c r="D79" s="82" t="s">
         <v>298</v>
       </c>
-      <c r="E79" s="84" t="s">
+      <c r="E79" s="80" t="s">
         <v>299</v>
       </c>
       <c r="F79" s="82" t="s">
@@ -12654,20 +12658,20 @@
         <f>SUM(K79:L79)</f>
         <v>144</v>
       </c>
-      <c r="N79" s="84" t="s">
+      <c r="N79" s="80" t="s">
         <v>300</v>
       </c>
-      <c r="O79" s="84" t="s">
+      <c r="O79" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="P79" s="84" t="s">
+      <c r="P79" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q79" s="84" t="s">
+      <c r="Q79" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A80" s="38" t="str">
         <f>_xlfn.XLOOKUP(B80,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -12677,7 +12681,7 @@
       </c>
       <c r="C80" s="82"/>
       <c r="D80" s="82"/>
-      <c r="E80" s="84"/>
+      <c r="E80" s="80"/>
       <c r="F80" s="82"/>
       <c r="G80" s="82"/>
       <c r="H80" s="82"/>
@@ -12686,12 +12690,12 @@
       <c r="K80" s="82"/>
       <c r="L80" s="82"/>
       <c r="M80" s="82"/>
-      <c r="N80" s="84"/>
-      <c r="O80" s="84"/>
-      <c r="P80" s="84"/>
-      <c r="Q80" s="84"/>
-    </row>
-    <row r="81" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N80" s="80"/>
+      <c r="O80" s="80"/>
+      <c r="P80" s="80"/>
+      <c r="Q80" s="80"/>
+    </row>
+    <row r="81" spans="1:18" ht="144" x14ac:dyDescent="0.3">
       <c r="A81" s="48" t="str">
         <f>_xlfn.XLOOKUP(B81,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -12701,7 +12705,7 @@
       </c>
       <c r="C81" s="83"/>
       <c r="D81" s="83"/>
-      <c r="E81" s="85"/>
+      <c r="E81" s="81"/>
       <c r="F81" s="83"/>
       <c r="G81" s="83"/>
       <c r="H81" s="83"/>
@@ -12710,16 +12714,16 @@
       <c r="K81" s="83"/>
       <c r="L81" s="83"/>
       <c r="M81" s="83"/>
-      <c r="N81" s="85"/>
-      <c r="O81" s="85"/>
-      <c r="P81" s="85"/>
-      <c r="Q81" s="85"/>
+      <c r="N81" s="81"/>
+      <c r="O81" s="81"/>
+      <c r="P81" s="81"/>
+      <c r="Q81" s="81"/>
       <c r="R81" s="3">
         <f>SUM(J44:J141)</f>
         <v>369</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A82" s="38" t="str">
         <f>_xlfn.XLOOKUP(B82,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12733,7 +12737,7 @@
       <c r="D82" s="82" t="s">
         <v>301</v>
       </c>
-      <c r="E82" s="84" t="s">
+      <c r="E82" s="80" t="s">
         <v>302</v>
       </c>
       <c r="F82" s="82" t="s">
@@ -12759,20 +12763,20 @@
         <f>SUM(K82:L82)</f>
         <v>144</v>
       </c>
-      <c r="N82" s="84" t="s">
+      <c r="N82" s="80" t="s">
         <v>303</v>
       </c>
-      <c r="O82" s="84" t="s">
+      <c r="O82" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="P82" s="84" t="s">
+      <c r="P82" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q82" s="84" t="s">
+      <c r="Q82" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A83" s="38" t="str">
         <f>_xlfn.XLOOKUP(B83,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -12782,7 +12786,7 @@
       </c>
       <c r="C83" s="82"/>
       <c r="D83" s="82"/>
-      <c r="E83" s="84"/>
+      <c r="E83" s="80"/>
       <c r="F83" s="82"/>
       <c r="G83" s="82"/>
       <c r="H83" s="82"/>
@@ -12791,12 +12795,12 @@
       <c r="K83" s="82"/>
       <c r="L83" s="82"/>
       <c r="M83" s="82"/>
-      <c r="N83" s="84"/>
-      <c r="O83" s="84"/>
-      <c r="P83" s="84"/>
-      <c r="Q83" s="84"/>
-    </row>
-    <row r="84" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N83" s="80"/>
+      <c r="O83" s="80"/>
+      <c r="P83" s="80"/>
+      <c r="Q83" s="80"/>
+    </row>
+    <row r="84" spans="1:18" ht="144" x14ac:dyDescent="0.3">
       <c r="A84" s="38" t="str">
         <f>_xlfn.XLOOKUP(B84,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -12806,7 +12810,7 @@
       </c>
       <c r="C84" s="82"/>
       <c r="D84" s="82"/>
-      <c r="E84" s="84"/>
+      <c r="E84" s="80"/>
       <c r="F84" s="82"/>
       <c r="G84" s="82"/>
       <c r="H84" s="82"/>
@@ -12815,12 +12819,12 @@
       <c r="K84" s="82"/>
       <c r="L84" s="82"/>
       <c r="M84" s="82"/>
-      <c r="N84" s="84"/>
-      <c r="O84" s="84"/>
-      <c r="P84" s="84"/>
-      <c r="Q84" s="84"/>
-    </row>
-    <row r="85" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N84" s="80"/>
+      <c r="O84" s="80"/>
+      <c r="P84" s="80"/>
+      <c r="Q84" s="80"/>
+    </row>
+    <row r="85" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A85" s="48" t="str">
         <f>_xlfn.XLOOKUP(B85,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12830,7 +12834,7 @@
       </c>
       <c r="C85" s="83"/>
       <c r="D85" s="83"/>
-      <c r="E85" s="85"/>
+      <c r="E85" s="81"/>
       <c r="F85" s="83"/>
       <c r="G85" s="83"/>
       <c r="H85" s="83"/>
@@ -12839,12 +12843,12 @@
       <c r="K85" s="83"/>
       <c r="L85" s="83"/>
       <c r="M85" s="83"/>
-      <c r="N85" s="85"/>
-      <c r="O85" s="85"/>
-      <c r="P85" s="85"/>
-      <c r="Q85" s="85"/>
-    </row>
-    <row r="86" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N85" s="81"/>
+      <c r="O85" s="81"/>
+      <c r="P85" s="81"/>
+      <c r="Q85" s="81"/>
+    </row>
+    <row r="86" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A86" s="38" t="str">
         <f>_xlfn.XLOOKUP(B86,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12858,7 +12862,7 @@
       <c r="D86" s="82" t="s">
         <v>304</v>
       </c>
-      <c r="E86" s="84" t="s">
+      <c r="E86" s="80" t="s">
         <v>305</v>
       </c>
       <c r="F86" s="82" t="s">
@@ -12884,20 +12888,20 @@
         <f>SUM(K86:L86)</f>
         <v>144</v>
       </c>
-      <c r="N86" s="84" t="s">
+      <c r="N86" s="80" t="s">
         <v>306</v>
       </c>
-      <c r="O86" s="84" t="s">
+      <c r="O86" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="P86" s="84" t="s">
+      <c r="P86" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q86" s="84" t="s">
+      <c r="Q86" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A87" s="38" t="str">
         <f>_xlfn.XLOOKUP(B87,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -12907,7 +12911,7 @@
       </c>
       <c r="C87" s="82"/>
       <c r="D87" s="82"/>
-      <c r="E87" s="84"/>
+      <c r="E87" s="80"/>
       <c r="F87" s="82"/>
       <c r="G87" s="82"/>
       <c r="H87" s="82"/>
@@ -12916,12 +12920,12 @@
       <c r="K87" s="82"/>
       <c r="L87" s="82"/>
       <c r="M87" s="82"/>
-      <c r="N87" s="84"/>
-      <c r="O87" s="84"/>
-      <c r="P87" s="84"/>
-      <c r="Q87" s="84"/>
-    </row>
-    <row r="88" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N87" s="80"/>
+      <c r="O87" s="80"/>
+      <c r="P87" s="80"/>
+      <c r="Q87" s="80"/>
+    </row>
+    <row r="88" spans="1:18" ht="144" x14ac:dyDescent="0.3">
       <c r="A88" s="38" t="str">
         <f>_xlfn.XLOOKUP(B88,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -12931,7 +12935,7 @@
       </c>
       <c r="C88" s="82"/>
       <c r="D88" s="82"/>
-      <c r="E88" s="84"/>
+      <c r="E88" s="80"/>
       <c r="F88" s="82"/>
       <c r="G88" s="82"/>
       <c r="H88" s="82"/>
@@ -12940,12 +12944,12 @@
       <c r="K88" s="82"/>
       <c r="L88" s="82"/>
       <c r="M88" s="82"/>
-      <c r="N88" s="84"/>
-      <c r="O88" s="84"/>
-      <c r="P88" s="84"/>
-      <c r="Q88" s="84"/>
-    </row>
-    <row r="89" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N88" s="80"/>
+      <c r="O88" s="80"/>
+      <c r="P88" s="80"/>
+      <c r="Q88" s="80"/>
+    </row>
+    <row r="89" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A89" s="48" t="str">
         <f>_xlfn.XLOOKUP(B89,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12955,7 +12959,7 @@
       </c>
       <c r="C89" s="83"/>
       <c r="D89" s="83"/>
-      <c r="E89" s="85"/>
+      <c r="E89" s="81"/>
       <c r="F89" s="83"/>
       <c r="G89" s="83"/>
       <c r="H89" s="83"/>
@@ -12964,12 +12968,12 @@
       <c r="K89" s="83"/>
       <c r="L89" s="83"/>
       <c r="M89" s="83"/>
-      <c r="N89" s="85"/>
-      <c r="O89" s="85"/>
-      <c r="P89" s="85"/>
-      <c r="Q89" s="85"/>
-    </row>
-    <row r="90" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N89" s="81"/>
+      <c r="O89" s="81"/>
+      <c r="P89" s="81"/>
+      <c r="Q89" s="81"/>
+    </row>
+    <row r="90" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A90" s="38" t="str">
         <f>_xlfn.XLOOKUP(B90,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -12983,7 +12987,7 @@
       <c r="D90" s="82" t="s">
         <v>307</v>
       </c>
-      <c r="E90" s="84" t="s">
+      <c r="E90" s="80" t="s">
         <v>308</v>
       </c>
       <c r="F90" s="82" t="s">
@@ -13009,20 +13013,20 @@
         <f>SUM(K90:L90)</f>
         <v>144</v>
       </c>
-      <c r="N90" s="84" t="s">
+      <c r="N90" s="80" t="s">
         <v>309</v>
       </c>
-      <c r="O90" s="84" t="s">
+      <c r="O90" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="P90" s="84" t="s">
+      <c r="P90" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q90" s="84" t="s">
+      <c r="Q90" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A91" s="38" t="str">
         <f>_xlfn.XLOOKUP(B91,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -13032,7 +13036,7 @@
       </c>
       <c r="C91" s="82"/>
       <c r="D91" s="82"/>
-      <c r="E91" s="84"/>
+      <c r="E91" s="80"/>
       <c r="F91" s="82"/>
       <c r="G91" s="82"/>
       <c r="H91" s="82"/>
@@ -13041,12 +13045,12 @@
       <c r="K91" s="82"/>
       <c r="L91" s="82"/>
       <c r="M91" s="82"/>
-      <c r="N91" s="84"/>
-      <c r="O91" s="84"/>
-      <c r="P91" s="84"/>
-      <c r="Q91" s="84"/>
-    </row>
-    <row r="92" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N91" s="80"/>
+      <c r="O91" s="80"/>
+      <c r="P91" s="80"/>
+      <c r="Q91" s="80"/>
+    </row>
+    <row r="92" spans="1:18" ht="144" x14ac:dyDescent="0.3">
       <c r="A92" s="38" t="str">
         <f>_xlfn.XLOOKUP(B92,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -13056,7 +13060,7 @@
       </c>
       <c r="C92" s="82"/>
       <c r="D92" s="82"/>
-      <c r="E92" s="84"/>
+      <c r="E92" s="80"/>
       <c r="F92" s="82"/>
       <c r="G92" s="82"/>
       <c r="H92" s="82"/>
@@ -13065,12 +13069,12 @@
       <c r="K92" s="82"/>
       <c r="L92" s="82"/>
       <c r="M92" s="82"/>
-      <c r="N92" s="84"/>
-      <c r="O92" s="84"/>
-      <c r="P92" s="84"/>
-      <c r="Q92" s="84"/>
-    </row>
-    <row r="93" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N92" s="80"/>
+      <c r="O92" s="80"/>
+      <c r="P92" s="80"/>
+      <c r="Q92" s="80"/>
+    </row>
+    <row r="93" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A93" s="48" t="str">
         <f>_xlfn.XLOOKUP(B93,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13080,7 +13084,7 @@
       </c>
       <c r="C93" s="83"/>
       <c r="D93" s="83"/>
-      <c r="E93" s="85"/>
+      <c r="E93" s="81"/>
       <c r="F93" s="83"/>
       <c r="G93" s="83"/>
       <c r="H93" s="83"/>
@@ -13089,12 +13093,12 @@
       <c r="K93" s="83"/>
       <c r="L93" s="83"/>
       <c r="M93" s="83"/>
-      <c r="N93" s="85"/>
-      <c r="O93" s="85"/>
-      <c r="P93" s="85"/>
-      <c r="Q93" s="85"/>
-    </row>
-    <row r="94" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N93" s="81"/>
+      <c r="O93" s="81"/>
+      <c r="P93" s="81"/>
+      <c r="Q93" s="81"/>
+    </row>
+    <row r="94" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A94" s="38" t="str">
         <f>_xlfn.XLOOKUP(B94,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13108,7 +13112,7 @@
       <c r="D94" s="82" t="s">
         <v>310</v>
       </c>
-      <c r="E94" s="84" t="s">
+      <c r="E94" s="80" t="s">
         <v>311</v>
       </c>
       <c r="F94" s="82" t="s">
@@ -13134,20 +13138,20 @@
         <f>SUM(K94:L94)</f>
         <v>144</v>
       </c>
-      <c r="N94" s="84" t="s">
+      <c r="N94" s="80" t="s">
         <v>312</v>
       </c>
-      <c r="O94" s="84" t="s">
+      <c r="O94" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="P94" s="84" t="s">
+      <c r="P94" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q94" s="84" t="s">
+      <c r="Q94" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A95" s="38" t="str">
         <f>_xlfn.XLOOKUP(B95,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -13157,7 +13161,7 @@
       </c>
       <c r="C95" s="82"/>
       <c r="D95" s="82"/>
-      <c r="E95" s="84"/>
+      <c r="E95" s="80"/>
       <c r="F95" s="82"/>
       <c r="G95" s="82"/>
       <c r="H95" s="82"/>
@@ -13166,12 +13170,12 @@
       <c r="K95" s="82"/>
       <c r="L95" s="82"/>
       <c r="M95" s="82"/>
-      <c r="N95" s="84"/>
-      <c r="O95" s="84"/>
-      <c r="P95" s="84"/>
-      <c r="Q95" s="84"/>
-    </row>
-    <row r="96" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N95" s="80"/>
+      <c r="O95" s="80"/>
+      <c r="P95" s="80"/>
+      <c r="Q95" s="80"/>
+    </row>
+    <row r="96" spans="1:18" ht="144" x14ac:dyDescent="0.3">
       <c r="A96" s="38" t="str">
         <f>_xlfn.XLOOKUP(B96,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -13181,7 +13185,7 @@
       </c>
       <c r="C96" s="82"/>
       <c r="D96" s="82"/>
-      <c r="E96" s="84"/>
+      <c r="E96" s="80"/>
       <c r="F96" s="82"/>
       <c r="G96" s="82"/>
       <c r="H96" s="82"/>
@@ -13190,12 +13194,12 @@
       <c r="K96" s="82"/>
       <c r="L96" s="82"/>
       <c r="M96" s="82"/>
-      <c r="N96" s="84"/>
-      <c r="O96" s="84"/>
-      <c r="P96" s="84"/>
-      <c r="Q96" s="84"/>
-    </row>
-    <row r="97" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N96" s="80"/>
+      <c r="O96" s="80"/>
+      <c r="P96" s="80"/>
+      <c r="Q96" s="80"/>
+    </row>
+    <row r="97" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A97" s="48" t="str">
         <f>_xlfn.XLOOKUP(B97,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13205,7 +13209,7 @@
       </c>
       <c r="C97" s="83"/>
       <c r="D97" s="83"/>
-      <c r="E97" s="85"/>
+      <c r="E97" s="81"/>
       <c r="F97" s="83"/>
       <c r="G97" s="83"/>
       <c r="H97" s="83"/>
@@ -13214,12 +13218,12 @@
       <c r="K97" s="83"/>
       <c r="L97" s="83"/>
       <c r="M97" s="83"/>
-      <c r="N97" s="85"/>
-      <c r="O97" s="85"/>
-      <c r="P97" s="85"/>
-      <c r="Q97" s="85"/>
-    </row>
-    <row r="98" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N97" s="81"/>
+      <c r="O97" s="81"/>
+      <c r="P97" s="81"/>
+      <c r="Q97" s="81"/>
+    </row>
+    <row r="98" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A98" s="38" t="str">
         <f>_xlfn.XLOOKUP(B98,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13233,7 +13237,7 @@
       <c r="D98" s="82" t="s">
         <v>313</v>
       </c>
-      <c r="E98" s="84" t="s">
+      <c r="E98" s="80" t="s">
         <v>314</v>
       </c>
       <c r="F98" s="82" t="s">
@@ -13259,20 +13263,20 @@
         <f>SUM(K98:L98)</f>
         <v>144</v>
       </c>
-      <c r="N98" s="84" t="s">
+      <c r="N98" s="80" t="s">
         <v>315</v>
       </c>
-      <c r="O98" s="84" t="s">
+      <c r="O98" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="P98" s="84" t="s">
+      <c r="P98" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q98" s="84" t="s">
+      <c r="Q98" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A99" s="38" t="str">
         <f>_xlfn.XLOOKUP(B99,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -13282,7 +13286,7 @@
       </c>
       <c r="C99" s="82"/>
       <c r="D99" s="82"/>
-      <c r="E99" s="84"/>
+      <c r="E99" s="80"/>
       <c r="F99" s="82"/>
       <c r="G99" s="82"/>
       <c r="H99" s="82"/>
@@ -13291,12 +13295,12 @@
       <c r="K99" s="82"/>
       <c r="L99" s="82"/>
       <c r="M99" s="82"/>
-      <c r="N99" s="84"/>
-      <c r="O99" s="84"/>
-      <c r="P99" s="84"/>
-      <c r="Q99" s="84"/>
-    </row>
-    <row r="100" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N99" s="80"/>
+      <c r="O99" s="80"/>
+      <c r="P99" s="80"/>
+      <c r="Q99" s="80"/>
+    </row>
+    <row r="100" spans="1:18" ht="144" x14ac:dyDescent="0.3">
       <c r="A100" s="38" t="str">
         <f>_xlfn.XLOOKUP(B100,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -13306,7 +13310,7 @@
       </c>
       <c r="C100" s="82"/>
       <c r="D100" s="82"/>
-      <c r="E100" s="84"/>
+      <c r="E100" s="80"/>
       <c r="F100" s="82"/>
       <c r="G100" s="82"/>
       <c r="H100" s="82"/>
@@ -13315,12 +13319,12 @@
       <c r="K100" s="82"/>
       <c r="L100" s="82"/>
       <c r="M100" s="82"/>
-      <c r="N100" s="84"/>
-      <c r="O100" s="84"/>
-      <c r="P100" s="84"/>
-      <c r="Q100" s="84"/>
-    </row>
-    <row r="101" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N100" s="80"/>
+      <c r="O100" s="80"/>
+      <c r="P100" s="80"/>
+      <c r="Q100" s="80"/>
+    </row>
+    <row r="101" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A101" s="48" t="str">
         <f>_xlfn.XLOOKUP(B101,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13330,7 +13334,7 @@
       </c>
       <c r="C101" s="83"/>
       <c r="D101" s="83"/>
-      <c r="E101" s="85"/>
+      <c r="E101" s="81"/>
       <c r="F101" s="83"/>
       <c r="G101" s="83"/>
       <c r="H101" s="83"/>
@@ -13339,16 +13343,16 @@
       <c r="K101" s="83"/>
       <c r="L101" s="83"/>
       <c r="M101" s="83"/>
-      <c r="N101" s="85"/>
-      <c r="O101" s="85"/>
-      <c r="P101" s="85"/>
-      <c r="Q101" s="85"/>
+      <c r="N101" s="81"/>
+      <c r="O101" s="81"/>
+      <c r="P101" s="81"/>
+      <c r="Q101" s="81"/>
       <c r="R101" s="3">
         <f>SUM(J82:J101)</f>
         <v>15</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A102" s="38" t="str">
         <f>_xlfn.XLOOKUP(B102,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13362,7 +13366,7 @@
       <c r="D102" s="82" t="s">
         <v>316</v>
       </c>
-      <c r="E102" s="84" t="s">
+      <c r="E102" s="80" t="s">
         <v>317</v>
       </c>
       <c r="F102" s="82" t="s">
@@ -13388,20 +13392,20 @@
         <f>SUM(K102:L102)</f>
         <v>144</v>
       </c>
-      <c r="N102" s="84" t="s">
+      <c r="N102" s="80" t="s">
         <v>318</v>
       </c>
-      <c r="O102" s="84" t="s">
+      <c r="O102" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="P102" s="84" t="s">
+      <c r="P102" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q102" s="84" t="s">
+      <c r="Q102" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A103" s="38" t="str">
         <f>_xlfn.XLOOKUP(B103,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -13411,7 +13415,7 @@
       </c>
       <c r="C103" s="82"/>
       <c r="D103" s="82"/>
-      <c r="E103" s="84"/>
+      <c r="E103" s="80"/>
       <c r="F103" s="82"/>
       <c r="G103" s="82"/>
       <c r="H103" s="82"/>
@@ -13420,12 +13424,12 @@
       <c r="K103" s="82"/>
       <c r="L103" s="82"/>
       <c r="M103" s="82"/>
-      <c r="N103" s="84"/>
-      <c r="O103" s="84"/>
-      <c r="P103" s="84"/>
-      <c r="Q103" s="84"/>
-    </row>
-    <row r="104" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N103" s="80"/>
+      <c r="O103" s="80"/>
+      <c r="P103" s="80"/>
+      <c r="Q103" s="80"/>
+    </row>
+    <row r="104" spans="1:18" ht="144" x14ac:dyDescent="0.3">
       <c r="A104" s="38" t="str">
         <f>_xlfn.XLOOKUP(B104,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -13435,7 +13439,7 @@
       </c>
       <c r="C104" s="82"/>
       <c r="D104" s="82"/>
-      <c r="E104" s="84"/>
+      <c r="E104" s="80"/>
       <c r="F104" s="82"/>
       <c r="G104" s="82"/>
       <c r="H104" s="82"/>
@@ -13444,12 +13448,12 @@
       <c r="K104" s="82"/>
       <c r="L104" s="82"/>
       <c r="M104" s="82"/>
-      <c r="N104" s="84"/>
-      <c r="O104" s="84"/>
-      <c r="P104" s="84"/>
-      <c r="Q104" s="84"/>
-    </row>
-    <row r="105" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N104" s="80"/>
+      <c r="O104" s="80"/>
+      <c r="P104" s="80"/>
+      <c r="Q104" s="80"/>
+    </row>
+    <row r="105" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A105" s="48" t="str">
         <f>_xlfn.XLOOKUP(B105,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13459,7 +13463,7 @@
       </c>
       <c r="C105" s="83"/>
       <c r="D105" s="83"/>
-      <c r="E105" s="85"/>
+      <c r="E105" s="81"/>
       <c r="F105" s="83"/>
       <c r="G105" s="83"/>
       <c r="H105" s="83"/>
@@ -13468,12 +13472,12 @@
       <c r="K105" s="83"/>
       <c r="L105" s="83"/>
       <c r="M105" s="83"/>
-      <c r="N105" s="85"/>
-      <c r="O105" s="85"/>
-      <c r="P105" s="85"/>
-      <c r="Q105" s="85"/>
-    </row>
-    <row r="106" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N105" s="81"/>
+      <c r="O105" s="81"/>
+      <c r="P105" s="81"/>
+      <c r="Q105" s="81"/>
+    </row>
+    <row r="106" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A106" s="38" t="str">
         <f>_xlfn.XLOOKUP(B106,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13487,7 +13491,7 @@
       <c r="D106" s="82" t="s">
         <v>319</v>
       </c>
-      <c r="E106" s="84" t="s">
+      <c r="E106" s="80" t="s">
         <v>320</v>
       </c>
       <c r="F106" s="82" t="s">
@@ -13513,20 +13517,20 @@
         <f>SUM(K106:L106)</f>
         <v>144</v>
       </c>
-      <c r="N106" s="84" t="s">
+      <c r="N106" s="80" t="s">
         <v>321</v>
       </c>
-      <c r="O106" s="84" t="s">
+      <c r="O106" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="P106" s="84" t="s">
+      <c r="P106" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q106" s="84" t="s">
+      <c r="Q106" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A107" s="38" t="str">
         <f>_xlfn.XLOOKUP(B107,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -13536,7 +13540,7 @@
       </c>
       <c r="C107" s="82"/>
       <c r="D107" s="82"/>
-      <c r="E107" s="84"/>
+      <c r="E107" s="80"/>
       <c r="F107" s="82"/>
       <c r="G107" s="82"/>
       <c r="H107" s="82"/>
@@ -13545,12 +13549,12 @@
       <c r="K107" s="82"/>
       <c r="L107" s="82"/>
       <c r="M107" s="82"/>
-      <c r="N107" s="84"/>
-      <c r="O107" s="84"/>
-      <c r="P107" s="84"/>
-      <c r="Q107" s="84"/>
-    </row>
-    <row r="108" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N107" s="80"/>
+      <c r="O107" s="80"/>
+      <c r="P107" s="80"/>
+      <c r="Q107" s="80"/>
+    </row>
+    <row r="108" spans="1:18" ht="144" x14ac:dyDescent="0.3">
       <c r="A108" s="38" t="str">
         <f>_xlfn.XLOOKUP(B108,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -13560,7 +13564,7 @@
       </c>
       <c r="C108" s="82"/>
       <c r="D108" s="82"/>
-      <c r="E108" s="84"/>
+      <c r="E108" s="80"/>
       <c r="F108" s="82"/>
       <c r="G108" s="82"/>
       <c r="H108" s="82"/>
@@ -13569,12 +13573,12 @@
       <c r="K108" s="82"/>
       <c r="L108" s="82"/>
       <c r="M108" s="82"/>
-      <c r="N108" s="84"/>
-      <c r="O108" s="84"/>
-      <c r="P108" s="84"/>
-      <c r="Q108" s="84"/>
-    </row>
-    <row r="109" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N108" s="80"/>
+      <c r="O108" s="80"/>
+      <c r="P108" s="80"/>
+      <c r="Q108" s="80"/>
+    </row>
+    <row r="109" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A109" s="48" t="str">
         <f>_xlfn.XLOOKUP(B109,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13584,7 +13588,7 @@
       </c>
       <c r="C109" s="83"/>
       <c r="D109" s="83"/>
-      <c r="E109" s="85"/>
+      <c r="E109" s="81"/>
       <c r="F109" s="83"/>
       <c r="G109" s="83"/>
       <c r="H109" s="83"/>
@@ -13593,12 +13597,12 @@
       <c r="K109" s="83"/>
       <c r="L109" s="83"/>
       <c r="M109" s="83"/>
-      <c r="N109" s="85"/>
-      <c r="O109" s="85"/>
-      <c r="P109" s="85"/>
-      <c r="Q109" s="85"/>
-    </row>
-    <row r="110" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N109" s="81"/>
+      <c r="O109" s="81"/>
+      <c r="P109" s="81"/>
+      <c r="Q109" s="81"/>
+    </row>
+    <row r="110" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A110" s="38" t="str">
         <f>_xlfn.XLOOKUP(B110,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13612,7 +13616,7 @@
       <c r="D110" s="82" t="s">
         <v>322</v>
       </c>
-      <c r="E110" s="84" t="s">
+      <c r="E110" s="80" t="s">
         <v>323</v>
       </c>
       <c r="F110" s="82" t="s">
@@ -13638,20 +13642,20 @@
         <f>SUM(K110:L110)</f>
         <v>144</v>
       </c>
-      <c r="N110" s="84" t="s">
+      <c r="N110" s="80" t="s">
         <v>324</v>
       </c>
-      <c r="O110" s="84" t="s">
+      <c r="O110" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="P110" s="84" t="s">
+      <c r="P110" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q110" s="84" t="s">
+      <c r="Q110" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A111" s="38" t="str">
         <f>_xlfn.XLOOKUP(B111,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -13661,7 +13665,7 @@
       </c>
       <c r="C111" s="82"/>
       <c r="D111" s="82"/>
-      <c r="E111" s="84"/>
+      <c r="E111" s="80"/>
       <c r="F111" s="82"/>
       <c r="G111" s="82"/>
       <c r="H111" s="82"/>
@@ -13670,12 +13674,12 @@
       <c r="K111" s="82"/>
       <c r="L111" s="82"/>
       <c r="M111" s="82"/>
-      <c r="N111" s="84"/>
-      <c r="O111" s="84"/>
-      <c r="P111" s="84"/>
-      <c r="Q111" s="84"/>
-    </row>
-    <row r="112" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N111" s="80"/>
+      <c r="O111" s="80"/>
+      <c r="P111" s="80"/>
+      <c r="Q111" s="80"/>
+    </row>
+    <row r="112" spans="1:18" ht="144" x14ac:dyDescent="0.3">
       <c r="A112" s="38" t="str">
         <f>_xlfn.XLOOKUP(B112,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -13685,7 +13689,7 @@
       </c>
       <c r="C112" s="82"/>
       <c r="D112" s="82"/>
-      <c r="E112" s="84"/>
+      <c r="E112" s="80"/>
       <c r="F112" s="82"/>
       <c r="G112" s="82"/>
       <c r="H112" s="82"/>
@@ -13694,12 +13698,12 @@
       <c r="K112" s="82"/>
       <c r="L112" s="82"/>
       <c r="M112" s="82"/>
-      <c r="N112" s="84"/>
-      <c r="O112" s="84"/>
-      <c r="P112" s="84"/>
-      <c r="Q112" s="84"/>
-    </row>
-    <row r="113" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N112" s="80"/>
+      <c r="O112" s="80"/>
+      <c r="P112" s="80"/>
+      <c r="Q112" s="80"/>
+    </row>
+    <row r="113" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A113" s="48" t="str">
         <f>_xlfn.XLOOKUP(B113,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13709,7 +13713,7 @@
       </c>
       <c r="C113" s="83"/>
       <c r="D113" s="83"/>
-      <c r="E113" s="85"/>
+      <c r="E113" s="81"/>
       <c r="F113" s="83"/>
       <c r="G113" s="83"/>
       <c r="H113" s="83"/>
@@ -13718,12 +13722,12 @@
       <c r="K113" s="83"/>
       <c r="L113" s="83"/>
       <c r="M113" s="83"/>
-      <c r="N113" s="85"/>
-      <c r="O113" s="85"/>
-      <c r="P113" s="85"/>
-      <c r="Q113" s="85"/>
-    </row>
-    <row r="114" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N113" s="81"/>
+      <c r="O113" s="81"/>
+      <c r="P113" s="81"/>
+      <c r="Q113" s="81"/>
+    </row>
+    <row r="114" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A114" s="38" t="str">
         <f>_xlfn.XLOOKUP(B114,'[1]Paso 3 Redacción RA '!I$3:I$12,'[1]Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13737,7 +13741,7 @@
       <c r="D114" s="82" t="s">
         <v>325</v>
       </c>
-      <c r="E114" s="84" t="s">
+      <c r="E114" s="80" t="s">
         <v>326</v>
       </c>
       <c r="F114" s="82" t="s">
@@ -13763,20 +13767,20 @@
         <f>SUM(K114:L114)</f>
         <v>144</v>
       </c>
-      <c r="N114" s="84" t="s">
+      <c r="N114" s="80" t="s">
         <v>327</v>
       </c>
-      <c r="O114" s="84" t="s">
+      <c r="O114" s="80" t="s">
         <v>328</v>
       </c>
-      <c r="P114" s="84" t="s">
+      <c r="P114" s="80" t="s">
         <v>293</v>
       </c>
-      <c r="Q114" s="84" t="s">
+      <c r="Q114" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A115" s="38" t="str">
         <f>_xlfn.XLOOKUP(B115,'[1]Paso 3 Redacción RA '!I$3:I$12,'[1]Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13786,7 +13790,7 @@
       </c>
       <c r="C115" s="82"/>
       <c r="D115" s="82"/>
-      <c r="E115" s="84"/>
+      <c r="E115" s="80"/>
       <c r="F115" s="82"/>
       <c r="G115" s="82"/>
       <c r="H115" s="82"/>
@@ -13795,12 +13799,12 @@
       <c r="K115" s="82"/>
       <c r="L115" s="82"/>
       <c r="M115" s="82"/>
-      <c r="N115" s="84"/>
-      <c r="O115" s="84"/>
-      <c r="P115" s="84"/>
-      <c r="Q115" s="84"/>
-    </row>
-    <row r="116" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N115" s="80"/>
+      <c r="O115" s="80"/>
+      <c r="P115" s="80"/>
+      <c r="Q115" s="80"/>
+    </row>
+    <row r="116" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A116" s="38" t="str">
         <f>_xlfn.XLOOKUP(B116,'[1]Paso 3 Redacción RA '!I$3:I$12,'[1]Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -13810,7 +13814,7 @@
       </c>
       <c r="C116" s="82"/>
       <c r="D116" s="82"/>
-      <c r="E116" s="84"/>
+      <c r="E116" s="80"/>
       <c r="F116" s="82"/>
       <c r="G116" s="82"/>
       <c r="H116" s="82"/>
@@ -13819,12 +13823,12 @@
       <c r="K116" s="82"/>
       <c r="L116" s="82"/>
       <c r="M116" s="82"/>
-      <c r="N116" s="84"/>
-      <c r="O116" s="84"/>
-      <c r="P116" s="84"/>
-      <c r="Q116" s="84"/>
-    </row>
-    <row r="117" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N116" s="80"/>
+      <c r="O116" s="80"/>
+      <c r="P116" s="80"/>
+      <c r="Q116" s="80"/>
+    </row>
+    <row r="117" spans="1:18" ht="144" x14ac:dyDescent="0.3">
       <c r="A117" s="48" t="str">
         <f>_xlfn.XLOOKUP(B117,'[1]Paso 3 Redacción RA '!I$3:I$12,'[1]Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -13834,7 +13838,7 @@
       </c>
       <c r="C117" s="83"/>
       <c r="D117" s="83"/>
-      <c r="E117" s="85"/>
+      <c r="E117" s="81"/>
       <c r="F117" s="83"/>
       <c r="G117" s="83"/>
       <c r="H117" s="83"/>
@@ -13843,12 +13847,12 @@
       <c r="K117" s="83"/>
       <c r="L117" s="83"/>
       <c r="M117" s="83"/>
-      <c r="N117" s="85"/>
-      <c r="O117" s="85"/>
-      <c r="P117" s="85"/>
-      <c r="Q117" s="85"/>
-    </row>
-    <row r="118" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N117" s="81"/>
+      <c r="O117" s="81"/>
+      <c r="P117" s="81"/>
+      <c r="Q117" s="81"/>
+    </row>
+    <row r="118" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A118" s="38" t="str">
         <f>_xlfn.XLOOKUP(B118,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13862,7 +13866,7 @@
       <c r="D118" s="82" t="s">
         <v>329</v>
       </c>
-      <c r="E118" s="84" t="s">
+      <c r="E118" s="80" t="s">
         <v>330</v>
       </c>
       <c r="F118" s="82" t="s">
@@ -13888,20 +13892,20 @@
         <f>SUM(K118:L118)</f>
         <v>144</v>
       </c>
-      <c r="N118" s="84" t="s">
+      <c r="N118" s="80" t="s">
         <v>331</v>
       </c>
-      <c r="O118" s="84" t="s">
+      <c r="O118" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="P118" s="84" t="s">
+      <c r="P118" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q118" s="84" t="s">
+      <c r="Q118" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A119" s="38" t="str">
         <f>_xlfn.XLOOKUP(B119,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -13911,7 +13915,7 @@
       </c>
       <c r="C119" s="82"/>
       <c r="D119" s="82"/>
-      <c r="E119" s="84"/>
+      <c r="E119" s="80"/>
       <c r="F119" s="82"/>
       <c r="G119" s="82"/>
       <c r="H119" s="82"/>
@@ -13920,12 +13924,12 @@
       <c r="K119" s="82"/>
       <c r="L119" s="82"/>
       <c r="M119" s="82"/>
-      <c r="N119" s="84"/>
-      <c r="O119" s="84"/>
-      <c r="P119" s="84"/>
-      <c r="Q119" s="84"/>
-    </row>
-    <row r="120" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N119" s="80"/>
+      <c r="O119" s="80"/>
+      <c r="P119" s="80"/>
+      <c r="Q119" s="80"/>
+    </row>
+    <row r="120" spans="1:18" ht="144" x14ac:dyDescent="0.3">
       <c r="A120" s="38" t="str">
         <f>_xlfn.XLOOKUP(B120,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -13935,7 +13939,7 @@
       </c>
       <c r="C120" s="82"/>
       <c r="D120" s="82"/>
-      <c r="E120" s="84"/>
+      <c r="E120" s="80"/>
       <c r="F120" s="82"/>
       <c r="G120" s="82"/>
       <c r="H120" s="82"/>
@@ -13944,12 +13948,12 @@
       <c r="K120" s="82"/>
       <c r="L120" s="82"/>
       <c r="M120" s="82"/>
-      <c r="N120" s="84"/>
-      <c r="O120" s="84"/>
-      <c r="P120" s="84"/>
-      <c r="Q120" s="84"/>
-    </row>
-    <row r="121" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N120" s="80"/>
+      <c r="O120" s="80"/>
+      <c r="P120" s="80"/>
+      <c r="Q120" s="80"/>
+    </row>
+    <row r="121" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A121" s="48" t="str">
         <f>_xlfn.XLOOKUP(B121,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13959,7 +13963,7 @@
       </c>
       <c r="C121" s="83"/>
       <c r="D121" s="83"/>
-      <c r="E121" s="85"/>
+      <c r="E121" s="81"/>
       <c r="F121" s="83"/>
       <c r="G121" s="83"/>
       <c r="H121" s="83"/>
@@ -13968,12 +13972,12 @@
       <c r="K121" s="83"/>
       <c r="L121" s="83"/>
       <c r="M121" s="83"/>
-      <c r="N121" s="85"/>
-      <c r="O121" s="85"/>
-      <c r="P121" s="85"/>
-      <c r="Q121" s="85"/>
-    </row>
-    <row r="122" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N121" s="81"/>
+      <c r="O121" s="81"/>
+      <c r="P121" s="81"/>
+      <c r="Q121" s="81"/>
+    </row>
+    <row r="122" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A122" s="38" t="str">
         <f>_xlfn.XLOOKUP(B122,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -13987,7 +13991,7 @@
       <c r="D122" s="82" t="s">
         <v>332</v>
       </c>
-      <c r="E122" s="84" t="s">
+      <c r="E122" s="80" t="s">
         <v>333</v>
       </c>
       <c r="F122" s="82" t="s">
@@ -14013,20 +14017,20 @@
         <f>SUM(K122:L122)</f>
         <v>144</v>
       </c>
-      <c r="N122" s="84" t="s">
+      <c r="N122" s="80" t="s">
         <v>334</v>
       </c>
-      <c r="O122" s="84" t="s">
+      <c r="O122" s="80" t="s">
         <v>179</v>
       </c>
-      <c r="P122" s="84" t="s">
+      <c r="P122" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="Q122" s="84" t="s">
+      <c r="Q122" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A123" s="38" t="str">
         <f>_xlfn.XLOOKUP(B123,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -14036,7 +14040,7 @@
       </c>
       <c r="C123" s="82"/>
       <c r="D123" s="82"/>
-      <c r="E123" s="84"/>
+      <c r="E123" s="80"/>
       <c r="F123" s="82"/>
       <c r="G123" s="82"/>
       <c r="H123" s="82"/>
@@ -14045,12 +14049,12 @@
       <c r="K123" s="82"/>
       <c r="L123" s="82"/>
       <c r="M123" s="82"/>
-      <c r="N123" s="84"/>
-      <c r="O123" s="84"/>
-      <c r="P123" s="84"/>
-      <c r="Q123" s="84"/>
-    </row>
-    <row r="124" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N123" s="80"/>
+      <c r="O123" s="80"/>
+      <c r="P123" s="80"/>
+      <c r="Q123" s="80"/>
+    </row>
+    <row r="124" spans="1:18" ht="144" x14ac:dyDescent="0.3">
       <c r="A124" s="38" t="str">
         <f>_xlfn.XLOOKUP(B124,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -14060,7 +14064,7 @@
       </c>
       <c r="C124" s="82"/>
       <c r="D124" s="82"/>
-      <c r="E124" s="84"/>
+      <c r="E124" s="80"/>
       <c r="F124" s="82"/>
       <c r="G124" s="82"/>
       <c r="H124" s="82"/>
@@ -14069,12 +14073,12 @@
       <c r="K124" s="82"/>
       <c r="L124" s="82"/>
       <c r="M124" s="82"/>
-      <c r="N124" s="84"/>
-      <c r="O124" s="84"/>
-      <c r="P124" s="84"/>
-      <c r="Q124" s="84"/>
-    </row>
-    <row r="125" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N124" s="80"/>
+      <c r="O124" s="80"/>
+      <c r="P124" s="80"/>
+      <c r="Q124" s="80"/>
+    </row>
+    <row r="125" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A125" s="48" t="str">
         <f>_xlfn.XLOOKUP(B125,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -14084,7 +14088,7 @@
       </c>
       <c r="C125" s="83"/>
       <c r="D125" s="83"/>
-      <c r="E125" s="85"/>
+      <c r="E125" s="81"/>
       <c r="F125" s="83"/>
       <c r="G125" s="83"/>
       <c r="H125" s="83"/>
@@ -14093,16 +14097,16 @@
       <c r="K125" s="83"/>
       <c r="L125" s="83"/>
       <c r="M125" s="83"/>
-      <c r="N125" s="85"/>
-      <c r="O125" s="85"/>
-      <c r="P125" s="85"/>
-      <c r="Q125" s="85"/>
+      <c r="N125" s="81"/>
+      <c r="O125" s="81"/>
+      <c r="P125" s="81"/>
+      <c r="Q125" s="81"/>
       <c r="R125" s="3">
         <f>SUM(J102:J125)</f>
         <v>18</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A126" s="38" t="str">
         <f>_xlfn.XLOOKUP(B126,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -14116,7 +14120,7 @@
       <c r="D126" s="82" t="s">
         <v>335</v>
       </c>
-      <c r="E126" s="84" t="s">
+      <c r="E126" s="80" t="s">
         <v>336</v>
       </c>
       <c r="F126" s="82" t="s">
@@ -14142,20 +14146,20 @@
         <f>SUM(K126:L126)</f>
         <v>144</v>
       </c>
-      <c r="N126" s="84" t="s">
+      <c r="N126" s="80" t="s">
         <v>338</v>
       </c>
-      <c r="O126" s="84" t="s">
+      <c r="O126" s="80" t="s">
         <v>339</v>
       </c>
-      <c r="P126" s="89" t="s">
+      <c r="P126" s="84" t="s">
         <v>340</v>
       </c>
-      <c r="Q126" s="84" t="s">
+      <c r="Q126" s="80" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A127" s="38" t="str">
         <f>_xlfn.XLOOKUP(B127,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberHacer</v>
@@ -14165,7 +14169,7 @@
       </c>
       <c r="C127" s="82"/>
       <c r="D127" s="82"/>
-      <c r="E127" s="84"/>
+      <c r="E127" s="80"/>
       <c r="F127" s="82"/>
       <c r="G127" s="82"/>
       <c r="H127" s="82"/>
@@ -14174,12 +14178,12 @@
       <c r="K127" s="82"/>
       <c r="L127" s="82"/>
       <c r="M127" s="82"/>
-      <c r="N127" s="84"/>
-      <c r="O127" s="84"/>
-      <c r="P127" s="89"/>
-      <c r="Q127" s="84"/>
-    </row>
-    <row r="128" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N127" s="80"/>
+      <c r="O127" s="80"/>
+      <c r="P127" s="84"/>
+      <c r="Q127" s="80"/>
+    </row>
+    <row r="128" spans="1:18" ht="144" x14ac:dyDescent="0.3">
       <c r="A128" s="38" t="str">
         <f>_xlfn.XLOOKUP(B128,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>SaberSer</v>
@@ -14189,7 +14193,7 @@
       </c>
       <c r="C128" s="82"/>
       <c r="D128" s="82"/>
-      <c r="E128" s="84"/>
+      <c r="E128" s="80"/>
       <c r="F128" s="82"/>
       <c r="G128" s="82"/>
       <c r="H128" s="82"/>
@@ -14198,12 +14202,12 @@
       <c r="K128" s="82"/>
       <c r="L128" s="82"/>
       <c r="M128" s="82"/>
-      <c r="N128" s="84"/>
-      <c r="O128" s="84"/>
-      <c r="P128" s="89"/>
-      <c r="Q128" s="84"/>
-    </row>
-    <row r="129" spans="1:18" ht="115.5" x14ac:dyDescent="0.35">
+      <c r="N128" s="80"/>
+      <c r="O128" s="80"/>
+      <c r="P128" s="84"/>
+      <c r="Q128" s="80"/>
+    </row>
+    <row r="129" spans="1:18" ht="126" x14ac:dyDescent="0.3">
       <c r="A129" s="48" t="str">
         <f>_xlfn.XLOOKUP(B129,'Paso 3 Redacción RA '!I$3:I$12,'Paso 3 Redacción RA '!C$3:C$12,,0,1)</f>
         <v>Saber</v>
@@ -14213,7 +14217,7 @@
       </c>
       <c r="C129" s="83"/>
       <c r="D129" s="83"/>
-      <c r="E129" s="85"/>
+      <c r="E129" s="81"/>
       <c r="F129" s="83"/>
       <c r="G129" s="83"/>
       <c r="H129" s="83"/>
@@ -14222,12 +14226,12 @@
       <c r="K129" s="83"/>
       <c r="L129" s="83"/>
       <c r="M129" s="83"/>
-      <c r="N129" s="85"/>
-      <c r="O129" s="85"/>
-      <c r="P129" s="90"/>
-      <c r="Q129" s="85"/>
-    </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="N129" s="81"/>
+      <c r="O129" s="81"/>
+      <c r="P129" s="85"/>
+      <c r="Q129" s="81"/>
+    </row>
+    <row r="130" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A130" s="77"/>
       <c r="B130" s="77"/>
       <c r="C130" s="78">
@@ -14263,7 +14267,7 @@
       <c r="P130" s="77"/>
       <c r="Q130" s="79"/>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A131" s="77"/>
       <c r="B131" s="77"/>
       <c r="C131" s="78">
@@ -14299,7 +14303,7 @@
       <c r="P131" s="77"/>
       <c r="Q131" s="79"/>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A132" s="77"/>
       <c r="B132" s="77"/>
       <c r="C132" s="78">
@@ -14335,7 +14339,7 @@
       <c r="P132" s="77"/>
       <c r="Q132" s="79"/>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A133" s="77"/>
       <c r="B133" s="77"/>
       <c r="C133" s="78">
@@ -14375,7 +14379,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="32" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:18" ht="50.4" x14ac:dyDescent="0.3">
       <c r="C134" s="65" t="s">
         <v>345</v>
       </c>
@@ -14398,7 +14402,7 @@
       <c r="N134" s="38"/>
       <c r="O134" s="38"/>
     </row>
-    <row r="135" spans="1:18" ht="48" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:18" ht="50.4" x14ac:dyDescent="0.3">
       <c r="I135" s="71" t="s">
         <v>347</v>
       </c>
@@ -14414,7 +14418,7 @@
       <c r="N135" s="38"/>
       <c r="O135" s="38"/>
     </row>
-    <row r="136" spans="1:18" ht="48" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:18" ht="50.4" x14ac:dyDescent="0.3">
       <c r="I136" s="71" t="s">
         <v>348</v>
       </c>
@@ -14430,7 +14434,7 @@
       <c r="N136" s="38"/>
       <c r="O136" s="38"/>
     </row>
-    <row r="137" spans="1:18" ht="48" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:18" ht="50.4" x14ac:dyDescent="0.3">
       <c r="C137" s="55"/>
       <c r="I137" s="71" t="s">
         <v>349</v>
@@ -14446,76 +14450,76 @@
       <c r="N137" s="38"/>
       <c r="O137" s="38"/>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C138" s="55"/>
       <c r="N138" s="38"/>
       <c r="O138" s="38"/>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C139" s="55"/>
       <c r="N139" s="38"/>
       <c r="O139" s="38"/>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C140" s="55"/>
       <c r="N140" s="38"/>
       <c r="O140" s="38"/>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C141" s="55"/>
       <c r="M141" s="59"/>
       <c r="N141" s="38"/>
       <c r="O141" s="38"/>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C142" s="55"/>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C143" s="55"/>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.3">
       <c r="C144" s="55"/>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
       <c r="L145" s="55"/>
       <c r="N145" s="38"/>
       <c r="O145" s="38"/>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="L146" s="55"/>
       <c r="N146" s="38"/>
       <c r="O146" s="38"/>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C147" s="55"/>
       <c r="M147" s="59"/>
       <c r="N147" s="38"/>
       <c r="O147" s="38"/>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C148" s="55"/>
       <c r="M148" s="59"/>
       <c r="N148" s="38"/>
       <c r="O148" s="38"/>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C149" s="55"/>
       <c r="M149" s="59"/>
       <c r="N149" s="38"/>
       <c r="O149" s="38"/>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C150" s="55"/>
       <c r="M150" s="59"/>
       <c r="N150" s="38"/>
       <c r="O150" s="38"/>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151" s="50"/>
       <c r="C151" s="55"/>
       <c r="N151" s="38"/>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B152" s="38"/>
       <c r="E152" s="19"/>
       <c r="F152" s="55"/>
@@ -14529,7 +14533,7 @@
       <c r="N152" s="38"/>
       <c r="O152" s="38"/>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B153" s="38"/>
       <c r="E153" s="19"/>
       <c r="F153" s="55"/>
@@ -14543,352 +14547,884 @@
       <c r="N153" s="38"/>
       <c r="O153" s="38"/>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C154" s="55"/>
       <c r="N154" s="38"/>
       <c r="O154" s="38"/>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C155" s="55"/>
       <c r="N155" s="38"/>
       <c r="O155" s="38"/>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C156" s="55"/>
       <c r="N156" s="38"/>
       <c r="O156" s="38"/>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C157" s="55"/>
       <c r="N157" s="38"/>
       <c r="O157" s="38"/>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C158" s="55"/>
       <c r="N158" s="38"/>
       <c r="O158" s="38"/>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C159" s="55"/>
       <c r="N159" s="38"/>
       <c r="O159" s="38"/>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C160" s="55"/>
       <c r="N160" s="38"/>
       <c r="O160" s="38"/>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C161" s="55"/>
       <c r="N161" s="38"/>
       <c r="O161" s="38"/>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A162" s="50"/>
       <c r="C162" s="55"/>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A163" s="50"/>
       <c r="C163" s="55"/>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A164" s="50"/>
       <c r="C164" s="55"/>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A165" s="50"/>
       <c r="C165" s="55"/>
     </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A166" s="50"/>
       <c r="C166" s="55"/>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A167" s="50"/>
       <c r="C167" s="55"/>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A168" s="50"/>
       <c r="C168" s="55"/>
       <c r="M168" s="55"/>
       <c r="N168" s="38"/>
       <c r="O168" s="38"/>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A169" s="50"/>
       <c r="C169" s="55"/>
       <c r="M169" s="55"/>
       <c r="N169" s="38"/>
       <c r="O169" s="38"/>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A170" s="50"/>
       <c r="C170" s="55"/>
       <c r="M170" s="55"/>
       <c r="N170" s="38"/>
       <c r="O170" s="38"/>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A171" s="50"/>
       <c r="C171" s="55"/>
       <c r="M171" s="55"/>
       <c r="N171" s="38"/>
       <c r="O171" s="38"/>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A172" s="50"/>
       <c r="C172" s="55"/>
       <c r="M172" s="55"/>
       <c r="N172" s="38"/>
       <c r="O172" s="38"/>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A173" s="50"/>
       <c r="C173" s="55"/>
       <c r="M173" s="55"/>
       <c r="N173" s="38"/>
       <c r="O173" s="38"/>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A174" s="50"/>
       <c r="C174" s="55"/>
       <c r="M174" s="55"/>
       <c r="N174" s="38"/>
       <c r="O174" s="38"/>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A175" s="50"/>
       <c r="C175" s="55"/>
       <c r="M175" s="55"/>
       <c r="N175" s="38"/>
       <c r="O175" s="38"/>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A176" s="50"/>
       <c r="C176" s="55"/>
       <c r="N176" s="38"/>
       <c r="O176" s="38"/>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A177" s="50"/>
       <c r="C177" s="55"/>
       <c r="N177" s="38"/>
       <c r="O177" s="38"/>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A178" s="50"/>
       <c r="C178" s="55"/>
       <c r="N178" s="38"/>
       <c r="O178" s="38"/>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A179" s="50"/>
       <c r="C179" s="55"/>
       <c r="N179" s="38"/>
       <c r="O179" s="38"/>
     </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
       <c r="L180" s="55"/>
       <c r="N180" s="38"/>
       <c r="O180" s="38"/>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
       <c r="L181" s="55"/>
       <c r="N181" s="38"/>
       <c r="O181" s="38"/>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C182" s="55"/>
       <c r="M182" s="59"/>
       <c r="N182" s="38"/>
       <c r="O182" s="38"/>
     </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C183" s="55"/>
       <c r="M183" s="59"/>
       <c r="N183" s="38"/>
       <c r="O183" s="38"/>
     </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C184" s="55"/>
       <c r="M184" s="59"/>
       <c r="N184" s="38"/>
       <c r="O184" s="38"/>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C185" s="55"/>
       <c r="M185" s="59"/>
       <c r="N185" s="38"/>
       <c r="O185" s="38"/>
     </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A186" s="50"/>
       <c r="C186" s="55"/>
       <c r="N186" s="38"/>
       <c r="O186" s="38"/>
     </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A187" s="50"/>
       <c r="C187" s="55"/>
       <c r="N187" s="38"/>
       <c r="O187" s="38"/>
     </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A188" s="50"/>
       <c r="C188" s="55"/>
       <c r="N188" s="38"/>
       <c r="O188" s="38"/>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A189" s="50"/>
       <c r="C189" s="55"/>
       <c r="N189" s="38"/>
       <c r="O189" s="38"/>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A190" s="50"/>
       <c r="C190" s="55"/>
       <c r="N190" s="38"/>
       <c r="O190" s="38"/>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A191" s="50"/>
       <c r="C191" s="55"/>
       <c r="N191" s="38"/>
       <c r="O191" s="38"/>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A192" s="50"/>
       <c r="C192" s="55"/>
       <c r="N192" s="38"/>
       <c r="O192" s="38"/>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A193" s="50"/>
       <c r="C193" s="55"/>
       <c r="N193" s="38"/>
       <c r="O193" s="38"/>
     </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A194" s="50"/>
       <c r="C194" s="55"/>
       <c r="N194" s="38"/>
       <c r="O194" s="38"/>
     </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A195" s="50"/>
       <c r="C195" s="55"/>
       <c r="N195" s="38"/>
       <c r="O195" s="38"/>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A196" s="50"/>
       <c r="C196" s="55"/>
       <c r="N196" s="38"/>
       <c r="O196" s="38"/>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A197" s="50"/>
       <c r="C197" s="55"/>
       <c r="N197" s="38"/>
       <c r="O197" s="38"/>
     </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A198" s="50"/>
       <c r="C198" s="55"/>
       <c r="N198" s="38"/>
       <c r="O198" s="38"/>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A199" s="50"/>
       <c r="C199" s="55"/>
       <c r="N199" s="38"/>
       <c r="O199" s="38"/>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A200" s="50"/>
       <c r="C200" s="55"/>
       <c r="N200" s="38"/>
       <c r="O200" s="38"/>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A201" s="50"/>
       <c r="C201" s="55"/>
       <c r="N201" s="38"/>
       <c r="O201" s="38"/>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A202" s="50"/>
       <c r="C202" s="55"/>
       <c r="N202" s="38"/>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A203" s="50"/>
       <c r="C203" s="55"/>
       <c r="N203" s="38"/>
     </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A204" s="50"/>
       <c r="C204" s="55"/>
       <c r="N204" s="38"/>
     </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A205" s="50"/>
       <c r="C205" s="55"/>
       <c r="N205" s="38"/>
     </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A206" s="50"/>
       <c r="C206" s="55"/>
       <c r="N206" s="38"/>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A207" s="50"/>
       <c r="C207" s="55"/>
       <c r="N207" s="38"/>
     </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A208" s="50"/>
       <c r="C208" s="55"/>
       <c r="N208" s="38"/>
     </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A209" s="50"/>
       <c r="C209" s="55"/>
       <c r="N209" s="38"/>
     </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A210" s="50"/>
       <c r="C210" s="55"/>
       <c r="N210" s="38"/>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A211" s="50"/>
       <c r="C211" s="55"/>
       <c r="N211" s="38"/>
     </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A212" s="50"/>
       <c r="C212" s="55"/>
       <c r="N212" s="38"/>
     </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A213" s="50"/>
       <c r="C213" s="55"/>
       <c r="N213" s="38"/>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
       <c r="L214" s="55"/>
       <c r="N214" s="38"/>
       <c r="O214" s="38"/>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:15" x14ac:dyDescent="0.3">
       <c r="L215" s="55"/>
       <c r="N215" s="38"/>
       <c r="O215" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="556">
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="I3:I5"/>
+    <mergeCell ref="J3:J5"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="Q3:Q5"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="P9:P10"/>
+    <mergeCell ref="Q9:Q10"/>
+    <mergeCell ref="M3:M5"/>
+    <mergeCell ref="N3:N5"/>
+    <mergeCell ref="O3:O5"/>
+    <mergeCell ref="P3:P5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="H3:H5"/>
+    <mergeCell ref="N16:N18"/>
+    <mergeCell ref="O16:O18"/>
+    <mergeCell ref="P16:P18"/>
+    <mergeCell ref="Q16:Q18"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="H13:H15"/>
+    <mergeCell ref="I13:I15"/>
+    <mergeCell ref="J13:J15"/>
+    <mergeCell ref="K13:K15"/>
+    <mergeCell ref="L13:L15"/>
+    <mergeCell ref="M13:M15"/>
+    <mergeCell ref="N13:N15"/>
+    <mergeCell ref="O13:O15"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="F3:F5"/>
+    <mergeCell ref="G3:G5"/>
+    <mergeCell ref="L3:L5"/>
+    <mergeCell ref="P13:P15"/>
+    <mergeCell ref="Q13:Q15"/>
+    <mergeCell ref="L19:L21"/>
+    <mergeCell ref="M19:M21"/>
+    <mergeCell ref="N19:N21"/>
+    <mergeCell ref="O19:O21"/>
+    <mergeCell ref="P19:P21"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="F16:F18"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="F19:F21"/>
+    <mergeCell ref="G19:G21"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="I19:I21"/>
+    <mergeCell ref="J19:J21"/>
+    <mergeCell ref="K19:K21"/>
+    <mergeCell ref="G16:G18"/>
+    <mergeCell ref="H16:H18"/>
+    <mergeCell ref="I16:I18"/>
+    <mergeCell ref="M16:M18"/>
+    <mergeCell ref="J16:J18"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="L16:L18"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="Q19:Q21"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="D22:D24"/>
+    <mergeCell ref="E22:E24"/>
+    <mergeCell ref="F22:F24"/>
+    <mergeCell ref="G22:G24"/>
+    <mergeCell ref="H22:H24"/>
+    <mergeCell ref="I22:I24"/>
+    <mergeCell ref="J22:J24"/>
+    <mergeCell ref="K22:K24"/>
+    <mergeCell ref="L22:L24"/>
+    <mergeCell ref="M22:M24"/>
+    <mergeCell ref="N22:N24"/>
+    <mergeCell ref="O22:O24"/>
+    <mergeCell ref="P22:P24"/>
+    <mergeCell ref="Q22:Q24"/>
+    <mergeCell ref="M25:M26"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="O25:O26"/>
+    <mergeCell ref="P25:P26"/>
+    <mergeCell ref="Q25:Q26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="Q41:Q43"/>
+    <mergeCell ref="H41:H43"/>
+    <mergeCell ref="I41:I43"/>
+    <mergeCell ref="J41:J43"/>
+    <mergeCell ref="K41:K43"/>
+    <mergeCell ref="L41:L43"/>
+    <mergeCell ref="M41:M43"/>
+    <mergeCell ref="N41:N43"/>
+    <mergeCell ref="O41:O43"/>
+    <mergeCell ref="P41:P43"/>
+    <mergeCell ref="Q28:Q30"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="D41:D43"/>
+    <mergeCell ref="E41:E43"/>
+    <mergeCell ref="F41:F43"/>
+    <mergeCell ref="G41:G43"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="F28:F30"/>
+    <mergeCell ref="G28:G30"/>
+    <mergeCell ref="H28:H30"/>
+    <mergeCell ref="I28:I30"/>
+    <mergeCell ref="J28:J30"/>
+    <mergeCell ref="K28:K30"/>
+    <mergeCell ref="L28:L30"/>
+    <mergeCell ref="M28:M30"/>
+    <mergeCell ref="N28:N30"/>
+    <mergeCell ref="O28:O30"/>
+    <mergeCell ref="P28:P30"/>
+    <mergeCell ref="Q34:Q36"/>
+    <mergeCell ref="H34:H36"/>
+    <mergeCell ref="I34:I36"/>
+    <mergeCell ref="J34:J36"/>
+    <mergeCell ref="Q37:Q38"/>
+    <mergeCell ref="H37:H38"/>
+    <mergeCell ref="I37:I38"/>
+    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="K37:K38"/>
+    <mergeCell ref="L37:L38"/>
+    <mergeCell ref="K34:K36"/>
+    <mergeCell ref="L34:L36"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="D34:D36"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="F34:F36"/>
+    <mergeCell ref="G34:G36"/>
+    <mergeCell ref="G37:G38"/>
+    <mergeCell ref="M34:M36"/>
+    <mergeCell ref="O44:O46"/>
+    <mergeCell ref="P44:P46"/>
+    <mergeCell ref="N34:N36"/>
+    <mergeCell ref="O34:O36"/>
+    <mergeCell ref="P34:P36"/>
+    <mergeCell ref="M37:M38"/>
+    <mergeCell ref="N37:N38"/>
+    <mergeCell ref="O37:O38"/>
+    <mergeCell ref="P37:P38"/>
+    <mergeCell ref="Q47:Q49"/>
+    <mergeCell ref="H47:H49"/>
+    <mergeCell ref="I47:I49"/>
+    <mergeCell ref="J47:J49"/>
+    <mergeCell ref="K47:K49"/>
+    <mergeCell ref="L47:L49"/>
+    <mergeCell ref="C44:C46"/>
+    <mergeCell ref="D44:D46"/>
+    <mergeCell ref="E44:E46"/>
+    <mergeCell ref="F44:F46"/>
+    <mergeCell ref="G44:G46"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="D47:D49"/>
+    <mergeCell ref="E47:E49"/>
+    <mergeCell ref="F47:F49"/>
+    <mergeCell ref="G47:G49"/>
+    <mergeCell ref="Q44:Q46"/>
+    <mergeCell ref="H44:H46"/>
+    <mergeCell ref="I44:I46"/>
+    <mergeCell ref="J44:J46"/>
+    <mergeCell ref="K44:K46"/>
+    <mergeCell ref="L44:L46"/>
+    <mergeCell ref="M44:M46"/>
+    <mergeCell ref="N44:N46"/>
+    <mergeCell ref="Q31:Q33"/>
+    <mergeCell ref="H31:H33"/>
+    <mergeCell ref="I31:I33"/>
+    <mergeCell ref="J31:J33"/>
+    <mergeCell ref="K31:K33"/>
+    <mergeCell ref="L31:L33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="F31:F33"/>
+    <mergeCell ref="G31:G33"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="F53:F54"/>
+    <mergeCell ref="G53:G54"/>
+    <mergeCell ref="M31:M33"/>
+    <mergeCell ref="N31:N33"/>
+    <mergeCell ref="O31:O33"/>
+    <mergeCell ref="P31:P33"/>
+    <mergeCell ref="M53:M54"/>
+    <mergeCell ref="N53:N54"/>
+    <mergeCell ref="O53:O54"/>
+    <mergeCell ref="P53:P54"/>
+    <mergeCell ref="N50:N52"/>
+    <mergeCell ref="O50:O52"/>
+    <mergeCell ref="P50:P52"/>
+    <mergeCell ref="M47:M49"/>
+    <mergeCell ref="N47:N49"/>
+    <mergeCell ref="O47:O49"/>
+    <mergeCell ref="P47:P49"/>
+    <mergeCell ref="C37:C38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="E37:E38"/>
+    <mergeCell ref="F37:F38"/>
+    <mergeCell ref="Q53:Q54"/>
+    <mergeCell ref="H53:H54"/>
+    <mergeCell ref="I53:I54"/>
+    <mergeCell ref="J53:J54"/>
+    <mergeCell ref="K53:K54"/>
+    <mergeCell ref="L53:L54"/>
+    <mergeCell ref="Q79:Q81"/>
+    <mergeCell ref="H79:H81"/>
+    <mergeCell ref="I79:I81"/>
+    <mergeCell ref="J79:J81"/>
+    <mergeCell ref="K79:K81"/>
+    <mergeCell ref="L79:L81"/>
+    <mergeCell ref="M79:M81"/>
+    <mergeCell ref="N79:N81"/>
+    <mergeCell ref="O79:O81"/>
+    <mergeCell ref="P79:P81"/>
+    <mergeCell ref="M56:M59"/>
+    <mergeCell ref="N56:N59"/>
+    <mergeCell ref="O56:O59"/>
+    <mergeCell ref="P56:P59"/>
+    <mergeCell ref="Q56:Q59"/>
+    <mergeCell ref="H56:H59"/>
+    <mergeCell ref="I56:I59"/>
+    <mergeCell ref="J56:J59"/>
+    <mergeCell ref="C79:C81"/>
+    <mergeCell ref="D79:D81"/>
+    <mergeCell ref="E79:E81"/>
+    <mergeCell ref="F79:F81"/>
+    <mergeCell ref="G79:G81"/>
+    <mergeCell ref="C56:C59"/>
+    <mergeCell ref="D56:D59"/>
+    <mergeCell ref="E56:E59"/>
+    <mergeCell ref="F56:F59"/>
+    <mergeCell ref="G56:G59"/>
+    <mergeCell ref="C64:C67"/>
+    <mergeCell ref="D64:D67"/>
+    <mergeCell ref="E64:E67"/>
+    <mergeCell ref="F64:F67"/>
+    <mergeCell ref="G64:G67"/>
+    <mergeCell ref="K56:K59"/>
+    <mergeCell ref="L56:L59"/>
+    <mergeCell ref="Q60:Q63"/>
+    <mergeCell ref="H60:H63"/>
+    <mergeCell ref="I60:I63"/>
+    <mergeCell ref="J60:J63"/>
+    <mergeCell ref="K60:K63"/>
+    <mergeCell ref="L60:L63"/>
+    <mergeCell ref="C60:C63"/>
+    <mergeCell ref="D60:D63"/>
+    <mergeCell ref="E60:E63"/>
+    <mergeCell ref="F60:F63"/>
+    <mergeCell ref="G60:G63"/>
+    <mergeCell ref="M60:M63"/>
+    <mergeCell ref="N60:N63"/>
+    <mergeCell ref="O60:O63"/>
+    <mergeCell ref="P60:P63"/>
+    <mergeCell ref="M64:M67"/>
+    <mergeCell ref="N64:N67"/>
+    <mergeCell ref="O64:O67"/>
+    <mergeCell ref="P64:P67"/>
+    <mergeCell ref="Q64:Q67"/>
+    <mergeCell ref="H64:H67"/>
+    <mergeCell ref="I64:I67"/>
+    <mergeCell ref="J64:J67"/>
+    <mergeCell ref="K64:K67"/>
+    <mergeCell ref="L64:L67"/>
+    <mergeCell ref="Q68:Q70"/>
+    <mergeCell ref="H68:H70"/>
+    <mergeCell ref="I68:I70"/>
+    <mergeCell ref="J68:J70"/>
+    <mergeCell ref="K68:K70"/>
+    <mergeCell ref="L68:L70"/>
+    <mergeCell ref="M68:M70"/>
+    <mergeCell ref="N68:N70"/>
+    <mergeCell ref="O68:O70"/>
+    <mergeCell ref="P68:P70"/>
+    <mergeCell ref="K71:K73"/>
+    <mergeCell ref="L71:L73"/>
+    <mergeCell ref="C68:C70"/>
+    <mergeCell ref="D68:D70"/>
+    <mergeCell ref="E68:E70"/>
+    <mergeCell ref="F68:F70"/>
+    <mergeCell ref="G68:G70"/>
+    <mergeCell ref="C71:C73"/>
+    <mergeCell ref="D71:D73"/>
+    <mergeCell ref="E71:E73"/>
+    <mergeCell ref="F71:F73"/>
+    <mergeCell ref="G71:G73"/>
+    <mergeCell ref="H76:H78"/>
+    <mergeCell ref="I76:I78"/>
+    <mergeCell ref="J76:J78"/>
+    <mergeCell ref="K76:K78"/>
+    <mergeCell ref="L76:L78"/>
+    <mergeCell ref="C76:C78"/>
+    <mergeCell ref="D76:D78"/>
+    <mergeCell ref="E76:E78"/>
+    <mergeCell ref="F76:F78"/>
+    <mergeCell ref="G76:G78"/>
+    <mergeCell ref="N76:N78"/>
+    <mergeCell ref="O76:O78"/>
+    <mergeCell ref="P76:P78"/>
+    <mergeCell ref="M82:M85"/>
+    <mergeCell ref="N82:N85"/>
+    <mergeCell ref="O82:O85"/>
+    <mergeCell ref="P82:P85"/>
+    <mergeCell ref="Q76:Q78"/>
+    <mergeCell ref="Q82:Q85"/>
+    <mergeCell ref="N86:N89"/>
+    <mergeCell ref="O86:O89"/>
+    <mergeCell ref="P86:P89"/>
+    <mergeCell ref="C82:C85"/>
+    <mergeCell ref="D82:D85"/>
+    <mergeCell ref="E82:E85"/>
+    <mergeCell ref="F82:F85"/>
+    <mergeCell ref="G82:G85"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="D86:D89"/>
+    <mergeCell ref="E86:E89"/>
+    <mergeCell ref="F86:F89"/>
+    <mergeCell ref="G86:G89"/>
+    <mergeCell ref="C90:C93"/>
+    <mergeCell ref="D90:D93"/>
+    <mergeCell ref="E90:E93"/>
+    <mergeCell ref="F90:F93"/>
+    <mergeCell ref="G90:G93"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="F6:F8"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="M90:M93"/>
+    <mergeCell ref="H82:H85"/>
+    <mergeCell ref="I82:I85"/>
+    <mergeCell ref="J82:J85"/>
+    <mergeCell ref="K82:K85"/>
+    <mergeCell ref="L82:L85"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="F50:F52"/>
+    <mergeCell ref="G50:G52"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="L86:L89"/>
+    <mergeCell ref="M86:M89"/>
+    <mergeCell ref="M76:M78"/>
+    <mergeCell ref="N90:N93"/>
+    <mergeCell ref="O90:O93"/>
+    <mergeCell ref="P90:P93"/>
+    <mergeCell ref="Q90:Q93"/>
+    <mergeCell ref="H90:H93"/>
+    <mergeCell ref="I90:I93"/>
+    <mergeCell ref="J90:J93"/>
+    <mergeCell ref="K90:K93"/>
+    <mergeCell ref="L90:L93"/>
+    <mergeCell ref="Q86:Q89"/>
+    <mergeCell ref="H86:H89"/>
+    <mergeCell ref="I86:I89"/>
+    <mergeCell ref="J86:J89"/>
+    <mergeCell ref="K86:K89"/>
+    <mergeCell ref="Q114:Q117"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="H50:H52"/>
+    <mergeCell ref="I50:I52"/>
+    <mergeCell ref="J50:J52"/>
+    <mergeCell ref="K50:K52"/>
+    <mergeCell ref="L50:L52"/>
+    <mergeCell ref="M50:M52"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="H6:H8"/>
+    <mergeCell ref="I6:I8"/>
+    <mergeCell ref="J6:J8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="I98:I101"/>
+    <mergeCell ref="J98:J101"/>
+    <mergeCell ref="K98:K101"/>
+    <mergeCell ref="L98:L101"/>
+    <mergeCell ref="M98:M101"/>
+    <mergeCell ref="N98:N101"/>
+    <mergeCell ref="O98:O101"/>
+    <mergeCell ref="P98:P101"/>
+    <mergeCell ref="N114:N117"/>
+    <mergeCell ref="O114:O117"/>
+    <mergeCell ref="P114:P117"/>
+    <mergeCell ref="P110:P113"/>
+    <mergeCell ref="C98:C101"/>
+    <mergeCell ref="D98:D101"/>
+    <mergeCell ref="E98:E101"/>
+    <mergeCell ref="F98:F101"/>
+    <mergeCell ref="G98:G101"/>
+    <mergeCell ref="C102:C105"/>
+    <mergeCell ref="D102:D105"/>
+    <mergeCell ref="E102:E105"/>
+    <mergeCell ref="F102:F105"/>
+    <mergeCell ref="G102:G105"/>
+    <mergeCell ref="P94:P97"/>
+    <mergeCell ref="M106:M109"/>
+    <mergeCell ref="N106:N109"/>
+    <mergeCell ref="O106:O109"/>
+    <mergeCell ref="P106:P109"/>
+    <mergeCell ref="Q94:Q97"/>
+    <mergeCell ref="H94:H97"/>
+    <mergeCell ref="I94:I97"/>
+    <mergeCell ref="J94:J97"/>
+    <mergeCell ref="K94:K97"/>
+    <mergeCell ref="L94:L97"/>
+    <mergeCell ref="Q106:Q109"/>
+    <mergeCell ref="M102:M105"/>
+    <mergeCell ref="N102:N105"/>
+    <mergeCell ref="O102:O105"/>
+    <mergeCell ref="P102:P105"/>
+    <mergeCell ref="Q102:Q105"/>
+    <mergeCell ref="H102:H105"/>
+    <mergeCell ref="I102:I105"/>
+    <mergeCell ref="J102:J105"/>
+    <mergeCell ref="K102:K105"/>
+    <mergeCell ref="L102:L105"/>
+    <mergeCell ref="Q98:Q101"/>
+    <mergeCell ref="H98:H101"/>
+    <mergeCell ref="H126:H129"/>
+    <mergeCell ref="C106:C109"/>
+    <mergeCell ref="D106:D109"/>
+    <mergeCell ref="E106:E109"/>
+    <mergeCell ref="F106:F109"/>
+    <mergeCell ref="G106:G109"/>
+    <mergeCell ref="M94:M97"/>
+    <mergeCell ref="N94:N97"/>
+    <mergeCell ref="O94:O97"/>
+    <mergeCell ref="C94:C97"/>
+    <mergeCell ref="D94:D97"/>
+    <mergeCell ref="E94:E97"/>
+    <mergeCell ref="F94:F97"/>
+    <mergeCell ref="G94:G97"/>
+    <mergeCell ref="H106:H109"/>
+    <mergeCell ref="I106:I109"/>
+    <mergeCell ref="J106:J109"/>
+    <mergeCell ref="K106:K109"/>
+    <mergeCell ref="L106:L109"/>
+    <mergeCell ref="M110:M113"/>
+    <mergeCell ref="N110:N113"/>
+    <mergeCell ref="O110:O113"/>
+    <mergeCell ref="C126:C129"/>
+    <mergeCell ref="D126:D129"/>
+    <mergeCell ref="H110:H113"/>
+    <mergeCell ref="I110:I113"/>
+    <mergeCell ref="J110:J113"/>
+    <mergeCell ref="K110:K113"/>
+    <mergeCell ref="L110:L113"/>
+    <mergeCell ref="Q110:Q113"/>
+    <mergeCell ref="C122:C125"/>
+    <mergeCell ref="D122:D125"/>
+    <mergeCell ref="E122:E125"/>
+    <mergeCell ref="F122:F125"/>
+    <mergeCell ref="G122:G125"/>
+    <mergeCell ref="G110:G113"/>
+    <mergeCell ref="H118:H121"/>
+    <mergeCell ref="H122:H125"/>
+    <mergeCell ref="K122:K125"/>
+    <mergeCell ref="M122:M125"/>
+    <mergeCell ref="N122:N125"/>
+    <mergeCell ref="H114:H117"/>
+    <mergeCell ref="I114:I117"/>
+    <mergeCell ref="J114:J117"/>
+    <mergeCell ref="K114:K117"/>
+    <mergeCell ref="L114:L117"/>
+    <mergeCell ref="M114:M117"/>
+    <mergeCell ref="E126:E129"/>
+    <mergeCell ref="F126:F129"/>
+    <mergeCell ref="G126:G129"/>
+    <mergeCell ref="C118:C121"/>
+    <mergeCell ref="D118:D121"/>
+    <mergeCell ref="E118:E121"/>
+    <mergeCell ref="F118:F121"/>
+    <mergeCell ref="G118:G121"/>
+    <mergeCell ref="C110:C113"/>
+    <mergeCell ref="D110:D113"/>
+    <mergeCell ref="E110:E113"/>
+    <mergeCell ref="F110:F113"/>
+    <mergeCell ref="C114:C117"/>
+    <mergeCell ref="D114:D117"/>
+    <mergeCell ref="E114:E117"/>
+    <mergeCell ref="F114:F117"/>
+    <mergeCell ref="G114:G117"/>
+    <mergeCell ref="I126:I129"/>
+    <mergeCell ref="J126:J129"/>
+    <mergeCell ref="K126:K129"/>
+    <mergeCell ref="L126:L129"/>
+    <mergeCell ref="Q122:Q125"/>
+    <mergeCell ref="M118:M121"/>
+    <mergeCell ref="N118:N121"/>
+    <mergeCell ref="O118:O121"/>
+    <mergeCell ref="P118:P121"/>
+    <mergeCell ref="Q118:Q121"/>
+    <mergeCell ref="O122:O125"/>
+    <mergeCell ref="M126:M129"/>
+    <mergeCell ref="N126:N129"/>
+    <mergeCell ref="O126:O129"/>
+    <mergeCell ref="L122:L125"/>
+    <mergeCell ref="P126:P129"/>
+    <mergeCell ref="Q126:Q129"/>
+    <mergeCell ref="I118:I121"/>
+    <mergeCell ref="J118:J121"/>
+    <mergeCell ref="K118:K121"/>
+    <mergeCell ref="L118:L121"/>
+    <mergeCell ref="P122:P125"/>
+    <mergeCell ref="I122:I125"/>
+    <mergeCell ref="J122:J125"/>
     <mergeCell ref="Q50:Q52"/>
     <mergeCell ref="C74:C75"/>
     <mergeCell ref="D74:D75"/>
@@ -14913,538 +15449,6 @@
     <mergeCell ref="H71:H73"/>
     <mergeCell ref="I71:I73"/>
     <mergeCell ref="J71:J73"/>
-    <mergeCell ref="I126:I129"/>
-    <mergeCell ref="J126:J129"/>
-    <mergeCell ref="K126:K129"/>
-    <mergeCell ref="L126:L129"/>
-    <mergeCell ref="Q122:Q125"/>
-    <mergeCell ref="M118:M121"/>
-    <mergeCell ref="N118:N121"/>
-    <mergeCell ref="O118:O121"/>
-    <mergeCell ref="P118:P121"/>
-    <mergeCell ref="Q118:Q121"/>
-    <mergeCell ref="O122:O125"/>
-    <mergeCell ref="M126:M129"/>
-    <mergeCell ref="N126:N129"/>
-    <mergeCell ref="O126:O129"/>
-    <mergeCell ref="L122:L125"/>
-    <mergeCell ref="P126:P129"/>
-    <mergeCell ref="Q126:Q129"/>
-    <mergeCell ref="I118:I121"/>
-    <mergeCell ref="J118:J121"/>
-    <mergeCell ref="K118:K121"/>
-    <mergeCell ref="L118:L121"/>
-    <mergeCell ref="P122:P125"/>
-    <mergeCell ref="I122:I125"/>
-    <mergeCell ref="J122:J125"/>
-    <mergeCell ref="E126:E129"/>
-    <mergeCell ref="F126:F129"/>
-    <mergeCell ref="G126:G129"/>
-    <mergeCell ref="C118:C121"/>
-    <mergeCell ref="D118:D121"/>
-    <mergeCell ref="E118:E121"/>
-    <mergeCell ref="F118:F121"/>
-    <mergeCell ref="G118:G121"/>
-    <mergeCell ref="C110:C113"/>
-    <mergeCell ref="D110:D113"/>
-    <mergeCell ref="E110:E113"/>
-    <mergeCell ref="F110:F113"/>
-    <mergeCell ref="C114:C117"/>
-    <mergeCell ref="D114:D117"/>
-    <mergeCell ref="E114:E117"/>
-    <mergeCell ref="F114:F117"/>
-    <mergeCell ref="G114:G117"/>
-    <mergeCell ref="H110:H113"/>
-    <mergeCell ref="I110:I113"/>
-    <mergeCell ref="J110:J113"/>
-    <mergeCell ref="K110:K113"/>
-    <mergeCell ref="L110:L113"/>
-    <mergeCell ref="Q110:Q113"/>
-    <mergeCell ref="C122:C125"/>
-    <mergeCell ref="D122:D125"/>
-    <mergeCell ref="E122:E125"/>
-    <mergeCell ref="F122:F125"/>
-    <mergeCell ref="G122:G125"/>
-    <mergeCell ref="G110:G113"/>
-    <mergeCell ref="H118:H121"/>
-    <mergeCell ref="H122:H125"/>
-    <mergeCell ref="K122:K125"/>
-    <mergeCell ref="M122:M125"/>
-    <mergeCell ref="N122:N125"/>
-    <mergeCell ref="H114:H117"/>
-    <mergeCell ref="I114:I117"/>
-    <mergeCell ref="J114:J117"/>
-    <mergeCell ref="K114:K117"/>
-    <mergeCell ref="L114:L117"/>
-    <mergeCell ref="M114:M117"/>
-    <mergeCell ref="H126:H129"/>
-    <mergeCell ref="C106:C109"/>
-    <mergeCell ref="D106:D109"/>
-    <mergeCell ref="E106:E109"/>
-    <mergeCell ref="F106:F109"/>
-    <mergeCell ref="G106:G109"/>
-    <mergeCell ref="M94:M97"/>
-    <mergeCell ref="N94:N97"/>
-    <mergeCell ref="O94:O97"/>
-    <mergeCell ref="C94:C97"/>
-    <mergeCell ref="D94:D97"/>
-    <mergeCell ref="E94:E97"/>
-    <mergeCell ref="F94:F97"/>
-    <mergeCell ref="G94:G97"/>
-    <mergeCell ref="H106:H109"/>
-    <mergeCell ref="I106:I109"/>
-    <mergeCell ref="J106:J109"/>
-    <mergeCell ref="K106:K109"/>
-    <mergeCell ref="L106:L109"/>
-    <mergeCell ref="M110:M113"/>
-    <mergeCell ref="N110:N113"/>
-    <mergeCell ref="O110:O113"/>
-    <mergeCell ref="C126:C129"/>
-    <mergeCell ref="D126:D129"/>
-    <mergeCell ref="P94:P97"/>
-    <mergeCell ref="M106:M109"/>
-    <mergeCell ref="N106:N109"/>
-    <mergeCell ref="O106:O109"/>
-    <mergeCell ref="P106:P109"/>
-    <mergeCell ref="Q94:Q97"/>
-    <mergeCell ref="H94:H97"/>
-    <mergeCell ref="I94:I97"/>
-    <mergeCell ref="J94:J97"/>
-    <mergeCell ref="K94:K97"/>
-    <mergeCell ref="L94:L97"/>
-    <mergeCell ref="Q106:Q109"/>
-    <mergeCell ref="M102:M105"/>
-    <mergeCell ref="N102:N105"/>
-    <mergeCell ref="O102:O105"/>
-    <mergeCell ref="P102:P105"/>
-    <mergeCell ref="Q102:Q105"/>
-    <mergeCell ref="H102:H105"/>
-    <mergeCell ref="I102:I105"/>
-    <mergeCell ref="J102:J105"/>
-    <mergeCell ref="K102:K105"/>
-    <mergeCell ref="L102:L105"/>
-    <mergeCell ref="Q98:Q101"/>
-    <mergeCell ref="H98:H101"/>
-    <mergeCell ref="C98:C101"/>
-    <mergeCell ref="D98:D101"/>
-    <mergeCell ref="E98:E101"/>
-    <mergeCell ref="F98:F101"/>
-    <mergeCell ref="G98:G101"/>
-    <mergeCell ref="C102:C105"/>
-    <mergeCell ref="D102:D105"/>
-    <mergeCell ref="E102:E105"/>
-    <mergeCell ref="F102:F105"/>
-    <mergeCell ref="G102:G105"/>
-    <mergeCell ref="K98:K101"/>
-    <mergeCell ref="L98:L101"/>
-    <mergeCell ref="M98:M101"/>
-    <mergeCell ref="N98:N101"/>
-    <mergeCell ref="O98:O101"/>
-    <mergeCell ref="P98:P101"/>
-    <mergeCell ref="N114:N117"/>
-    <mergeCell ref="O114:O117"/>
-    <mergeCell ref="P114:P117"/>
-    <mergeCell ref="P110:P113"/>
-    <mergeCell ref="Q86:Q89"/>
-    <mergeCell ref="H86:H89"/>
-    <mergeCell ref="I86:I89"/>
-    <mergeCell ref="J86:J89"/>
-    <mergeCell ref="K86:K89"/>
-    <mergeCell ref="Q114:Q117"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="P6:P8"/>
-    <mergeCell ref="H50:H52"/>
-    <mergeCell ref="I50:I52"/>
-    <mergeCell ref="J50:J52"/>
-    <mergeCell ref="K50:K52"/>
-    <mergeCell ref="L50:L52"/>
-    <mergeCell ref="M50:M52"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="H6:H8"/>
-    <mergeCell ref="I6:I8"/>
-    <mergeCell ref="J6:J8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="I98:I101"/>
-    <mergeCell ref="J98:J101"/>
-    <mergeCell ref="N90:N93"/>
-    <mergeCell ref="O90:O93"/>
-    <mergeCell ref="P90:P93"/>
-    <mergeCell ref="Q90:Q93"/>
-    <mergeCell ref="H90:H93"/>
-    <mergeCell ref="I90:I93"/>
-    <mergeCell ref="J90:J93"/>
-    <mergeCell ref="K90:K93"/>
-    <mergeCell ref="L90:L93"/>
-    <mergeCell ref="C90:C93"/>
-    <mergeCell ref="D90:D93"/>
-    <mergeCell ref="E90:E93"/>
-    <mergeCell ref="F90:F93"/>
-    <mergeCell ref="G90:G93"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="F6:F8"/>
-    <mergeCell ref="G6:G8"/>
-    <mergeCell ref="M90:M93"/>
-    <mergeCell ref="H82:H85"/>
-    <mergeCell ref="I82:I85"/>
-    <mergeCell ref="J82:J85"/>
-    <mergeCell ref="K82:K85"/>
-    <mergeCell ref="L82:L85"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="D50:D52"/>
-    <mergeCell ref="E50:E52"/>
-    <mergeCell ref="F50:F52"/>
-    <mergeCell ref="G50:G52"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="L86:L89"/>
-    <mergeCell ref="M86:M89"/>
-    <mergeCell ref="M76:M78"/>
-    <mergeCell ref="N86:N89"/>
-    <mergeCell ref="O86:O89"/>
-    <mergeCell ref="P86:P89"/>
-    <mergeCell ref="C82:C85"/>
-    <mergeCell ref="D82:D85"/>
-    <mergeCell ref="E82:E85"/>
-    <mergeCell ref="F82:F85"/>
-    <mergeCell ref="G82:G85"/>
-    <mergeCell ref="C86:C89"/>
-    <mergeCell ref="D86:D89"/>
-    <mergeCell ref="E86:E89"/>
-    <mergeCell ref="F86:F89"/>
-    <mergeCell ref="G86:G89"/>
-    <mergeCell ref="N76:N78"/>
-    <mergeCell ref="O76:O78"/>
-    <mergeCell ref="P76:P78"/>
-    <mergeCell ref="M82:M85"/>
-    <mergeCell ref="N82:N85"/>
-    <mergeCell ref="O82:O85"/>
-    <mergeCell ref="P82:P85"/>
-    <mergeCell ref="Q76:Q78"/>
-    <mergeCell ref="Q82:Q85"/>
-    <mergeCell ref="H76:H78"/>
-    <mergeCell ref="I76:I78"/>
-    <mergeCell ref="J76:J78"/>
-    <mergeCell ref="K76:K78"/>
-    <mergeCell ref="L76:L78"/>
-    <mergeCell ref="C76:C78"/>
-    <mergeCell ref="D76:D78"/>
-    <mergeCell ref="E76:E78"/>
-    <mergeCell ref="F76:F78"/>
-    <mergeCell ref="G76:G78"/>
-    <mergeCell ref="K71:K73"/>
-    <mergeCell ref="L71:L73"/>
-    <mergeCell ref="C68:C70"/>
-    <mergeCell ref="D68:D70"/>
-    <mergeCell ref="E68:E70"/>
-    <mergeCell ref="F68:F70"/>
-    <mergeCell ref="G68:G70"/>
-    <mergeCell ref="C71:C73"/>
-    <mergeCell ref="D71:D73"/>
-    <mergeCell ref="E71:E73"/>
-    <mergeCell ref="F71:F73"/>
-    <mergeCell ref="G71:G73"/>
-    <mergeCell ref="Q68:Q70"/>
-    <mergeCell ref="H68:H70"/>
-    <mergeCell ref="I68:I70"/>
-    <mergeCell ref="J68:J70"/>
-    <mergeCell ref="K68:K70"/>
-    <mergeCell ref="L68:L70"/>
-    <mergeCell ref="M68:M70"/>
-    <mergeCell ref="N68:N70"/>
-    <mergeCell ref="O68:O70"/>
-    <mergeCell ref="P68:P70"/>
-    <mergeCell ref="M64:M67"/>
-    <mergeCell ref="N64:N67"/>
-    <mergeCell ref="O64:O67"/>
-    <mergeCell ref="P64:P67"/>
-    <mergeCell ref="Q64:Q67"/>
-    <mergeCell ref="H64:H67"/>
-    <mergeCell ref="I64:I67"/>
-    <mergeCell ref="J64:J67"/>
-    <mergeCell ref="K64:K67"/>
-    <mergeCell ref="L64:L67"/>
-    <mergeCell ref="K56:K59"/>
-    <mergeCell ref="L56:L59"/>
-    <mergeCell ref="Q60:Q63"/>
-    <mergeCell ref="H60:H63"/>
-    <mergeCell ref="I60:I63"/>
-    <mergeCell ref="J60:J63"/>
-    <mergeCell ref="K60:K63"/>
-    <mergeCell ref="L60:L63"/>
-    <mergeCell ref="C60:C63"/>
-    <mergeCell ref="D60:D63"/>
-    <mergeCell ref="E60:E63"/>
-    <mergeCell ref="F60:F63"/>
-    <mergeCell ref="G60:G63"/>
-    <mergeCell ref="M60:M63"/>
-    <mergeCell ref="N60:N63"/>
-    <mergeCell ref="O60:O63"/>
-    <mergeCell ref="P60:P63"/>
-    <mergeCell ref="C79:C81"/>
-    <mergeCell ref="D79:D81"/>
-    <mergeCell ref="E79:E81"/>
-    <mergeCell ref="F79:F81"/>
-    <mergeCell ref="G79:G81"/>
-    <mergeCell ref="C56:C59"/>
-    <mergeCell ref="D56:D59"/>
-    <mergeCell ref="E56:E59"/>
-    <mergeCell ref="F56:F59"/>
-    <mergeCell ref="G56:G59"/>
-    <mergeCell ref="C64:C67"/>
-    <mergeCell ref="D64:D67"/>
-    <mergeCell ref="E64:E67"/>
-    <mergeCell ref="F64:F67"/>
-    <mergeCell ref="G64:G67"/>
-    <mergeCell ref="Q53:Q54"/>
-    <mergeCell ref="H53:H54"/>
-    <mergeCell ref="I53:I54"/>
-    <mergeCell ref="J53:J54"/>
-    <mergeCell ref="K53:K54"/>
-    <mergeCell ref="L53:L54"/>
-    <mergeCell ref="Q79:Q81"/>
-    <mergeCell ref="H79:H81"/>
-    <mergeCell ref="I79:I81"/>
-    <mergeCell ref="J79:J81"/>
-    <mergeCell ref="K79:K81"/>
-    <mergeCell ref="L79:L81"/>
-    <mergeCell ref="M79:M81"/>
-    <mergeCell ref="N79:N81"/>
-    <mergeCell ref="O79:O81"/>
-    <mergeCell ref="P79:P81"/>
-    <mergeCell ref="M56:M59"/>
-    <mergeCell ref="N56:N59"/>
-    <mergeCell ref="O56:O59"/>
-    <mergeCell ref="P56:P59"/>
-    <mergeCell ref="Q56:Q59"/>
-    <mergeCell ref="H56:H59"/>
-    <mergeCell ref="I56:I59"/>
-    <mergeCell ref="J56:J59"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="E53:E54"/>
-    <mergeCell ref="F53:F54"/>
-    <mergeCell ref="G53:G54"/>
-    <mergeCell ref="M31:M33"/>
-    <mergeCell ref="N31:N33"/>
-    <mergeCell ref="O31:O33"/>
-    <mergeCell ref="P31:P33"/>
-    <mergeCell ref="M53:M54"/>
-    <mergeCell ref="N53:N54"/>
-    <mergeCell ref="O53:O54"/>
-    <mergeCell ref="P53:P54"/>
-    <mergeCell ref="N50:N52"/>
-    <mergeCell ref="O50:O52"/>
-    <mergeCell ref="P50:P52"/>
-    <mergeCell ref="M47:M49"/>
-    <mergeCell ref="N47:N49"/>
-    <mergeCell ref="O47:O49"/>
-    <mergeCell ref="P47:P49"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="F37:F38"/>
-    <mergeCell ref="Q31:Q33"/>
-    <mergeCell ref="H31:H33"/>
-    <mergeCell ref="I31:I33"/>
-    <mergeCell ref="J31:J33"/>
-    <mergeCell ref="K31:K33"/>
-    <mergeCell ref="L31:L33"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="F31:F33"/>
-    <mergeCell ref="G31:G33"/>
-    <mergeCell ref="Q47:Q49"/>
-    <mergeCell ref="H47:H49"/>
-    <mergeCell ref="I47:I49"/>
-    <mergeCell ref="J47:J49"/>
-    <mergeCell ref="K47:K49"/>
-    <mergeCell ref="L47:L49"/>
-    <mergeCell ref="C44:C46"/>
-    <mergeCell ref="D44:D46"/>
-    <mergeCell ref="E44:E46"/>
-    <mergeCell ref="F44:F46"/>
-    <mergeCell ref="G44:G46"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="D47:D49"/>
-    <mergeCell ref="E47:E49"/>
-    <mergeCell ref="F47:F49"/>
-    <mergeCell ref="G47:G49"/>
-    <mergeCell ref="Q44:Q46"/>
-    <mergeCell ref="H44:H46"/>
-    <mergeCell ref="I44:I46"/>
-    <mergeCell ref="J44:J46"/>
-    <mergeCell ref="K44:K46"/>
-    <mergeCell ref="L44:L46"/>
-    <mergeCell ref="M44:M46"/>
-    <mergeCell ref="N44:N46"/>
-    <mergeCell ref="O44:O46"/>
-    <mergeCell ref="P44:P46"/>
-    <mergeCell ref="N34:N36"/>
-    <mergeCell ref="O34:O36"/>
-    <mergeCell ref="P34:P36"/>
-    <mergeCell ref="M37:M38"/>
-    <mergeCell ref="N37:N38"/>
-    <mergeCell ref="O37:O38"/>
-    <mergeCell ref="P37:P38"/>
-    <mergeCell ref="Q37:Q38"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="K37:K38"/>
-    <mergeCell ref="L37:L38"/>
-    <mergeCell ref="K34:K36"/>
-    <mergeCell ref="L34:L36"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="D34:D36"/>
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="F34:F36"/>
-    <mergeCell ref="G34:G36"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="M34:M36"/>
-    <mergeCell ref="Q28:Q30"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="D41:D43"/>
-    <mergeCell ref="E41:E43"/>
-    <mergeCell ref="F41:F43"/>
-    <mergeCell ref="G41:G43"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="F28:F30"/>
-    <mergeCell ref="G28:G30"/>
-    <mergeCell ref="H28:H30"/>
-    <mergeCell ref="I28:I30"/>
-    <mergeCell ref="J28:J30"/>
-    <mergeCell ref="K28:K30"/>
-    <mergeCell ref="L28:L30"/>
-    <mergeCell ref="M28:M30"/>
-    <mergeCell ref="N28:N30"/>
-    <mergeCell ref="O28:O30"/>
-    <mergeCell ref="P28:P30"/>
-    <mergeCell ref="Q34:Q36"/>
-    <mergeCell ref="H34:H36"/>
-    <mergeCell ref="I34:I36"/>
-    <mergeCell ref="J34:J36"/>
-    <mergeCell ref="Q41:Q43"/>
-    <mergeCell ref="H41:H43"/>
-    <mergeCell ref="I41:I43"/>
-    <mergeCell ref="J41:J43"/>
-    <mergeCell ref="K41:K43"/>
-    <mergeCell ref="L41:L43"/>
-    <mergeCell ref="M41:M43"/>
-    <mergeCell ref="N41:N43"/>
-    <mergeCell ref="O41:O43"/>
-    <mergeCell ref="P41:P43"/>
-    <mergeCell ref="M25:M26"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="O25:O26"/>
-    <mergeCell ref="P25:P26"/>
-    <mergeCell ref="Q25:Q26"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="K25:K26"/>
-    <mergeCell ref="L25:L26"/>
-    <mergeCell ref="J16:J18"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="L16:L18"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="Q19:Q21"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="D22:D24"/>
-    <mergeCell ref="E22:E24"/>
-    <mergeCell ref="F22:F24"/>
-    <mergeCell ref="G22:G24"/>
-    <mergeCell ref="H22:H24"/>
-    <mergeCell ref="I22:I24"/>
-    <mergeCell ref="J22:J24"/>
-    <mergeCell ref="K22:K24"/>
-    <mergeCell ref="L22:L24"/>
-    <mergeCell ref="M22:M24"/>
-    <mergeCell ref="N22:N24"/>
-    <mergeCell ref="O22:O24"/>
-    <mergeCell ref="P22:P24"/>
-    <mergeCell ref="Q22:Q24"/>
-    <mergeCell ref="P13:P15"/>
-    <mergeCell ref="Q13:Q15"/>
-    <mergeCell ref="L19:L21"/>
-    <mergeCell ref="M19:M21"/>
-    <mergeCell ref="N19:N21"/>
-    <mergeCell ref="O19:O21"/>
-    <mergeCell ref="P19:P21"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="F16:F18"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="E19:E21"/>
-    <mergeCell ref="F19:F21"/>
-    <mergeCell ref="G19:G21"/>
-    <mergeCell ref="H19:H21"/>
-    <mergeCell ref="I19:I21"/>
-    <mergeCell ref="J19:J21"/>
-    <mergeCell ref="K19:K21"/>
-    <mergeCell ref="G16:G18"/>
-    <mergeCell ref="H16:H18"/>
-    <mergeCell ref="I16:I18"/>
-    <mergeCell ref="M16:M18"/>
-    <mergeCell ref="H3:H5"/>
-    <mergeCell ref="N16:N18"/>
-    <mergeCell ref="O16:O18"/>
-    <mergeCell ref="P16:P18"/>
-    <mergeCell ref="Q16:Q18"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="F13:F15"/>
-    <mergeCell ref="G13:G15"/>
-    <mergeCell ref="H13:H15"/>
-    <mergeCell ref="I13:I15"/>
-    <mergeCell ref="J13:J15"/>
-    <mergeCell ref="K13:K15"/>
-    <mergeCell ref="L13:L15"/>
-    <mergeCell ref="M13:M15"/>
-    <mergeCell ref="N13:N15"/>
-    <mergeCell ref="O13:O15"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="F3:F5"/>
-    <mergeCell ref="G3:G5"/>
-    <mergeCell ref="L3:L5"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="I3:I5"/>
-    <mergeCell ref="J3:J5"/>
-    <mergeCell ref="K3:K5"/>
-    <mergeCell ref="Q3:Q5"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="N9:N10"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="P9:P10"/>
-    <mergeCell ref="Q9:Q10"/>
-    <mergeCell ref="M3:M5"/>
-    <mergeCell ref="N3:N5"/>
-    <mergeCell ref="O3:O5"/>
-    <mergeCell ref="P3:P5"/>
-    <mergeCell ref="D3:D5"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB94:XFD94 AB131:XFD131 AB76:XFD76 AB122:XFD122" xr:uid="{00000000-0002-0000-0400-000000000000}">
@@ -15476,187 +15480,187 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:B36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="27.1796875" customWidth="1"/>
+    <col min="2" max="2" width="27.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="1" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B1" s="1" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="2" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B2" s="1" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="3" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B4" s="1" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="5" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="5" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B5" s="1" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="6" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="6" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B6" s="1" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="7" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="7" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B7" s="1" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="8" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="8" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B8" s="1" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="9" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="9" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B9" s="1" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="10" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="10" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B10" s="1" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="11" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="11" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B11" s="1" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="12" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="12" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B12" s="1" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="13" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="13" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B13" s="1" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="14" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="14" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B14" s="1" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="15" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="15" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B15" s="1" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="16" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="16" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B16" s="1" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="17" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="17" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B17" s="1" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="18" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="18" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B18" s="1" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="19" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="19" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B19" s="1" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="20" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="20" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B20" s="1" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="21" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="21" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B21" s="1" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="22" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="22" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B22" s="1" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="23" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="23" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B23" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="24" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B24" s="1" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="25" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="25" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B25" s="1" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="26" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="26" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B26" s="1" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="27" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="27" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B27" s="1" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="28" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="28" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B28" s="1" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="29" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="29" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B29" s="1" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="30" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="30" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B30" s="1" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="31" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="31" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B31" s="1" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="32" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="32" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B32" s="1" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="33" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="33" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B33" s="1" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="34" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="34" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B34" s="1" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="35" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="35" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B35" s="1" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="36" spans="2:2" ht="16.5" x14ac:dyDescent="0.5">
+    <row r="36" spans="2:2" ht="18" x14ac:dyDescent="0.5">
       <c r="B36" s="39" t="s">
         <v>61</v>
       </c>
@@ -15672,126 +15676,126 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:BC108"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="16.5" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="18" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="20.453125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.26953125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.1796875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="21.54296875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="20.7265625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.81640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="21.81640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="26.1796875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="25.26953125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="24.453125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.26953125" style="1" customWidth="1"/>
-    <col min="12" max="17" width="17.7265625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="22.54296875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="15.54296875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="20.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.77734375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="26.21875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="25.21875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24.44140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.21875" style="1" customWidth="1"/>
+    <col min="12" max="17" width="17.77734375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="22.5546875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="15.5546875" style="1" customWidth="1"/>
     <col min="20" max="20" width="15" style="1" customWidth="1"/>
-    <col min="21" max="25" width="13.1796875" style="1" customWidth="1"/>
-    <col min="26" max="26" width="16.54296875" style="1" customWidth="1"/>
-    <col min="27" max="28" width="13.1796875" style="1" customWidth="1"/>
-    <col min="29" max="29" width="19.453125" style="1" customWidth="1"/>
-    <col min="30" max="30" width="13.81640625" style="1" customWidth="1"/>
-    <col min="31" max="31" width="13.1796875" style="1" customWidth="1"/>
-    <col min="32" max="32" width="13.453125" style="1" customWidth="1"/>
-    <col min="33" max="33" width="30.7265625" style="1" customWidth="1"/>
-    <col min="34" max="36" width="13.1796875" style="1" customWidth="1"/>
-    <col min="37" max="37" width="14.54296875" style="1" customWidth="1"/>
-    <col min="38" max="43" width="16.7265625" style="1" customWidth="1"/>
-    <col min="44" max="45" width="13.26953125" style="1" customWidth="1"/>
-    <col min="46" max="46" width="23.81640625" style="1" customWidth="1"/>
-    <col min="47" max="47" width="22.54296875" style="1" customWidth="1"/>
-    <col min="48" max="48" width="24.1796875" style="1" customWidth="1"/>
-    <col min="49" max="49" width="27.81640625" style="1" customWidth="1"/>
-    <col min="50" max="50" width="24.7265625" style="1" customWidth="1"/>
-    <col min="51" max="51" width="22.7265625" style="1" customWidth="1"/>
-    <col min="52" max="55" width="13.26953125" style="1" customWidth="1"/>
-    <col min="56" max="16384" width="11.453125" style="1"/>
+    <col min="21" max="25" width="13.21875" style="1" customWidth="1"/>
+    <col min="26" max="26" width="16.5546875" style="1" customWidth="1"/>
+    <col min="27" max="28" width="13.21875" style="1" customWidth="1"/>
+    <col min="29" max="29" width="19.44140625" style="1" customWidth="1"/>
+    <col min="30" max="30" width="13.77734375" style="1" customWidth="1"/>
+    <col min="31" max="31" width="13.21875" style="1" customWidth="1"/>
+    <col min="32" max="32" width="13.44140625" style="1" customWidth="1"/>
+    <col min="33" max="33" width="30.77734375" style="1" customWidth="1"/>
+    <col min="34" max="36" width="13.21875" style="1" customWidth="1"/>
+    <col min="37" max="37" width="14.5546875" style="1" customWidth="1"/>
+    <col min="38" max="43" width="16.77734375" style="1" customWidth="1"/>
+    <col min="44" max="45" width="13.21875" style="1" customWidth="1"/>
+    <col min="46" max="46" width="23.77734375" style="1" customWidth="1"/>
+    <col min="47" max="47" width="22.5546875" style="1" customWidth="1"/>
+    <col min="48" max="48" width="24.21875" style="1" customWidth="1"/>
+    <col min="49" max="49" width="27.77734375" style="1" customWidth="1"/>
+    <col min="50" max="50" width="24.77734375" style="1" customWidth="1"/>
+    <col min="51" max="51" width="22.77734375" style="1" customWidth="1"/>
+    <col min="52" max="55" width="13.21875" style="1" customWidth="1"/>
+    <col min="56" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:55" x14ac:dyDescent="0.5">
-      <c r="S1" s="103" t="s">
+      <c r="S1" s="104" t="s">
         <v>383</v>
       </c>
-      <c r="T1" s="103"/>
-      <c r="U1" s="103"/>
-      <c r="V1" s="103"/>
-      <c r="W1" s="103"/>
-      <c r="X1" s="103"/>
-      <c r="Y1" s="103"/>
-      <c r="Z1" s="103"/>
-      <c r="AA1" s="103"/>
-      <c r="AB1" s="103"/>
-      <c r="AC1" s="103"/>
-      <c r="AD1" s="103"/>
-      <c r="AE1" s="103"/>
-      <c r="AF1" s="103"/>
-      <c r="AG1" s="103"/>
+      <c r="T1" s="104"/>
+      <c r="U1" s="104"/>
+      <c r="V1" s="104"/>
+      <c r="W1" s="104"/>
+      <c r="X1" s="104"/>
+      <c r="Y1" s="104"/>
+      <c r="Z1" s="104"/>
+      <c r="AA1" s="104"/>
+      <c r="AB1" s="104"/>
+      <c r="AC1" s="104"/>
+      <c r="AD1" s="104"/>
+      <c r="AE1" s="104"/>
+      <c r="AF1" s="104"/>
+      <c r="AG1" s="104"/>
       <c r="AH1" s="5"/>
       <c r="AI1" s="5"/>
       <c r="AJ1" s="5"/>
-      <c r="AL1" s="103" t="s">
+      <c r="AL1" s="104" t="s">
         <v>384</v>
       </c>
-      <c r="AM1" s="103"/>
-      <c r="AN1" s="103"/>
-      <c r="AO1" s="103"/>
-      <c r="AP1" s="103"/>
-      <c r="AQ1" s="103"/>
+      <c r="AM1" s="104"/>
+      <c r="AN1" s="104"/>
+      <c r="AO1" s="104"/>
+      <c r="AP1" s="104"/>
+      <c r="AQ1" s="104"/>
       <c r="AR1" s="5"/>
       <c r="AS1" s="5"/>
-      <c r="AT1" s="103" t="s">
+      <c r="AT1" s="104" t="s">
         <v>385</v>
       </c>
-      <c r="AU1" s="103"/>
-      <c r="AV1" s="103"/>
-      <c r="AW1" s="103"/>
-      <c r="AX1" s="103"/>
-      <c r="AY1" s="103"/>
+      <c r="AU1" s="104"/>
+      <c r="AV1" s="104"/>
+      <c r="AW1" s="104"/>
+      <c r="AX1" s="104"/>
+      <c r="AY1" s="104"/>
       <c r="AZ1" s="5"/>
       <c r="BC1" s="5"/>
     </row>
     <row r="2" spans="1:55" x14ac:dyDescent="0.5">
-      <c r="L2" s="103" t="s">
+      <c r="L2" s="104" t="s">
         <v>386</v>
       </c>
-      <c r="M2" s="103"/>
-      <c r="N2" s="103"/>
-      <c r="O2" s="103"/>
-      <c r="P2" s="103"/>
-      <c r="Q2" s="103"/>
-      <c r="S2" s="104" t="s">
+      <c r="M2" s="104"/>
+      <c r="N2" s="104"/>
+      <c r="O2" s="104"/>
+      <c r="P2" s="104"/>
+      <c r="Q2" s="104"/>
+      <c r="S2" s="105" t="s">
         <v>387</v>
       </c>
-      <c r="T2" s="104"/>
-      <c r="U2" s="104"/>
-      <c r="V2" s="104"/>
-      <c r="W2" s="104"/>
-      <c r="X2" s="104"/>
-      <c r="Y2" s="104" t="s">
+      <c r="T2" s="105"/>
+      <c r="U2" s="105"/>
+      <c r="V2" s="105"/>
+      <c r="W2" s="105"/>
+      <c r="X2" s="105"/>
+      <c r="Y2" s="105" t="s">
         <v>388</v>
       </c>
-      <c r="Z2" s="104"/>
-      <c r="AA2" s="104"/>
-      <c r="AB2" s="104"/>
-      <c r="AC2" s="104" t="s">
+      <c r="Z2" s="105"/>
+      <c r="AA2" s="105"/>
+      <c r="AB2" s="105"/>
+      <c r="AC2" s="105" t="s">
         <v>389</v>
       </c>
-      <c r="AD2" s="104"/>
-      <c r="AE2" s="104"/>
-      <c r="AF2" s="104"/>
-      <c r="AG2" s="104"/>
+      <c r="AD2" s="105"/>
+      <c r="AE2" s="105"/>
+      <c r="AF2" s="105"/>
+      <c r="AG2" s="105"/>
       <c r="AH2" s="5"/>
       <c r="AI2" s="5"/>
       <c r="AJ2" s="5"/>
-      <c r="AL2" s="103"/>
-      <c r="AM2" s="103"/>
-      <c r="AN2" s="103"/>
-      <c r="AO2" s="103"/>
-      <c r="AP2" s="103"/>
-      <c r="AQ2" s="103"/>
+      <c r="AL2" s="104"/>
+      <c r="AM2" s="104"/>
+      <c r="AN2" s="104"/>
+      <c r="AO2" s="104"/>
+      <c r="AP2" s="104"/>
+      <c r="AQ2" s="104"/>
       <c r="AR2" s="5"/>
       <c r="AS2" s="5"/>
       <c r="AT2" s="5"/>
@@ -15888,16 +15892,16 @@
       <c r="AG3" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="AL3" s="105" t="s">
+      <c r="AL3" s="103" t="s">
         <v>412</v>
       </c>
-      <c r="AM3" s="105"/>
-      <c r="AN3" s="105"/>
-      <c r="AO3" s="105" t="s">
+      <c r="AM3" s="103"/>
+      <c r="AN3" s="103"/>
+      <c r="AO3" s="103" t="s">
         <v>413</v>
       </c>
-      <c r="AP3" s="105"/>
-      <c r="AQ3" s="105"/>
+      <c r="AP3" s="103"/>
+      <c r="AQ3" s="103"/>
       <c r="AR3" s="6"/>
       <c r="AS3" s="6"/>
       <c r="AT3" s="6"/>
@@ -20842,16 +20846,16 @@
     <sortCondition ref="AU5:AU66"/>
   </sortState>
   <mergeCells count="10">
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="S2:X2"/>
+    <mergeCell ref="Y2:AB2"/>
+    <mergeCell ref="AC2:AG2"/>
+    <mergeCell ref="AL2:AQ2"/>
     <mergeCell ref="AL3:AN3"/>
     <mergeCell ref="AO3:AQ3"/>
     <mergeCell ref="AT1:AY1"/>
     <mergeCell ref="S1:AG1"/>
     <mergeCell ref="AL1:AQ1"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="S2:X2"/>
-    <mergeCell ref="Y2:AB2"/>
-    <mergeCell ref="AC2:AG2"/>
-    <mergeCell ref="AL2:AQ2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
